--- a/data/verified_step1/step1_verified_dogs_latest.xlsx
+++ b/data/verified_step1/step1_verified_dogs_latest.xlsx
@@ -428,17 +428,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -495,36 +495,1838 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61579338393951</t>
+          <t>100081804938692</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>mazora</t>
+          <t>Redhill Boykin Spaniels</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=61579338393951</t>
+          <t>https://www.facebook.com/RedhillBoykinSpaniels</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cún cưng đạt chuẩn AI Thị Giác (P_dog=0.82)</t>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: boykin, spaniels)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>adult_dog (P=0.82)</t>
+          <t>non_dog (P=0.85)</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.8197</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>0.85</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>boykin, spaniels</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn2-4.fna.fbcdn.net/v/t39.30808-1/759871619_122169590066977946_1033339009703974655_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx736x743&amp;ctp=p80x80&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=edfymLxSlhcQ7kNvwGo_utM&amp;_nc_oc=AdqayCmQ7nC2NpGSO9ex1Wyhrr5K_kEpivoHEmG_aszu5kPYlUqVpl-IawGgowKzqec&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-4.fna&amp;_nc_gid=SWF0arEU3Hh5DrS2xgAVSQ&amp;_nc_ss=7b2a8&amp;oh=00_AQOo25OoOPF8iCLA_l1pu1blSev83dZoujlskE1Rq201nw&amp;oe=6ADB8071</t>
+          <t>https://scontent.fsgn2-10.fna.fbcdn.net/v/t39.30808-1/780104405_1042413175162171_4016551396372726401_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=jL82okdLHuoQ7kNvwG407i7&amp;_nc_oc=AdoueWHs-w3xyO8dxkD01gpGC24aZuBmuD_qIwoa7cZe-jWTAyMWAoqbGB3zLT-AFq0&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-10.fna&amp;_nc_gid=j0SeNJfMMuxlZ_D87eT2sw&amp;_nc_ss=7b2a8&amp;oh=00_AQPiLtZZxwXSdcH6Psq_ROhy73414EKsDDtCsOTtmyK0Rw&amp;oe=6ADBE33E</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>61552753361052</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Eliana’s Shih Tzu Home</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61552753361052</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: shih tzu, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>shih tzu</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-4.fna.fbcdn.net/v/t39.30808-1/838967521_122256247310091778_3876985609640057852_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1320x1320&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=SqzPzn63QhcQ7kNvwFLcTW7&amp;_nc_oc=Ador46L1zHe8l3A2JTGrIxwI7_EOQIrtFWNjYxDI1kX9F-1RgNVtONrOKQeURDKXU8s&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-4.fna&amp;_nc_gid=j0SeNJfMMuxlZ_D87eT2sw&amp;_nc_ss=7b2a8&amp;oh=00_AQPiuEKdWhlMJW8xACgF9C3gRtHIAXr_FoG-x7b5vk9p-g&amp;oe=6ADBC2A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>100068177232065</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Family Loved Golden Retrievers</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/FamilyLovedGoldenRetrievers</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: golden retrievers, retrievers, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>golden retrievers, retrievers, goldens</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-10.fna.fbcdn.net/v/t39.30808-1/326488783_909141020535285_7958935178343501974_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=D_B4l-l7Tr4Q7kNvwHKjELe&amp;_nc_oc=AdoNU-z88TOi00VA6AS6n6QexAOKCyQoETgBH4NIOubc8eydMfJzzmW62GCRS29uEBk&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-10.fna&amp;_nc_gid=j0SeNJfMMuxlZ_D87eT2sw&amp;_nc_ss=7b2a8&amp;oh=00_AQN1srU1G6SeyBAl7CcmUOJ70PbXmI4eHXnFxCKe5L2kvw&amp;oe=6ADBB2C8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>61591593760286</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>I Love Dogs Forge 'N Fetch</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61591593760286</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dogs, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>dogs</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-9.fna.fbcdn.net/v/t39.30808-1/753954046_122112615273386458_4146374115223244916_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1079x1078&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=Ni6iO7UEIhAQ7kNvwGHxjBt&amp;_nc_oc=AdpMIU3a5raFnQaDZiQSnTecMLIM1v8IvA_g2uV78ELnJCybO5lk1fnqtDO4jX2gBOs&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-9.fna&amp;_nc_gid=j0SeNJfMMuxlZ_D87eT2sw&amp;_nc_ss=7b2a8&amp;oh=00_AQOlZZCosOXFbJljb0KBckpIsMHMw9LWZ3SCz_cVgNww0A&amp;oe=6ADBD84D</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>61594775080228</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Yorkshih Pupco</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61594775080228</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: breeder, breeders, pupco)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.95)</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>breeder, breeders, pupco, yorkshire, shih tzu, pup, puppy, dog</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-11.fna.fbcdn.net/v/t39.30808-1/830513831_122102418099492502_4902222354387580447_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx800x800&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=yqqkmQ3XwqwQ7kNvwHAA1L2&amp;_nc_oc=AdqqiGgrByYtjyEA-9XGq5_zCmRQdGgY-61-mXsCSjxNsYcvtO5rG6AIjGR-jQsSVkE&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-11.fna&amp;_nc_gid=j0SeNJfMMuxlZ_D87eT2sw&amp;_nc_ss=7b2a8&amp;oh=00_AQPwvObvzfopmKxAynjQH3FGITqj-UP5rFSPaUtbdaPSNA&amp;oe=6ADBDCF5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>61551532070511</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Oakhaven Acres Aussies- AKC Australian Shepherds</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61551532070511</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: akc, shepherds, aussies)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.95)</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>akc, shepherds, aussies, australian shepherd</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-9.fna.fbcdn.net/v/t39.30808-1/427143042_122133778058051069_7335697382670797595_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1170x1170&amp;_nc_cat=102&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=S1XDbXl9UtEQ7kNvwF4VIVk&amp;_nc_oc=AdpxD3TijcgH-ylSuL5NrmZ1p7yt14Kbwa6RufX4zIILnneKdKQceOn1El-5DkI80-I&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-9.fna&amp;_nc_gid=8Zyh4tKsMAoxt1Skryj7PA&amp;_nc_ss=7b2a8&amp;oh=00_AQOxub4NnJJATL-nY2He740qF4xjBGX_kDJcZWkpFTnpZg&amp;oe=6ADBCAD2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>61588242310496</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bottom Top Basset’s</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61588242310496</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: basset)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>basset</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-4.fna.fbcdn.net/v/t39.30808-1/825267903_122124942699274743_5172081817443253017_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1254x1254&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=GKU7JoN128cQ7kNvwEAg_tV&amp;_nc_oc=Adp5wK-iRPL1nGSeTn3nSouGZKT-77wKX2f-GEt4J23kePf3pnnIMZYPzllcl12NlwQ&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-4.fna&amp;_nc_gid=8Zyh4tKsMAoxt1Skryj7PA&amp;_nc_ss=7b2a8&amp;oh=00_AQPfmOc7-4IEABA8EDi5ExLNh7hEjY3Wn5wlgmCDJPOcyg&amp;oe=6ADBE851</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>61594781858150</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Pawsome Daschund Puppies</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61594781858150</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: puppies, puppy, dog)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>puppies, puppy, dog</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-9.fna.fbcdn.net/v/t39.30808-1/839806917_122108759649492728_2289165301397021762_n.jpg?stp=c0.0.540.540a_cp0_dst-jpg_tt6&amp;cstp=mx540x540&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=UhsWya0bu5kQ7kNvwG_217d&amp;_nc_oc=Adqk7RM_dAOkyv9q40RlVNemofbyvYp40K5XZJzyvGfPv7pNhL0PWXtbXJsJTKEA5t4&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-9.fna&amp;_nc_gid=9RXVtVSJcH_YehD813TmiA&amp;_nc_ss=7b2a8&amp;oh=00_AQP6GAqyoklUO7MNX7_KuRevmML6Wq4mxYpkgdBB5nY4Tg&amp;oe=6ADBCC40</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>100063674375803</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Tambali Pembroke welsh corgis est. 1998</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Tambalicorgis</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: corgis, pembroke)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>corgis, pembroke</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-3.fna.fbcdn.net/v/t39.30808-1/628787013_1489668089832323_6013872381075739493_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1024x1024&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=78QAEnU19pYQ7kNvwGxYj8E&amp;_nc_oc=Adp1_ysIFfL_ILZmD1llcOAqAgQGpRh8-bu01Ugxw-mGRYxzUHPuROdFO-cMG6KK7Zk&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-3.fna&amp;_nc_gid=Zn6-z2pa6UnZwcMXwHj8pA&amp;_nc_ss=7b2a8&amp;oh=00_AQOqV8enGX20V0zZIYxfibxiUdMiQxfSOouiFAmfVpZq1Q&amp;oe=6ADBD927</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>61591427093472</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Franklineschipperkes Kennel</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61591427093472</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: kennel)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>kennel</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-8.fna.fbcdn.net/v/t39.30808-1/818936768_122125355133380903_6137241591030814058_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx845x845&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=hekGuXarAzkQ7kNvwFVhA0T&amp;_nc_oc=AdrhXQuZ2r2xWnXzPuaitY67ho4W1Uu2P0H-ChBUbnSTnlsjI6ZGXACi3GdXfBFuvw8&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-8.fna&amp;_nc_gid=Zn6-z2pa6UnZwcMXwHj8pA&amp;_nc_ss=7b2a8&amp;oh=00_AQPDZrF7f3U2GHRvEFi7VhQta_FphM2zl9sbwsoy6U9TuQ&amp;oe=6ADBDC59</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>61593315111061</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Dachshund Puppies For Adoption And Rehoming</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61593315111061</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: puppies, dachshund, puppy)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>puppies, dachshund, puppy, dog</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-4.fna.fbcdn.net/v/t39.30808-1/766890471_122093395911443837_496170756872224230_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx828x828&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=_khz97jsH30Q7kNvwEoZtd2&amp;_nc_oc=Ado0UpHZ06X4SiSL-zc9nhg5xJnYqeeKKk-KojS8mp0AZQZTVWTWzQrr86RZqRoPgmQ&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-4.fna&amp;_nc_gid=Zn6-z2pa6UnZwcMXwHj8pA&amp;_nc_ss=7b2a8&amp;oh=00_AQNtKwvo2HswAU6FKyem4e4JCb1bUvVekZH280ZSBOFFMQ&amp;oe=6ADBC14E</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>61594494459425</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Autumn's Aussies</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61594494459425</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: aussies, australian shepherd, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>aussies, australian shepherd</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-5.fna.fbcdn.net/v/t39.30808-1/820934527_2313498826091469_1498160885209143484_n.jpg?stp=c0.0.1536.1536a_cp0_dst-jpg_tt6&amp;cstp=mx1536x1536&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=5q-lLkTmkTgQ7kNvwGzlRsF&amp;_nc_oc=AdqpEePssaVnFqEWRqbIEjIOE91zoirz9ecUMgad6Nnvu3KYJLkjCKkA9yal-kdBxm8&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-5.fna&amp;_nc_gid=uxKwerkAu71oeJTU8diDNw&amp;_nc_ss=7b2a8&amp;oh=00_AQPVTpjZHmNj0QRRQNRedJtciHiCo-DxBtcS1hTKbOPChA&amp;oe=6ADBD529</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100040041254193</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Pelican &amp; Friends</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Pelican.and.friends</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AI Thị giác nhận diện chó trưởng thành (Adult=0.92, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0.9982</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-11.fna.fbcdn.net/v/t39.30808-1/292449699_737020464309322_6439185362993122046_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x959&amp;_nc_cat=102&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=LTSee7h_BCcQ7kNvwEsNRrO&amp;_nc_oc=AdrCb02kFEvmuIRIQOTUp0S6qkXZtwBZO4HukxPIxGAkOxKLtokQhVQhS3XEfy08hiU&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-11.fna&amp;_nc_gid=uxKwerkAu71oeJTU8diDNw&amp;_nc_ss=7b2a8&amp;oh=00_AQO28pmefPePozwXzomO3STNAAH-xMX3IiGsHAgRIKOdMg&amp;oe=6ADBB8F9</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>61568326866118</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Knock &amp; Bark Miniature Schnauzer.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/knockandbark</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: schnauzer, miniature schnauzer, P_dog=0.97)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>puppy (P=0.97)</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0.9741</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>schnauzer, miniature schnauzer</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-9.fna.fbcdn.net/v/t39.30808-1/779082815_122193681896610895_1254854747032187011_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1134x1122&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=N6pIjA1Ts40Q7kNvwGoXvFJ&amp;_nc_oc=AdrsvN9GYTA_JFSxb7DGQJu8Dv8YGt5E3brZ6TW9oCZANRmnCWIJo2Ir1xaQh61ChtY&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-9.fna&amp;_nc_gid=uxKwerkAu71oeJTU8diDNw&amp;_nc_ss=7b2a8&amp;oh=00_AQO1sv4XiQKg9d9I8Jc40FaE9WsQLQUKMuQMYzaAMyrr0w&amp;oe=6ADBC47C</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>61593913773814</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Responsible Breeder Mentorship Program</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61593913773814</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: breeder)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.95)</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>breeder</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-8.fna.fbcdn.net/v/t39.30808-1/789960755_10215640356039617_8106197547239706512_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1254x1254&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=zzjq-DH2fe4Q7kNvwGHGEwa&amp;_nc_oc=Ado-2hwNBIorQIVT9zd-qzC17gfV6ucydKQFaS0Ok5nOZ2auysfW0f9_XGOVRoDcV5w&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-8.fna&amp;_nc_gid=uxKwerkAu71oeJTU8diDNw&amp;_nc_ss=7b2a8&amp;oh=00_AQMcdWDNw9S4H3nuk3LCxVUC7AKzKyvpwgZ7R1jL0Vh8zw&amp;oe=6ADBC6C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>61551260240234</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>948 Cane Corso</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61551260240234</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: cane corso, corso)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>cane corso, corso</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-6.fna.fbcdn.net/v/t39.30808-1/405246072_122127983492042008_5422575660859054780_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1448x1448&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=1SHxRRdZeYcQ7kNvwGamyVp&amp;_nc_oc=AdptNJkAUw0hm7cNyVcCHwz4JCN5KhMk5Onivcd7bz9KgME_VP4iM0UeGpdZNHUg14I&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-6.fna&amp;_nc_gid=uxKwerkAu71oeJTU8diDNw&amp;_nc_ss=7b2a8&amp;oh=00_AQNkuYNPVt2P1CVbMEOs-qV_a8eoATd1quGKFLpeGaGvkw&amp;oe=6ADBE2AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>61594727570399</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Polly's Farm Pembroke Welsh Corgis &amp; Miniature Dachshunds</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61594727570399</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: corgis, pembroke, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>corgis, pembroke, dachshunds</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-8.fna.fbcdn.net/v/t39.30808-1/816996336_122112476091444595_648359482195584616_n.jpg?stp=c0.0.1220.1220a_cp0_dst-jpg_tt6&amp;cstp=mx1220x1220&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=jNFPSRSVDEMQ7kNvwFaeJes&amp;_nc_oc=AdrNnh_HCpL2LlpuavPbPhukTb6SAOcebtPTO69RzSrJLmwDFfrTbAoo5ybzxKn2B_Y&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-8.fna&amp;_nc_gid=uxKwerkAu71oeJTU8diDNw&amp;_nc_ss=7b2a8&amp;oh=00_AQMRZMoMteOvJgjV4ojJJYmzl0rqMWxmRfQlOAXvCSWlCw&amp;oe=6ADBD537</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>61594358583267</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>The Daily Doggo</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61594358583267</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: dog)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-8.fna.fbcdn.net/v/t39.30808-1/805763280_10176161854575422_4288387135773466042_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1024x1024&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=wJuGISXnO18Q7kNvwHlv8XJ&amp;_nc_oc=AdrZzh17CyEkwDOZ-X1POoBJhW6O122k1ByheNBnUTm8P51m9HFyETAr2vpvfdO7zo4&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-8.fna&amp;_nc_gid=uxKwerkAu71oeJTU8diDNw&amp;_nc_ss=7b2a8&amp;oh=00_AQMGuC7Ym2NbNkjZRFZ4imuJghav05ktPwMLB45l_CKs-w&amp;oe=6ADBB274</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>61594354922562</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Linda Rottweiler puppy for adoption</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61594354922562</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: puppy, rottweiler, dog)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>puppy, rottweiler, dog</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-5.fna.fbcdn.net/v/t39.30808-1/843551321_122120349219478497_6210589935705443458_n.jpg?stp=c0.0.720.720a_cp0_dst-jpg_tt6&amp;cstp=mx720x720&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=wIsUI-6JU8UQ7kNvwHqqZvz&amp;_nc_oc=Adom3NuRjs_KsSAB5Hewt6k85k7onmSOhhK7zhVY3nKo6XJq-t7S70K1DYWStHAWaoI&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-5.fna&amp;_nc_gid=T8OyLSbfD_RUaywOpxI1wg&amp;_nc_ss=7b2a8&amp;oh=00_AQPbPZ0-GCR1s3L5gG8znUOkuc6tVtcdkAHZ-HU-iEtipg&amp;oe=6ADBBFAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>61594523153572</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Heartland Schnauzer Puppies for Adoption &amp; Rehoming</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61594523153572</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: puppies, schnauzer, puppy)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>puppy (P=0.95)</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>puppies, schnauzer, puppy, dog</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-6.fna.fbcdn.net/v/t39.30808-1/810246531_122095004037484105_2142050790308638206_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1199x1208&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=UghD7V6oAswQ7kNvwGB-qMd&amp;_nc_oc=AdpsFmmR4TXTBkjAPwOOww3yg-jpuff3qEJXSa4EWzeOhsGPQb2ZZcfK4zhhO0CGF6E&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-6.fna&amp;_nc_gid=T8OyLSbfD_RUaywOpxI1wg&amp;_nc_ss=7b2a8&amp;oh=00_AQMqFzK4UxMhT44RvA5O50by2GZEOppi7JT_fkYOZz_ENg&amp;oe=6ADBC31B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>61593860979577</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Frenchie forever</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61593860979577</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: frenchie, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>frenchie</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-11.fna.fbcdn.net/v/t39.30808-1/799279242_122105264901462032_3104521594671155506_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx543x551&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=OcnA7d5hAX4Q7kNvwEpUVDU&amp;_nc_oc=AdqY-GBfZGTKiHM5tZp_EHsD0kMZhxtg1I6WQBICs9vxVBVjmfVwipR7a8gIjnr5Gc0&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-11.fna&amp;_nc_gid=T8OyLSbfD_RUaywOpxI1wg&amp;_nc_ss=7b2a8&amp;oh=00_AQOYv3IaIX1X-3pz9E8yJXA8mE7WK0O0JJoN5i9GDINfDw&amp;oe=6ADBCA73</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>100083675791629</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Scherrer Sweet Doodles</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=100083675791629</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: doodles)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>doodles</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-10.fna.fbcdn.net/v/t39.30808-1/721779281_971577072308144_4733230633786410222_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1314x1313&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=zcWKcDg78YAQ7kNvwGF0LBH&amp;_nc_oc=Adqs7rDIFyoXBosBZzy4mDYARTzeCjxQhMY6pB4MGFYWajE-hVPeZQ4r0d3UybXlpNw&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-10.fna&amp;_nc_gid=T8OyLSbfD_RUaywOpxI1wg&amp;_nc_ss=7b2a8&amp;oh=00_AQNTKhxqJBj9H62Hr7qgsRgX4qi3GW_NMx8v9udi9i1CWA&amp;oe=6ADBBF7B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>61593966614797</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Heavenly Dachshunds</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/HeavenlyDachshunds</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: dachshunds)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>dachshunds</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-6.fna.fbcdn.net/v/t39.30808-1/801924750_122106295533465553_3582681563697098512_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1230x1230&amp;_nc_cat=102&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=KvJeIlfrCPYQ7kNvwGEgTvv&amp;_nc_oc=AdrVTz0ffQIZpDDTK_pbOXF_pd6mwd8tyvpvl_R2VwCCYEPXAJumF2wNAOnSgLEWQ4M&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-6.fna&amp;_nc_gid=T8OyLSbfD_RUaywOpxI1wg&amp;_nc_ss=7b2a8&amp;oh=00_AQPFT_HJ_DFw_MK6eBRI1qFag2Rp2DLDMqUWy5bWPiXc4A&amp;oe=6ADBDBCA</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>100092010588302</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Family Dog Vaycay Pet Sitting</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=100092010588302</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dog, P_dog=0.93)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>puppy (P=0.93)</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0.9288</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-6.fna.fbcdn.net/v/t39.30808-1/343973399_950772516342723_8863261499823246812_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx500x500&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=eSwhdLXll_sQ7kNvwEcxgcv&amp;_nc_oc=AdojpLfSaDkQcpq0dXtScMCVrG2CCD-cPjrPdBIMF7GQvF7_ViU_R31EDX4Lw2LkR2U&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-6.fna&amp;_nc_gid=wWKKYrquLNWzktadeOAp4g&amp;_nc_ss=7b2a8&amp;oh=00_AQNvx4rmp-ieAeelegpwil6D_E0Hf65Cf5sE2-a_SPxWCA&amp;oe=6ADBCE9F</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>61593185582221</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ava the Australian Shepherd</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/avaaustralianshepherd</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: shepherd, australian shepherd, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>shepherd, australian shepherd</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-9.fna.fbcdn.net/v/t39.30808-1/819775887_122114813811439519_8141716067517529323_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx2047x2048&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=p8li4iTdwnEQ7kNvwGOgMWr&amp;_nc_oc=Adp2F8wdTjugRPzD0bNMOpnMfiTd3c1qxwrc2Z_im31ic63ngG4WAcUYTdhaxtV3tf8&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-9.fna&amp;_nc_gid=wWKKYrquLNWzktadeOAp4g&amp;_nc_ss=7b2a8&amp;oh=00_AQOHLlxgaBgXAGCehqQULypztjx-vCxcbA718UgF8PHhJQ&amp;oe=6ADBBDBB</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>100064337693424</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Karma's Dachshunds</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KarmasDoxies</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dachshunds, dachshund, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>dachshunds, dachshund</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-5.fna.fbcdn.net/v/t39.30808-1/464851534_940565858097995_8598999594224709224_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx2048x2048&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=ASrSVIkb3HEQ7kNvwFgnbI6&amp;_nc_oc=Adoch4h3Ftl9-TiJuXO22XIasOHjO7IVbInmD_Tn0c6Fa5k7H2fLAHlCQxC9ZUUPDoU&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-5.fna&amp;_nc_gid=8FMi0KV6vUSSOBm5lOuUKg&amp;_nc_ss=7b2a8&amp;oh=00_AQMjqxsmLC5sIxVdXIEFRHFDEySzqhknfwQRVLS-aBJtIg&amp;oe=6ADBB327</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>61594091660932</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Gluten Off Lab doo</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61594091660932</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: lab)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>lab</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-11.fna.fbcdn.net/v/t39.30808-1/787542034_122203646186759747_6776481724409914524_n.jpg?stp=c31.0.1143.1143a_cp6_dst-jpg_tt6&amp;cstp=mx1143x1143&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=q-oEuSzTkuEQ7kNvwGJ6bad&amp;_nc_oc=Adr0wPHKwHVH2kapA2BuH_wCUg12PWgXYldRibPIM8_LWkdwxZ8l-jJ8Pbo7d8dk7Gg&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-11.fna&amp;_nc_gid=8FMi0KV6vUSSOBm5lOuUKg&amp;_nc_ss=7b2a8&amp;oh=00_AQPlMPTpBMCBO3OBTXP0ST6QJ7mD8rvLRrF_jbO18BdHcg&amp;oe=6ADBE3DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>61552188929671</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PNP Dachshunds LLC</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61552188929671</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dachshunds, P_dog=0.84)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>puppy (P=0.84)</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0.8369</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>dachshunds</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-11.fna.fbcdn.net/v/t39.30808-1/485002964_122218989122072964_3967638820016736599_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx500x500&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=BdH9YpaNU3MQ7kNvwFBtMf0&amp;_nc_oc=Adq9e91hLjs3J3MQRBT41fhTXvoLhTPoRYc1Y2zXsstatMSXDuxXKnJW1GdhJFtIlME&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-11.fna&amp;_nc_gid=8FMi0KV6vUSSOBm5lOuUKg&amp;_nc_ss=7b2a8&amp;oh=00_AQOI78XEVRc7V6D4sflG_NssHJaD59PMTC8Ux8x1y1dczQ&amp;oe=6ADBD951</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>100077471214410</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Beaut Boxers</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/BeautBoxers</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: boxers)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>boxers</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-3.fna.fbcdn.net/v/t39.30808-1/819497572_1131867759405587_209993174050059485_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1254x1254&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=lz59M37rZNEQ7kNvwGdbnNm&amp;_nc_oc=AdoYYENngNQu_4Gsjdy4WVB1aqV9cwuNZkSyBkssVX7Y6CnJy2mZsKamFEJMQhSdZgU&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-3.fna&amp;_nc_gid=eWSb79gqwIoJ2uZMMRq1nw&amp;_nc_ss=7b2a8&amp;oh=00_AQMfWD_T72AY2YqyXbfDv9GRvW115vSIVC27mqFWQBZk3w&amp;oe=6ADBD021</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>61565119225294</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Magic Eagle Miniature Dachshunds</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/magiceagledoxies</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dachshunds, dachshund, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>dachshunds, dachshund</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-4.fna.fbcdn.net/v/t39.30808-1/783508002_122215974986503974_8899483936714065272_n.jpg?stp=c0.0.720.720a_cp0_dst-jpg_tt6&amp;cstp=mx720x720&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=ITID03AEcL0Q7kNvwGgRRxQ&amp;_nc_oc=AdoHqOw2CgyenWI6sdEcqlEk9x-3yCwcqXBJ2DW-TcLZ23kRBVu2ZhDPGyboOprdFzQ&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-4.fna&amp;_nc_gid=eWSb79gqwIoJ2uZMMRq1nw&amp;_nc_ss=7b2a8&amp;oh=00_AQOxUCyRwzN3CeXCoClV4Tq7bzKlHJdzSuv5TMrcnfNYAA&amp;oe=6ADBD6CF</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>61590471037312</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Loving Chihuahua Companions.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61590471037312</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: chihuahua, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>chihuahua</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-6.fna.fbcdn.net/v/t39.30808-1/843240300_122147696481349034_8275671350763553642_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx768x768&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=Vu4xLttt6PgQ7kNvwFUC-We&amp;_nc_oc=AdqOxNLRckgXjza8ZcK0Lz96F-DfoSx1odmAWFvUXCnNIdRRWn9fOR0boZT0s9-XFxc&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-6.fna&amp;_nc_gid=eWSb79gqwIoJ2uZMMRq1nw&amp;_nc_ss=7b2a8&amp;oh=00_AQMwT4UoN24x1E0nxCfMrhc33zvw26HKucDKgFDkfmKzPA&amp;oe=6ADBBDBA</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>100067623948311</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ivory &amp; Pine Goldens</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/IvoryandPineGoldens</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: goldens, golden retriever, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>goldens, golden retriever</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-7.fna.fbcdn.net/v/t39.30808-1/782615968_1384681697129282_5212663262034129488_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1933x1920&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=aZwKdecMfX8Q7kNvwG5E8rU&amp;_nc_oc=Adq7kNd4t1ND1PjvN0nHKyH2raeJ8L1sZnVWor_biV0RHIYu7RDoWHWMcr4tPGazhzA&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-7.fna&amp;_nc_gid=eWSb79gqwIoJ2uZMMRq1nw&amp;_nc_ss=7b2a8&amp;oh=00_AQOwthtfXNOmK8zSlpZtsV6ZgyjSv69YzY8-1kiPLrB9QQ&amp;oe=6ADBB77D</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>61591518293400</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>My Pawesome Boutique</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61591518293400</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Logo/Biển hiệu trại chó &amp; Từ khóa xác thực: dog, pet (không có mặt người)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.88)</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>dog, pet</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-5.fna.fbcdn.net/v/t39.30808-1/796969485_122127654063383943_1012761263205707610_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx2048x2048&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=cHm7XmwFU50Q7kNvwEoUe_2&amp;_nc_oc=AdqstLTGGiCAzkflZ3Pjw0stXtrU3TZgw2vJh6svpeM_2Mk9KD2Rv-QhCwEfPzbtkdA&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-5.fna&amp;_nc_gid=eWSb79gqwIoJ2uZMMRq1nw&amp;_nc_ss=7b2a8&amp;oh=00_AQOSCt9PCe2MHWNIqLHyyGoYUGwr-i7jaBWMX1YGK9dAEw&amp;oe=6ADBD8E7</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>61574790396010</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Gilded Glen Golden Retrievers</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61574790396010</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: golden retrievers, retrievers, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>golden retrievers, retrievers, goldens</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-11.fna.fbcdn.net/v/t39.30808-1/838966442_122181791750826346_2008532119779598613_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx2048x2043&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=jU4w85ESF-oQ7kNvwG2gvX1&amp;_nc_oc=Adr3sTnrhPSdyAzw-j-y3ExW8MG8eMOeGPZlTr-KbSagbRnXNBbMvUtcpUO9vS6c5aA&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-11.fna&amp;_nc_gid=rDRzbk4MF1d9kBrzrW4O6A&amp;_nc_ss=7b2a8&amp;oh=00_AQPTAhmdPbNl9Z2sr4IgdnAYJMvwQJik_mItbRyIh6puOQ&amp;oe=6ADBD19E</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>61591574075039</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Kristy's Cocker Spaniel</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61591574075039</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: cocker spaniel, cocker, P_dog=0.99)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>puppy (P=0.99)</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0.9916</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>cocker spaniel, cocker, spaniel</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-10.fna.fbcdn.net/v/t39.30808-1/738261667_122101295223385802_7358638121422389416_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1254x1254&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=CIKSmJKyPIkQ7kNvwHcOv22&amp;_nc_oc=AdpPH7Y0j8iD3b6lwp4uiTLnRDYRZOC8FHr82Ni9ZMtluI9fiWtaGerIPaqXoEFShlQ&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-10.fna&amp;_nc_gid=rDRzbk4MF1d9kBrzrW4O6A&amp;_nc_ss=7b2a8&amp;oh=00_AQMTMU8sYl7DGxJuhWyJuuy4kiVbu17ZkilWJ5CVRug0Sg&amp;oe=6ADBE746</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>61593002885039</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Melissa's intelligence and loving golden retriever puppies for adoption</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61593002885039</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: puppies, golden retriever, retriever)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>puppy (P=0.98)</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>puppies, golden retriever, retriever, puppy, dog, goldens</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-6.fna.fbcdn.net/v/t39.30808-1/775568628_122108102511433429_8072695245474966359_n.jpg?stp=c0.0.540.540a_cp0_dst-jpg_tt6&amp;cstp=mx540x540&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=xYTKzkWipWgQ7kNvwG8qTcY&amp;_nc_oc=AdrZz-GlnkMUONRpzLn-mdgcsWU74V3-vXTj4S6JObZrSbJybFr36H5jqaF65i1jipM&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-6.fna&amp;_nc_gid=rDRzbk4MF1d9kBrzrW4O6A&amp;_nc_ss=7b2a8&amp;oh=00_AQNVDuPqyIfVaa-VmsC1oc8Uv-MJo1ocySFjKGEScdk1cg&amp;oe=6ADBCE75</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>100057171741197</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>501 Shepherds</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/501shepherds</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: shepherds)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>shepherds</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-7.fna.fbcdn.net/v/t39.30808-1/724068393_1519028250012885_5132289179446813982_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1229x1229&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=TN9s3Sx1du0Q7kNvwHLKbKw&amp;_nc_oc=Adq-Mqq7owZSYO3LNDIQvn4U4kSRtApTHBHdPSWVvyrnWSkxaSaJ4j87bdXNjVVEMfI&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-7.fna&amp;_nc_gid=rDRzbk4MF1d9kBrzrW4O6A&amp;_nc_ss=7b2a8&amp;oh=00_AQM1-JB1suWJzyvHle3qfoyuGSu9pUIVLWWDrSs4le9HSQ&amp;oe=6ADBD364</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>100057622690855</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Doodle Denise Designs</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/doodledenisedesigns</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: doodle, P_dog=0.98)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>puppy (P=0.98)</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0.9835</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>doodle</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-6.fna.fbcdn.net/v/t39.30808-1/771694472_1511430180787724_1527618184332262383_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx360x360&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=s39yCkZxl7AQ7kNvwG-_K0z&amp;_nc_oc=AdpzqqyE5utNWfKstVJejtxpFbB101y4p7RVpdlUlpocZmiwGseeAkXejwi5ElIMgh0&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-6.fna&amp;_nc_gid=rDRzbk4MF1d9kBrzrW4O6A&amp;_nc_ss=7b2a8&amp;oh=00_AQNKXAzIOKWXkQbgqY35fg_9V6oqnpIeIwLyerkJRhHDTg&amp;oe=6ADBB534</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>100082969255746</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Sterling Run Retrievers</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SterlingRunRetrievers</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: retrievers)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>retrievers</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-6.fna.fbcdn.net/v/t39.30808-1/337398196_667116724869919_321658006795666061_n.jpg?stp=c40.40.770.770a_cp0_dst-jpg_tt6&amp;cstp=mx770x770&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=ofrjoYyYe5UQ7kNvwGppCOR&amp;_nc_oc=Adpqc310jk8Ul9RJdCphU-tSbIjWwTGP3NJZ5s_DbcRY-DSc5O5UT0iJVqq2MNGHbC8&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-6.fna&amp;_nc_gid=TDYxriTklat71Keid_AFYA&amp;_nc_ss=7b2a8&amp;oh=00_AQMKlu3KMTM7ROizGJhH2YrdvQSXpbLAEZDsY1MXZmPQOA&amp;oe=6ADBDEE4</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>100082062487155</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Kathryn,s Dachshunds</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=100082062487155</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: dachshunds)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>dachshunds</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-7.fna.fbcdn.net/v/t39.30808-1/792029861_1056334347111972_7582008765450913435_n.jpg?stp=c115.0.922.922a_cp0_dst-jpg_tt6&amp;cstp=mx922x922&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=L0Zi5NSWCoUQ7kNvwG3OJT_&amp;_nc_oc=AdpR7Yz6rLa2cEig3jmNww2ewh8uFc7pyBr9S60HWM2hzc21aYTcPQjSK0liDJuRQqU&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-7.fna&amp;_nc_gid=TDYxriTklat71Keid_AFYA&amp;_nc_ss=7b2a8&amp;oh=00_AQNYYKOFVRw2jVXFtlzI-PpCCb6IK3UeTDHqaMumk0AU5Q&amp;oe=6ADBBD3B</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>61590891808028</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Lil Debbies Darling Pets</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61590891808028</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AI Thị giác nhận diện chó trưởng thành (Adult=0.98, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-7.fna.fbcdn.net/v/t39.30808-1/789034386_122120608101363060_6764403641595204862_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx765x768&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=XJdAslo7VmkQ7kNvwGA-4Jw&amp;_nc_oc=AdrPfm-GI35QztTTp_V9opzjQIGJRWlXqff6wIcCdCS9xwn1ODIaTkx7g9BieJmEcug&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-7.fna&amp;_nc_gid=TDYxriTklat71Keid_AFYA&amp;_nc_ss=7b2a8&amp;oh=00_AQNFUFp6AgEl0s_MfhL0AkuYKLrrx-QSKrZCNREMZyzFyA&amp;oe=6ADBD1C8</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>100063635496530</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>My Cavalier Puppies</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CKCSpuppies</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: puppies, cavalier, puppy)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>puppies, cavalier, puppy, dog</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-6.fna.fbcdn.net/v/t39.30808-1/518654113_1292014406263064_7026757245242116044_n.jpg?stp=c183.0.733.733a_cp0_dst-jpg_tt6&amp;cstp=mx733x733&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=QMPH9tUW92sQ7kNvwEeb4LJ&amp;_nc_oc=AdofNmDHMz5p58sGMn8iGU9J0W9Z2Yfo7gq8hDIL6EtcyGbSWURPADWQA0QVHw_5U-Q&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-6.fna&amp;_nc_gid=DcywuF2wpVi51IbgKaoiHw&amp;_nc_ss=7b2a8&amp;oh=00_AQNKruxItNUgAEzN7zRgesffghgV4XANls_qRNmoci3HOQ&amp;oe=6ADBCBDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>61573687850343</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Lizzie’s Doxies</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Lizziesdoxies</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: doxies, dachshund)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>doxies, dachshund</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-7.fna.fbcdn.net/v/t39.30808-1/722606315_122197262402789595_3440958979727817129_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1254x1254&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=vo5jxlckh2AQ7kNvwHNTcBG&amp;_nc_oc=AdrxhFe0d-sRwKCtcxoJJagH1OSZ6v3fwnWY1aI2PkOOF3YaMuuSvHfd1zjpbJkJgEA&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-7.fna&amp;_nc_gid=DcywuF2wpVi51IbgKaoiHw&amp;_nc_ss=7b2a8&amp;oh=00_AQNV4w7oAkEVlLLzEaHbTGwCy42Hjsa4TYFE1oYeSUE5xw&amp;oe=6ADBE4AB</t>
         </is>
       </c>
     </row>

--- a/data/verified_step1/step1_verified_dogs_latest.xlsx
+++ b/data/verified_step1/step1_verified_dogs_latest.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -438,7 +438,7 @@
     <col width="45" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="38" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -495,40 +495,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61594731538136</t>
+          <t>990587153326216</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cocker Spaniel</t>
+          <t>Stephanie’s Puppy Colony</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=61594731538136</t>
+          <t>https://www.facebook.com/stephaniespuppycolony</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: cocker spaniel, cocker, P_dog=1.00)</t>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: puppy, dog)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>adult_dog (P=1.00)</t>
+          <t>non_dog (P=0.95)</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>cocker spaniel, cocker, spaniel</t>
+          <t>puppy, dog</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn9-1.fna.fbcdn.net/v/t39.30808-1/799676841_122095967409491051_5891965567465364453_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1290x1290&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=Ymha57zXx_IQ7kNvwE75H-2&amp;_nc_oc=AdpGUknfutZcuNbtFir-EQiA4Fpb-CaowPGR2RXfWqhMsFwnXU_26gK-dI-wKQ7L1JQ&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn9-1.fna&amp;_nc_gid=OzYFzMbeZJVf-lKCp-SPQw&amp;_nc_ss=7b2a8&amp;oh=00_AQNeWFbDXtU2-10Zz6hSG7j9u1IsICavyzOdmw1pyM6OfA&amp;oe=6ADD9673</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/696012345_990587153326216_235921294833267089_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1254x1254&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=aikJ6ENAQrYQ7kNvwHzmK2b&amp;_nc_oc=AdqqI-iDUD_hCiFmrgfgCpz2hWtdR8rV0a0DxEPdwE1mZo-KRs6Ak6lHvuK-FE2l-bc&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=TwICOsyVNFPr1QMO3-Kemw&amp;_nc_ss=7b2a8&amp;oh=00_AQOhEGIqNeYTF1X7iMkn_MglHpgDQ_GKTEsAjekMf7PQYg&amp;oe=6ADE3155</t>
         </is>
       </c>
     </row>
@@ -538,40 +538,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61595513098587</t>
+          <t>61595211969465</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>free dachshund puppies for adoption and rehoming</t>
+          <t>CaviCajun Kennels Cavapoos&amp;Cavaliers</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=61595513098587</t>
+          <t>https://www.facebook.com/profile.php?id=61595211969465</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: puppies, dachshund, puppy)</t>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: kennels, cavalier, poodle)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>puppy (P=1.00)</t>
+          <t>puppy (P=0.95)</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.9993</v>
+        <v>0.95</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>puppies, dachshund, puppy, dog</t>
+          <t>kennels, cavalier, poodle, cavapoo</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn9-1.fna.fbcdn.net/v/t39.30808-1/853444971_122096623407517103_2508650680056135816_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx2026x2048&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=mQc1kpvezdMQ7kNvwHZRa0X&amp;_nc_oc=Adpo3LNNAhd_KH1qGnc7tEnHME9Zsucl2edBgrcaDgrMrOZycKl1ru__TaGElpvYdmI&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn9-1.fna&amp;_nc_gid=OzYFzMbeZJVf-lKCp-SPQw&amp;_nc_ss=7b2a8&amp;oh=00_AQP_mRDcdtHIIcJy0PAqbPrV-xEYPoP0ZZu3lo742mSUWA&amp;oe=6ADD93C7</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/848993890_122103405711507065_2101132370405643345_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1094x1104&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=wmrDpQCvqlQQ7kNvwFOxhqS&amp;_nc_oc=Adrla7AbjZzoN3_2yJ034He_jcO1yaI3lkyAOaetgAU7c9X3M3kav7YZAhHw8_lZr5M&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=TwICOsyVNFPr1QMO3-Kemw&amp;_nc_ss=7b2a8&amp;oh=00_AQOEqW7QtF7l9HwdoYHNGGLzuQxBC5czwDBO2clPwQ2ZLw&amp;oe=6ADE4358</t>
         </is>
       </c>
     </row>
@@ -581,40 +581,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>100082804552805</t>
+          <t>1042413175162171</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chandra K9 Commando Working Dog Kennel Bengaluru</t>
+          <t>Redhill Boykin Spaniels</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=100082804552805</t>
+          <t>https://www.facebook.com/RedhillBoykinSpaniels</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>B2B Breeder / Trại chó xác thực qua NLP &amp; Từ khóa (dog, k9, kennel)</t>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: boykin, spaniels)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>puppy (P=1.00)</t>
+          <t>non_dog (P=0.85)</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>dog, k9, kennel, working dog</t>
+          <t>boykin, spaniels</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn9-1.fna.fbcdn.net/v/t39.30808-1/440336552_418005740969574_7966871653006742989_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=TSqss9UjjzMQ7kNvwEqAW_7&amp;_nc_oc=Adp1iZ3SualCnXsqbDmCfPhvxWtXtDKpSCOGgLhSZNY1MTbEDNoIkIoUZgfIASzZ3vg&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn9-1.fna&amp;_nc_gid=OzYFzMbeZJVf-lKCp-SPQw&amp;_nc_ss=7b2a8&amp;oh=00_AQPajJCoARtRJJ9fnm47pW2DKfmZnaypS230qW_9fjm2Og&amp;oe=6ADD9901</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/780104405_1042413175162171_4016551396372726401_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=Hgx53HAhos4Q7kNvwG7ULQ1&amp;_nc_oc=AdpiS4cY3jkx_YKrdp-Rj9a1puGI7YMNbmqeVw3eUC5EWiDLsTL54FCIBp6YfR7Be5Y&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=TwICOsyVNFPr1QMO3-Kemw&amp;_nc_ss=7b2a8&amp;oh=00_AQOQxEkwjDSowV8otco6c1JQ56-v5vGWyYuek0bVXHOn6g&amp;oe=6ADE4DFE</t>
         </is>
       </c>
     </row>
@@ -624,40 +624,40 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>61595221846060</t>
+          <t>61552753361052</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Greenhouse Yorkies</t>
+          <t>Eliana’s Shih Tzu Home</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=61595221846060</t>
+          <t>https://www.facebook.com/profile.php?id=61552753361052</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: yorkies, P_dog=0.57)</t>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: shih tzu, P_dog=1.00)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>adult_dog (P=0.57)</t>
+          <t>adult_dog (P=1.00)</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.5735</v>
+        <v>1</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>yorkies</t>
+          <t>shih tzu</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn9-1.fna.fbcdn.net/v/t39.30808-1/853675465_122107209423507394_8773063100519475064_n.jpg?stp=c0.0.736.736a_cp0_dst-jpg_tt6&amp;cstp=mx736x736&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=bB8XyIMvgRsQ7kNvwGim8JX&amp;_nc_oc=AdoTjxZ2WxtuRe32c29II2VguQWs76Y2BUjM_tvPdgg7yAGJ5sOwFJhduCcJmR7a19E&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn9-1.fna&amp;_nc_gid=fhmXFF3Ink9ZXE2wPEBPpQ&amp;_nc_ss=7b2a8&amp;oh=00_AQNsEn5_nWdrZUc4VnYs6PKbrCUmlExBTWSNOvwf2ngLJA&amp;oe=6ADDB286</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/838967521_122256247310091778_3876985609640057852_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1320x1320&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=1zSXN-tHW60Q7kNvwH-KUnB&amp;_nc_oc=Adrc_fhEGh1mGV1c3FFbYPc5uIAxmk8GO6m7mBgQ7fdJH3Ty_8f1QYh3GZO-pNFxepM&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=TwICOsyVNFPr1QMO3-Kemw&amp;_nc_ss=7b2a8&amp;oh=00_AQOZcfg42vUA05lqNSqu4Y70ZV55QgWmYsRDhYrkhjoCjw&amp;oe=6ADE65A5</t>
         </is>
       </c>
     </row>
@@ -667,40 +667,40 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>61595352087577</t>
+          <t>909141020535285</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>𝐑𝐑𝐨𝐬𝐞𝐰𝐨𝐨𝐝 𝐅𝐚𝐦𝐢𝐥𝐲 𝐏𝐨𝐨𝐝𝐥𝐞𝐬</t>
+          <t>Family Loved Golden Retrievers</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=61595352087577</t>
+          <t>https://www.facebook.com/FamilyLovedGoldenRetrievers</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: poodles)</t>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: golden retrievers, retrievers, P_dog=1.00)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>non_dog (P=0.85)</t>
+          <t>adult_dog (P=1.00)</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>poodles</t>
+          <t>golden retrievers, retrievers, goldens</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn9-1.fna.fbcdn.net/v/t39.30808-1/841343199_122096667393511736_1512305433899181321_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1024x1024&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=he-uNEKilPwQ7kNvwE9YVQQ&amp;_nc_oc=AdrUG9Gu0qAD4bm9caItGxTLIR7AMgGTpbK7KcS1TbCj-OuoZTbiKSyJXpewD5wqAvc&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn9-1.fna&amp;_nc_gid=qX2cURIoXveZ8q3ypB7H8g&amp;_nc_ss=7b2a8&amp;oh=00_AQMvvm2AE9kQ2p2xrwI0TP-vSOT6TE4BI-3eYD0GIIlkLA&amp;oe=6ADD853E</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/326488783_909141020535285_7958935178343501974_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=KCkBpAyH_X4Q7kNvwG_0u7p&amp;_nc_oc=AdqpaFrDKUJWZ0RjZaw1Ftlhn-WNPFO_xA6h11WNnO0orGxBODdWYLepdmmoMZCNvhU&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=TwICOsyVNFPr1QMO3-Kemw&amp;_nc_ss=7b2a8&amp;oh=00_AQMIEW37_fVuRYohQzq54OCkEnN8kOT6qgITq91MNuE5tg&amp;oe=6ADE55C8</t>
         </is>
       </c>
     </row>
@@ -710,31 +710,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>61594231833777</t>
+          <t>61591593760286</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Soft For Dogs</t>
+          <t>I Love Dogs Forge 'N Fetch</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=61594231833777</t>
+          <t>https://www.facebook.com/profile.php?id=61591593760286</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Logo/Biển hiệu trại chó &amp; Từ khóa xác thực: dogs (không có mặt người)</t>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dogs, P_dog=1.00)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>non_dog (P=0.88)</t>
+          <t>puppy (P=1.00)</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn9-1.fna.fbcdn.net/v/t39.30808-1/802072198_122099903445474394_6740119027340512439_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1080x1080&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=rcCG6sSZoRIQ7kNvwGM6gQC&amp;_nc_oc=AdqR-BTMwbz-9Aiz9ezsZ8NJrBHKMNmpV-HfjJj39gaqnj8aN6hYBIAfP72LD3tAZ-k&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn9-1.fna&amp;_nc_gid=5YXrbTSB9IDYBoSM_3Pp2Q&amp;_nc_ss=7b2a8&amp;oh=00_AQMRwWS84imM2_pXxgdzwhIK3ZaJkA4Qb6-mEBYeh6Eiqg&amp;oe=6ADD8C21</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/753954046_122112615273386458_4146374115223244916_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1079x1078&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=Ni6iO7UEIhAQ7kNvwEX3aDq&amp;_nc_oc=Adrz8cAAO2KmFnkZuRFza8iqAvdl16K9ANiruVQlW0Gf0J8H84W8375VrlBdRXWu9Uo&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=HP3imHJzQbwK5_D9L5y4YQ&amp;_nc_ss=7b2a8&amp;oh=00_AQO2tZAE_PYlpJU34MDZlFQD15hI23WOU7elgwST5qh6bw&amp;oe=6ADE430D</t>
         </is>
       </c>
     </row>
@@ -753,40 +753,40 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>61595290116794</t>
+          <t>61594775080228</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dachshund Puppies</t>
+          <t>Yorkshih Pupco</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=61595290116794</t>
+          <t>https://www.facebook.com/profile.php?id=61594775080228</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: puppies, dachshund, puppy)</t>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: breeder, breeders, pupco)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>adult_dog (P=1.00)</t>
+          <t>non_dog (P=0.95)</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>puppies, dachshund, puppy, dog</t>
+          <t>breeder, breeders, pupco, yorkshire, shih tzu, pup, puppy, dog</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn9-1.fna.fbcdn.net/v/t39.30808-1/853053396_122102754147509670_4567344291178019063_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1440x1440&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=W5qnkOd7qBsQ7kNvwFN9Goh&amp;_nc_oc=Adp5jXl5s2yJ4q7I28E2_oTqjqm-XINrrawXKX8qltpS6k4S8wCKSA3pvYBHqKTAKi0&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn9-1.fna&amp;_nc_gid=5YXrbTSB9IDYBoSM_3Pp2Q&amp;_nc_ss=7b2a8&amp;oh=00_AQPpBwkHSIwD5t77bIJBr7GNNOXT9pTfLZ5Cs1doB5AHHg&amp;oe=6ADDAA7C</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/830513831_122102418099492502_4902222354387580447_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx800x800&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=EsJnYIDH-P0Q7kNvwF_S4j8&amp;_nc_oc=AdolxT1vtUo6WEzYifsxx3wdxMH5qMFOkvd3Dv6_4e8LN-DXvU8v0UGTTe9ILvMYdig&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=HP3imHJzQbwK5_D9L5y4YQ&amp;_nc_ss=7b2a8&amp;oh=00_AQMxPuNOASl5lLsgUP07MQPcBGYSzfk1IVucqOeJFMC7Vw&amp;oe=6ADE47B5</t>
         </is>
       </c>
     </row>
@@ -796,40 +796,40 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>61595289693197</t>
+          <t>61551532070511</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Paradise Frenchies</t>
+          <t>Oakhaven Acres Aussies- AKC Australian Shepherds</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=61595289693197</t>
+          <t>https://www.facebook.com/profile.php?id=61551532070511</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: frenchies, frenchie)</t>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: akc, shepherds, aussies)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>non_dog (P=0.85)</t>
+          <t>non_dog (P=0.95)</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>frenchies, frenchie, french bulldog</t>
+          <t>akc, shepherds, aussies, australian shepherd</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn9-1.fna.fbcdn.net/v/t39.30808-1/848995038_122099228025509656_4048205347987609657_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx640x640&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=Fv4WV33GQWgQ7kNvwEv4qzX&amp;_nc_oc=AdrYYYPMyjK3d_DgwPY9BXatJnkie0jHpuHTJ9pvm75P0dPzVpOJmpn_DES7ZUwB7BM&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn9-1.fna&amp;_nc_gid=5YXrbTSB9IDYBoSM_3Pp2Q&amp;_nc_ss=7b2a8&amp;oh=00_AQNl8V2nFNTA-b9B-pkwF8pBbhDwHZgyNUWAp3-ML6Cy6Q&amp;oe=6ADDA41C</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/427143042_122133778058051069_7335697382670797595_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1170x1170&amp;_nc_cat=102&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=FXFGb8mH_kEQ7kNvwGyHi8Y&amp;_nc_oc=Adr7QPqn9TWmoPvg5PVMQ0XhE5o0u6TghXQJDLA6BUNVWjNBCwYGYaq3OEn_ED4uQBQ&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=HP3imHJzQbwK5_D9L5y4YQ&amp;_nc_ss=7b2a8&amp;oh=00_AQPI-hF_GlM-ASJS-S_YyieWtSZ-BN8gDQKxOwDEdZiD9Q&amp;oe=6ADE3592</t>
         </is>
       </c>
     </row>
@@ -839,40 +839,40 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>61594332256058</t>
+          <t>61588242310496</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>German Shepherd World</t>
+          <t>Bottom Top Basset’s</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=61594332256058</t>
+          <t>https://www.facebook.com/profile.php?id=61588242310496</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: german shepherd, shepherd, P_dog=0.89)</t>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: basset)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>puppy (P=0.89)</t>
+          <t>non_dog (P=0.85)</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.8907</v>
+        <v>0.85</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>german shepherd, shepherd</t>
+          <t>basset</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn9-1.fna.fbcdn.net/v/t39.30808-1/845925005_122118219585477741_7967768453723125043_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1254x1254&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=HflOslV30asQ7kNvwFtZQYz&amp;_nc_oc=AdreAgC6WxrN9g0mmdn_4edELu3837jsqawtp-noYL_XuakaVzqSac3qjlEwf2YMTl8&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn9-1.fna&amp;_nc_gid=5YXrbTSB9IDYBoSM_3Pp2Q&amp;_nc_ss=7b2a8&amp;oh=00_AQPEwHkwOF4qCxKv9-vrv6IWX41c_vSEXj86mmoEg2NiIw&amp;oe=6ADD876C</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/825267903_122124942699274743_5172081817443253017_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1254x1254&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=2Nx0sQfNEdYQ7kNvwEEHpwQ&amp;_nc_oc=AdrGG7ydqjr2dqoG-wqqKcuIg7HL53ZRvs1rZ-bH9HiCb8i1oCMaFNiwOeeYbo3oF-8&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=d0EBryXU1UgygpoH5zQ81A&amp;_nc_ss=7b2a8&amp;oh=00_AQMClSH_3Pr7Fo8AETARMoZoeLNCTt3jcoMjIHQnaOycgg&amp;oe=6ADE5311</t>
         </is>
       </c>
     </row>
@@ -882,22 +882,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100076508311524</t>
+          <t>61594781858150</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Golden Acres Poodle Farm</t>
+          <t>Pawsome Daschund Puppies</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=100076508311524</t>
+          <t>https://www.facebook.com/profile.php?id=61594781858150</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: poodle, goldens, P_dog=1.00)</t>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: puppies, puppy, dog)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -910,12 +910,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>poodle, goldens</t>
+          <t>puppies, puppy, dog</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn9-1.fna.fbcdn.net/v/t39.30808-1/467616410_586656400561299_7608861023452401031_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1536x1536&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=DyEWKZ-Grj4Q7kNvwFm_K9C&amp;_nc_oc=Adqq3Tum4IVuxbmj4xYpZ9WpR1BfyFXu6hX_wpSoZ8Wf2OACCK9Jz2fs4E10oe9mRXU&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn9-1.fna&amp;_nc_gid=c87bpxjG87PHL7f6oGAZnA&amp;_nc_ss=7b2a8&amp;oh=00_AQNyibrJCO1a34DlH-LpivM-brzQM7GIP7rlSlT34IJRsQ&amp;oe=6ADD856B</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/839806917_122108759649492728_2289165301397021762_n.jpg?stp=c0.0.540.540a_cp0_dst-jpg_tt6&amp;cstp=mx540x540&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=2UvAoPM99EEQ7kNvwHxkrkL&amp;_nc_oc=AdrESu6ut2JVf7qtFuvRkFUswJlaQsHriYHFk6b4MTqBZbGWen-GSMMdPRKni2uuexU&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=y4c-DeRUU11dMr2UX5j8JA&amp;_nc_ss=7b2a8&amp;oh=00_AQOcoHhyZy0YKhN_sW7QUn2AkPK_Kt9grNoXmvOIjVca6w&amp;oe=6ADE3700</t>
         </is>
       </c>
     </row>
@@ -925,22 +925,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>61594975678956</t>
+          <t>61594195772352</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ABC VIP DOGS</t>
+          <t>Jose MiniPuppies</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=61594975678956</t>
+          <t>https://www.facebook.com/profile.php?id=61594195772352</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dogs, P_dog=1.00)</t>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: puppy, dog)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -949,16 +949,16 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>dogs</t>
+          <t>puppy, dog</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn9-1.fna.fbcdn.net/v/t39.30808-1/855164329_122110907037499189_877532196647671267_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1145x1146&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=5eKwegKjQesQ7kNvwG6OmjZ&amp;_nc_oc=Adr791HwdvEcX3kI8Uakb6zOhBK1g_1GzYmngDfNdOuYLEX4GzXMV5MEje7f_h4e7PY&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn9-1.fna&amp;_nc_gid=c87bpxjG87PHL7f6oGAZnA&amp;_nc_ss=7b2a8&amp;oh=00_AQO2M9yk1JYAS2Er27WrImuYK0P3rAa393X0C7pvxST2ig&amp;oe=6ADDAB34</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/855646238_122124401871473192_6657591073014986332_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1053x1050&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=fpciUtL0RqgQ7kNvwHvDvml&amp;_nc_oc=AdrkOtpO68tVOeHRBbQwGKPXDMKv6JIvACChqv-71ZDlzMeiB7o2zM5DLwzGe9EmfD0&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=y4c-DeRUU11dMr2UX5j8JA&amp;_nc_ss=7b2a8&amp;oh=00_AQMoTuCS5W_fKqhvV4ISSWCagCN3T9NI57HCSPDhZ-PTug&amp;oe=6ADE44CF</t>
         </is>
       </c>
     </row>
@@ -968,40 +968,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>61595707163197</t>
+          <t>1489668089832323</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lakeland Terrier México “Apolo’s Kennel”</t>
+          <t>Tambali Pembroke welsh corgis est. 1998</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=61595707163197</t>
+          <t>https://www.facebook.com/Tambalicorgis</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: kennel, terrier)</t>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: corgis, pembroke)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>puppy (P=1.00)</t>
+          <t>non_dog (P=0.85)</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>kennel, terrier</t>
+          <t>corgis, pembroke</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn9-1.fna.fbcdn.net/v/t39.30808-1/856470882_1773914520573760_7422947113457391568_n.jpg?stp=c102.0.819.819a_cp0_dst-jpg_tt6&amp;cstp=mx819x819&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=FshYNu6WXGYQ7kNvwEr-ckj&amp;_nc_oc=AdqkcB7O6QYjx1skN5BVUUh2-E725fSZ8XPu_aCQfwfEtf5wm6B2d_GkVicPXatP6zU&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn9-1.fna&amp;_nc_gid=FXpsU-C4WHklfFJi9gwJnA&amp;_nc_ss=7b2a8&amp;oh=00_AQMj1o6d6gKHb4XGveQ93Kpjk_cgONZVeQ6yF0_0VjMhmw&amp;oe=6ADDAFD8</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/628787013_1489668089832323_6013872381075739493_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1024x1024&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=78QAEnU19pYQ7kNvwEdF6M8&amp;_nc_oc=AdqAnBQs8chVNgaUNDOr8kq6u2kY2oQbBOhBaUC2ubsjg00tY22Uoqr4BrypC7ogkqs&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=y4c-DeRUU11dMr2UX5j8JA&amp;_nc_ss=7b2a8&amp;oh=00_AQOjodBjmS0_j0jf04e6FFQTcRlWSJdebAz-hS_2oJMDmQ&amp;oe=6ADE43E7</t>
         </is>
       </c>
     </row>
@@ -1011,40 +1011,40 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>61594915838249</t>
+          <t>61591427093472</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lone Wolf Breeders</t>
+          <t>Franklineschipperkes Kennel</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=61594915838249</t>
+          <t>https://www.facebook.com/profile.php?id=61591427093472</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: breeders)</t>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: kennel)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>non_dog (P=0.95)</t>
+          <t>adult_dog (P=1.00)</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>breeders</t>
+          <t>kennel</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn9-1.fna.fbcdn.net/v/t39.30808-1/834526337_4533280666990767_3514549822735751705_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx2000x2000&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=e5HOzZ7aqDYQ7kNvwFuIwkZ&amp;_nc_oc=AdrVKGHkEW0WKmTMXZR4TsSU1iwRmKg4Y5iQ8ixGaLqTtelyN_NfKPk1Ss9MQ3O6-gM&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn9-1.fna&amp;_nc_gid=lUlIPiuATfIiJ4DmKfT7jg&amp;_nc_ss=7b2a8&amp;oh=00_AQPKpaExbgEjnMFR0E0Th96WvxMPTCc34l7L7lrxgFJm4w&amp;oe=6ADDA91F</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/818936768_122125355133380903_6137241591030814058_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx845x845&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=hekGuXarAzkQ7kNvwHSLKZB&amp;_nc_oc=AdqK_Pk1Vju7cJ78k38AbjiQxUPrgFfqzKFFtHS2yrhswAlzj4zAGl4mSWwr17GgtnE&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=y4c-DeRUU11dMr2UX5j8JA&amp;_nc_ss=7b2a8&amp;oh=00_AQMzIJk4OUXN4yGcWHszoK85mTqgYKndymGkEqsoTNLJQA&amp;oe=6ADE4719</t>
         </is>
       </c>
     </row>
@@ -1054,22 +1054,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>122093871489524357</t>
+          <t>61593315111061</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dolly Baby K9</t>
+          <t>Dachshund Puppies For Adoption And Rehoming</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/dollybaby.k9</t>
+          <t>https://www.facebook.com/profile.php?id=61593315111061</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: k9, P_dog=1.00)</t>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: puppies, dachshund, puppy)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>k9</t>
+          <t>puppies, dachshund, puppy, dog</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn9-1.fna.fbcdn.net/v/t39.30808-1/853578531_122093871489524357_34586254437558028_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx2045x2045&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=-7CGtPEIG2oQ7kNvwGfqgj7&amp;_nc_oc=Adp0CBstvJhKh3O4TgAx-nAE5qicnpjYjbP1gnMVo8B_tHfpYeL5n5cx13xlqwI_fzw&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn9-1.fna&amp;_nc_gid=TgUWhg1SebUjfM7T33oocg&amp;_nc_ss=7b2a8&amp;oh=00_AQOxh-NOuP7ZUZ8fFeBmaWXQnMkDEL4J05LDJ58OrhKyKw&amp;oe=6ADD9FD0</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/766890471_122093395911443837_496170756872224230_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx828x828&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=ihYNssPKU28Q7kNvwEDZvlm&amp;_nc_oc=AdqfWpLpHPGHmq5J1VKT75IRA-swUUjpIjvWsYT90OxxjutYdMMbhfsCNAn4PNy0MWw&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=te8O4haIQ4bk8DSKcpSW7w&amp;_nc_ss=7b2a8&amp;oh=00_AQPNEnh89ueLb2hAllV42UGJvYLcE2NzbTXbGNnpUNbBcg&amp;oe=6ADE644E</t>
         </is>
       </c>
     </row>
@@ -1097,22 +1097,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>61590419896312</t>
+          <t>61594494459425</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Elite schnauzers rescue and rehoming</t>
+          <t>Autumn's Aussies</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=61590419896312</t>
+          <t>https://www.facebook.com/profile.php?id=61594494459425</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: schnauzers, P_dog=1.00)</t>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: aussies, australian shepherd, P_dog=1.00)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>schnauzers</t>
+          <t>aussies, australian shepherd</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn9-1.fna.fbcdn.net/v/t39.30808-1/724194389_122110156515347329_8649130341916381884_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1122x1123&amp;_nc_cat=102&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=xW_6qi_H5e4Q7kNvwEssLh2&amp;_nc_oc=AdpA_9mf_FS6lPe0OAd1y1tgdYQ0FI7UJN46Tw8OdA8xQrTExJ5WLAJ2IKORHhsE6bI&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn9-1.fna&amp;_nc_gid=8AMkU5dntGptVHluBOghoA&amp;_nc_ss=7b2a8&amp;oh=00_AQMhuDm_n4qQ_jAHavwe08OA9H02h91HaVZtfvK5NsAGRA&amp;oe=6ADDA89B</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/820934527_2313498826091469_1498160885209143484_n.jpg?stp=c0.0.1536.1536a_cp0_dst-jpg_tt6&amp;cstp=mx1536x1536&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=L03VojkGVZUQ7kNvwEmEWpp&amp;_nc_oc=AdpipHwllV-m4oMIMNa0_C0eG8SYzQy-oJfiT01OuEgrzjRX2jTN7jORBhtWizMu61Y&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=te8O4haIQ4bk8DSKcpSW7w&amp;_nc_ss=7b2a8&amp;oh=00_AQNfQcVVHLnK9yS2OtyTyFQgwP57d7A1ktjz9h38oZnzCQ&amp;oe=6ADE3FE9</t>
         </is>
       </c>
     </row>
@@ -1140,40 +1140,83 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>61595452472675</t>
+          <t>122193681896610895</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pirate Paws Grooming</t>
+          <t>Knock &amp; Bark Miniature Schnauzer.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=61595452472675</t>
+          <t>https://www.facebook.com/knockandbark</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: grooming, P_dog=0.99)</t>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: schnauzer, miniature schnauzer, P_dog=0.97)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>puppy (P=0.99)</t>
+          <t>puppy (P=0.97)</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.9918</v>
+        <v>0.9741</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>grooming</t>
+          <t>schnauzer, miniature schnauzer</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn9-1.fna.fbcdn.net/v/t39.30808-1/853048787_122099219925515082_8756659190000181024_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1122x1122&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=0jh7DvbrDsYQ7kNvwE4lQyX&amp;_nc_oc=Ado7fFc3THZO5EG5QEeKo_IEwWlYhzmJHvU8I6vW45Hb8k_1UC8WOaiAON-RH7rJFmM&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn9-1.fna&amp;_nc_gid=8AMkU5dntGptVHluBOghoA&amp;_nc_ss=7b2a8&amp;oh=00_AQNGtrPFr_KwF_pccehe1nDymlRpDGwXrlRfeAMbj4Ib8A&amp;oe=6ADD928D</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/779082815_122193681896610895_1254854747032187011_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1134x1122&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=N6pIjA1Ts40Q7kNvwGdzE7P&amp;_nc_oc=AdrKeMKHlIsY0Br3XkfOG2hxdtvMcmsaoRr84NZDJtCAPggWhjKVPK2mvbARdKt8b_A&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=te8O4haIQ4bk8DSKcpSW7w&amp;_nc_ss=7b2a8&amp;oh=00_AQOOfR66vg0y_jnCql9iGHPoPUknemKeAXcUGQCJ5PiMOw&amp;oe=6ADE2F3C</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>61593913773814</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Responsible Breeder Mentorship Program</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61593913773814</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: breeder)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.95)</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>breeder</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/789960755_10215640356039617_8106197547239706512_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1254x1254&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=Ch42QEEATugQ7kNvwFkzIiS&amp;_nc_oc=Adphq4c8PLfRYPgEWIBtAJ-M8vh4V2BGW3LeogcZpQlX8eo9WjUJSbS0GNyPedmjw2I&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=te8O4haIQ4bk8DSKcpSW7w&amp;_nc_ss=7b2a8&amp;oh=00_AQN5vX4_YYWjLBxPJO8dxEdp3cxECEz9Rb-Q5FKwVbRF9w&amp;oe=6ADE3182</t>
         </is>
       </c>
     </row>

--- a/data/verified_step1/step1_verified_dogs_latest.xlsx
+++ b/data/verified_step1/step1_verified_dogs_latest.xlsx
@@ -428,17 +428,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="41" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -495,40 +495,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>990587153326216</t>
+          <t>1596373112283090</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Stephanie’s Puppy Colony</t>
+          <t>Firestorm Goldens</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/stephaniespuppycolony</t>
+          <t>https://www.facebook.com/Firestormgoldenretrievers</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: puppy, dog)</t>
+          <t>Logo/Biển hiệu trại chó &amp; Từ khóa xác thực: goldens, golden retriever (không có mặt người)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>non_dog (P=0.95)</t>
+          <t>non_dog (P=0.88)</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>puppy, dog</t>
+          <t>goldens, golden retriever</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/696012345_990587153326216_235921294833267089_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1254x1254&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=aikJ6ENAQrYQ7kNvwHzmK2b&amp;_nc_oc=AdqqI-iDUD_hCiFmrgfgCpz2hWtdR8rV0a0DxEPdwE1mZo-KRs6Ak6lHvuK-FE2l-bc&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=TwICOsyVNFPr1QMO3-Kemw&amp;_nc_ss=7b2a8&amp;oh=00_AQOhEGIqNeYTF1X7iMkn_MglHpgDQ_GKTEsAjekMf7PQYg&amp;oe=6ADE3155</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/760620948_1596373112283090_8124428097826053721_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx2048x2048&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=vQnoXfeIIAsQ7kNvwHIoe36&amp;_nc_oc=AdrRtHloFKO14oKmFm4hrxLJpVJ4J7kh_TzW0hNMYCZans0AfawhWRHo7Z3aypBJT94&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=wvBxwXYC6uM7D2fsdOPfcA&amp;_nc_ss=7b2a8&amp;oh=00_AQOkNojq6ZxWDllkdngCdZ4PW99tEfnO33OsWHCSOcAGlQ&amp;oe=6ADE3BAE</t>
         </is>
       </c>
     </row>
@@ -538,40 +538,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61595211969465</t>
+          <t>1058086863465242</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CaviCajun Kennels Cavapoos&amp;Cavaliers</t>
+          <t>Smooches for Pooches</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=61595211969465</t>
+          <t>https://www.facebook.com/loveofpups</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: kennels, cavalier, poodle)</t>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: puppy, dog, puppies)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>puppy (P=0.95)</t>
+          <t>adult_dog (P=1.00)</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>kennels, cavalier, poodle, cavapoo</t>
+          <t>puppy, dog, puppies</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/848993890_122103405711507065_2101132370405643345_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1094x1104&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=wmrDpQCvqlQQ7kNvwFOxhqS&amp;_nc_oc=Adrla7AbjZzoN3_2yJ034He_jcO1yaI3lkyAOaetgAU7c9X3M3kav7YZAhHw8_lZr5M&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=TwICOsyVNFPr1QMO3-Kemw&amp;_nc_ss=7b2a8&amp;oh=00_AQOEqW7QtF7l9HwdoYHNGGLzuQxBC5czwDBO2clPwQ2ZLw&amp;oe=6ADE4358</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/773486111_1058086863465242_344051957738859922_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1086x1086&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=Q7quceSoaj4Q7kNvwF9pNK7&amp;_nc_oc=Adowdu5feQlQuIM8cMskP7WX5FjSWMgEsv_sozqn4lbdoomeyZZ9i1cgkZALzQ_EcJw&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=wvBxwXYC6uM7D2fsdOPfcA&amp;_nc_ss=7b2a8&amp;oh=00_AQPT5aTSyALYre6DBDFzRfYcLpomB41eaR0Yd_XXP1HpHg&amp;oe=6ADE5BEE</t>
         </is>
       </c>
     </row>
@@ -581,40 +581,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1042413175162171</t>
+          <t>122095855856933094</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Redhill Boykin Spaniels</t>
+          <t>Bailey’s Cajun Canines LLC</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/RedhillBoykinSpaniels</t>
+          <t>https://www.facebook.com/Baileyscajuncaninesllc</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: boykin, spaniels)</t>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: canines, P_dog=0.97)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>non_dog (P=0.85)</t>
+          <t>puppy (P=0.97)</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.85</v>
+        <v>0.972</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>boykin, spaniels</t>
+          <t>canines</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/780104405_1042413175162171_4016551396372726401_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=Hgx53HAhos4Q7kNvwG7ULQ1&amp;_nc_oc=AdpiS4cY3jkx_YKrdp-Rj9a1puGI7YMNbmqeVw3eUC5EWiDLsTL54FCIBp6YfR7Be5Y&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=TwICOsyVNFPr1QMO3-Kemw&amp;_nc_ss=7b2a8&amp;oh=00_AQOQxEkwjDSowV8otco6c1JQ56-v5vGWyYuek0bVXHOn6g&amp;oe=6ADE4DFE</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/514361430_122095855856933094_4776262354102086972_n.jpg?stp=c28.0.1160.1160a_cp0_dst-jpg_tt6&amp;cstp=mx1160x1160&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=m0gI9fOCmkoQ7kNvwGO-eGL&amp;_nc_oc=AdqJQi32T0aUKVaL0X8svdciqgtz6-VRtlNQtRrFAGJkrxaU99PDIDKzTD8ht5sJWus&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=pelMvMZbxRbN5uMQAHbS1Q&amp;_nc_ss=7b2a8&amp;oh=00_AQPUrI0rX38UHxgde2mbt26ygN76wHf49g8rVFWk6NIEZw&amp;oe=6ADE463A</t>
         </is>
       </c>
     </row>
@@ -624,40 +624,40 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>61552753361052</t>
+          <t>1117686188781662</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eliana’s Shih Tzu Home</t>
+          <t>Doodles of Louisiana</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=61552753361052</t>
+          <t>https://www.facebook.com/DoodlesOfLouisiana</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: shih tzu, P_dog=1.00)</t>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: doodles)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>adult_dog (P=1.00)</t>
+          <t>non_dog (P=0.85)</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>shih tzu</t>
+          <t>doodles</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/838967521_122256247310091778_3876985609640057852_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1320x1320&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=1zSXN-tHW60Q7kNvwH-KUnB&amp;_nc_oc=Adrc_fhEGh1mGV1c3FFbYPc5uIAxmk8GO6m7mBgQ7fdJH3Ty_8f1QYh3GZO-pNFxepM&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=TwICOsyVNFPr1QMO3-Kemw&amp;_nc_ss=7b2a8&amp;oh=00_AQOZcfg42vUA05lqNSqu4Y70ZV55QgWmYsRDhYrkhjoCjw&amp;oe=6ADE65A5</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/280485787_1117686188781662_1773497406171536734_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx958x958&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=LvizzZ2jb68Q7kNvwG_-9za&amp;_nc_oc=AdrZ-6_n-rmjW0KFAoW248Qa7-Eczl9XNgE3CdB6Cq7AoXc4Fs6vhLSe-W2mKmgREGY&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=pelMvMZbxRbN5uMQAHbS1Q&amp;_nc_ss=7b2a8&amp;oh=00_AQM9fvnyUQYVOsjpJy_ToFyAqhYK3KsK0rzWs8DVS57_BQ&amp;oe=6ADE69C2</t>
         </is>
       </c>
     </row>
@@ -667,22 +667,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>909141020535285</t>
+          <t>122348323874064888</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Family Loved Golden Retrievers</t>
+          <t>16 Paws Goldens</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/FamilyLovedGoldenRetrievers</t>
+          <t>https://www.facebook.com/16PawsGoldens</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: golden retrievers, retrievers, P_dog=1.00)</t>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: goldens, golden retriever, P_dog=1.00)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -695,12 +695,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>golden retrievers, retrievers, goldens</t>
+          <t>goldens, golden retriever</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/326488783_909141020535285_7958935178343501974_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=KCkBpAyH_X4Q7kNvwG_0u7p&amp;_nc_oc=AdqpaFrDKUJWZ0RjZaw1Ftlhn-WNPFO_xA6h11WNnO0orGxBODdWYLepdmmoMZCNvhU&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=TwICOsyVNFPr1QMO3-Kemw&amp;_nc_ss=7b2a8&amp;oh=00_AQMIEW37_fVuRYohQzq54OCkEnN8kOT6qgITq91MNuE5tg&amp;oe=6ADE55C8</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/853441685_122348323874064888_3226424898471433872_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx2048x2048&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=12YKDZ0y3MoQ7kNvwE4F8SH&amp;_nc_oc=AdrfUphicb9s0yPRDTKRQnAvg71twQHzKlsle2Vw5awfEH_wJTAAcLXSKsN9Sw-esN0&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=pelMvMZbxRbN5uMQAHbS1Q&amp;_nc_ss=7b2a8&amp;oh=00_AQPwNvT5R7xJXZlNuaZ4yyZlfF4OD0i7s4Y4_3A1PRpPOQ&amp;oe=6ADE3E17</t>
         </is>
       </c>
     </row>
@@ -710,40 +710,40 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>61591593760286</t>
+          <t>167575609124204</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>I Love Dogs Forge 'N Fetch</t>
+          <t>Brandi’s Southern Doodles &amp; Poodles, LLC</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=61591593760286</t>
+          <t>https://www.facebook.com/BrandisSouthernDoodlesandPoodles</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dogs, P_dog=1.00)</t>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: poodles, doodles)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>puppy (P=1.00)</t>
+          <t>non_dog (P=0.85)</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>dogs</t>
+          <t>poodles, doodles</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/753954046_122112615273386458_4146374115223244916_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1079x1078&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=Ni6iO7UEIhAQ7kNvwEX3aDq&amp;_nc_oc=Adrz8cAAO2KmFnkZuRFza8iqAvdl16K9ANiruVQlW0Gf0J8H84W8375VrlBdRXWu9Uo&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=HP3imHJzQbwK5_D9L5y4YQ&amp;_nc_ss=7b2a8&amp;oh=00_AQO2tZAE_PYlpJU34MDZlFQD15hI23WOU7elgwST5qh6bw&amp;oe=6ADE430D</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/290874043_167575609124204_8051960330153032304_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=YQZymWJ3-y4Q7kNvwHVe2fB&amp;_nc_oc=Adrqjmp_DmhWnTiBimR93_qm4amEiy2QcxlW4LVFWkB4fnSxouhi4zAZCyA3UsGb2NM&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=pelMvMZbxRbN5uMQAHbS1Q&amp;_nc_ss=7b2a8&amp;oh=00_AQO4M9H1q9mWC48B-W7v-25Td6UV0PlCaHWQh7MMjNl9Lg&amp;oe=6ADE4DE9</t>
         </is>
       </c>
     </row>
@@ -753,40 +753,40 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>61594775080228</t>
+          <t>224535483884124</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yorkshih Pupco</t>
+          <t>Galaxy Golden Retrievers</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=61594775080228</t>
+          <t>https://www.facebook.com/galaxygoldenretrievers</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: breeder, breeders, pupco)</t>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: golden retrievers, retrievers)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>non_dog (P=0.95)</t>
+          <t>non_dog (P=0.85)</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>breeder, breeders, pupco, yorkshire, shih tzu, pup, puppy, dog</t>
+          <t>golden retrievers, retrievers, goldens</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/830513831_122102418099492502_4902222354387580447_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx800x800&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=EsJnYIDH-P0Q7kNvwF_S4j8&amp;_nc_oc=AdolxT1vtUo6WEzYifsxx3wdxMH5qMFOkvd3Dv6_4e8LN-DXvU8v0UGTTe9ILvMYdig&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=HP3imHJzQbwK5_D9L5y4YQ&amp;_nc_ss=7b2a8&amp;oh=00_AQMxPuNOASl5lLsgUP07MQPcBGYSzfk1IVucqOeJFMC7Vw&amp;oe=6ADE47B5</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/368381343_224535483884124_7262168979554044494_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx956x960&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=Fozk3m8ofZUQ7kNvwHk3Dev&amp;_nc_oc=AdoY_TUW80Ixf2IsE5KV1w5oPOPzi_ptw2OQjkTde9VcAhkPP-WYZF--YAjl8MBH2kY&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=W3-63CRhSeTi0X6tRyjinQ&amp;_nc_ss=7b2a8&amp;oh=00_AQMz1t90gf2bxZRAOPmzS40sKuqK23udRILxoIZ99ekuEA&amp;oe=6ADE565A</t>
         </is>
       </c>
     </row>
@@ -796,40 +796,40 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>61551532070511</t>
+          <t>727311656940554</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Oakhaven Acres Aussies- AKC Australian Shepherds</t>
+          <t>Golden Puppies</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=61551532070511</t>
+          <t>https://www.facebook.com/goldenpuppies2004</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: akc, shepherds, aussies)</t>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: puppies, puppy, dog)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>non_dog (P=0.95)</t>
+          <t>adult_dog (P=1.00)</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>akc, shepherds, aussies, australian shepherd</t>
+          <t>puppies, puppy, dog, goldens</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/427143042_122133778058051069_7335697382670797595_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1170x1170&amp;_nc_cat=102&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=FXFGb8mH_kEQ7kNvwGyHi8Y&amp;_nc_oc=Adr7QPqn9TWmoPvg5PVMQ0XhE5o0u6TghXQJDLA6BUNVWjNBCwYGYaq3OEn_ED4uQBQ&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=HP3imHJzQbwK5_D9L5y4YQ&amp;_nc_ss=7b2a8&amp;oh=00_AQPI-hF_GlM-ASJS-S_YyieWtSZ-BN8gDQKxOwDEdZiD9Q&amp;oe=6ADE3592</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/530235894_727311656940554_8801302940165924973_n.jpg?stp=c507.540.1422.1423a_cp0_dst-jpg_tt6&amp;cstp=mx1422x1423&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=Hoq6NuCogV8Q7kNvwEB7GfP&amp;_nc_oc=AdpXKgkhgvSL0qJc_-82d8oRZNf-J9oCE9OiklOMFQxEb4pDVAiVaMHpK6DlJcTS0zU&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=W3-63CRhSeTi0X6tRyjinQ&amp;_nc_ss=7b2a8&amp;oh=00_AQMVJL9PwWeX-QIYDMIBsq4DIFAw8HukSKTfDaAwYbrD_A&amp;oe=6ADE3D7D</t>
         </is>
       </c>
     </row>
@@ -839,40 +839,40 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>61588242310496</t>
+          <t>1713907270555802</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bottom Top Basset’s</t>
+          <t>Beauty and the Beast Shih Tzu</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=61588242310496</t>
+          <t>https://www.facebook.com/BeautysShihTzu</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: basset)</t>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: shih tzu, P_dog=1.00)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>non_dog (P=0.85)</t>
+          <t>adult_dog (P=1.00)</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>basset</t>
+          <t>shih tzu</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/825267903_122124942699274743_5172081817443253017_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1254x1254&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=2Nx0sQfNEdYQ7kNvwEEHpwQ&amp;_nc_oc=AdrGG7ydqjr2dqoG-wqqKcuIg7HL53ZRvs1rZ-bH9HiCb8i1oCMaFNiwOeeYbo3oF-8&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=d0EBryXU1UgygpoH5zQ81A&amp;_nc_ss=7b2a8&amp;oh=00_AQMClSH_3Pr7Fo8AETARMoZoeLNCTt3jcoMjIHQnaOycgg&amp;oe=6ADE5311</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/854337368_1713907270555802_3166642091340115423_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=WCfvxI38zx8Q7kNvwEjrNu9&amp;_nc_oc=Adob3XQ7o0vsKe8Rgt9BxFxPabxD6XcuUfYHgIvADOzYI7RB2-3hq8lgzeK92i34aLk&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=W3-63CRhSeTi0X6tRyjinQ&amp;_nc_ss=7b2a8&amp;oh=00_AQPuUc2qyLkwN3kVJj2jjdzhdI_z8WbladuDG1hEbwWhcQ&amp;oe=6ADE3F59</t>
         </is>
       </c>
     </row>
@@ -882,27 +882,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>61594781858150</t>
+          <t>122193969698840038</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pawsome Daschund Puppies</t>
+          <t>Shih Tzu Love'r</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=61594781858150</t>
+          <t>https://www.facebook.com/shihtzulovers02</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: puppies, puppy, dog)</t>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: shih tzu, P_dog=1.00)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>adult_dog (P=1.00)</t>
+          <t>puppy (P=1.00)</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -910,12 +910,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>puppies, puppy, dog</t>
+          <t>shih tzu</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/839806917_122108759649492728_2289165301397021762_n.jpg?stp=c0.0.540.540a_cp0_dst-jpg_tt6&amp;cstp=mx540x540&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=2UvAoPM99EEQ7kNvwHxkrkL&amp;_nc_oc=AdrESu6ut2JVf7qtFuvRkFUswJlaQsHriYHFk6b4MTqBZbGWen-GSMMdPRKni2uuexU&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=y4c-DeRUU11dMr2UX5j8JA&amp;_nc_ss=7b2a8&amp;oh=00_AQOcoHhyZy0YKhN_sW7QUn2AkPK_Kt9grNoXmvOIjVca6w&amp;oe=6ADE3700</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/751883689_122193969698840038_5392462303461976167_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1254x1254&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=6neccbWYohAQ7kNvwE-4Qlt&amp;_nc_oc=AdpFYRDPh9z0v8qmF9i8I8G5BGFYcr52nPHR8mg1--IoueFm2rurFK3muXwEoS5i8Ng&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=W3-63CRhSeTi0X6tRyjinQ&amp;_nc_ss=7b2a8&amp;oh=00_AQMjw30eryhv4uI7o57_txEXm663N77XwQ5uan6uE4rzdw&amp;oe=6ADE3DD7</t>
         </is>
       </c>
     </row>
@@ -925,40 +925,40 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>61594195772352</t>
+          <t>134105013011006</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jose MiniPuppies</t>
+          <t>Lil’ Bit’s Shih Tzu PUPS of NC</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=61594195772352</t>
+          <t>https://www.facebook.com/lilbitspups</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: puppy, dog)</t>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: pups, shih tzu, puppy)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>puppy (P=1.00)</t>
+          <t>adult_dog (P=1.00)</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>puppy, dog</t>
+          <t>pups, shih tzu, puppy, dog, puppies</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/855646238_122124401871473192_6657591073014986332_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1053x1050&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=fpciUtL0RqgQ7kNvwHvDvml&amp;_nc_oc=AdrkOtpO68tVOeHRBbQwGKPXDMKv6JIvACChqv-71ZDlzMeiB7o2zM5DLwzGe9EmfD0&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=y4c-DeRUU11dMr2UX5j8JA&amp;_nc_ss=7b2a8&amp;oh=00_AQMoTuCS5W_fKqhvV4ISSWCagCN3T9NI57HCSPDhZ-PTug&amp;oe=6ADE44CF</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/349320352_134105013011006_4377198773058659903_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1170x1170&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=dWgF00YllvgQ7kNvwFoblVY&amp;_nc_oc=AdpcjWk8V-ykX3wgyPm0TKbA-DOC6ueNtT7fBoymBY0v1cD56Oc5vKGCFhYxxsgQkeo&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=W3-63CRhSeTi0X6tRyjinQ&amp;_nc_ss=7b2a8&amp;oh=00_AQNoIW2nGko2V6-xIK8cQ1KYCC5mlJGs3kvJHcor3w8_KQ&amp;oe=6ADE4B68</t>
         </is>
       </c>
     </row>
@@ -968,22 +968,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1489668089832323</t>
+          <t>103750072031616</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tambali Pembroke welsh corgis est. 1998</t>
+          <t>Willow Oak Farm White Labs</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/Tambalicorgis</t>
+          <t>https://www.facebook.com/willowoakfarmwhitelabs</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: corgis, pembroke)</t>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: labs)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>corgis, pembroke</t>
+          <t>labs</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/628787013_1489668089832323_6013872381075739493_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1024x1024&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=78QAEnU19pYQ7kNvwEdF6M8&amp;_nc_oc=AdqAnBQs8chVNgaUNDOr8kq6u2kY2oQbBOhBaUC2ubsjg00tY22Uoqr4BrypC7ogkqs&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=y4c-DeRUU11dMr2UX5j8JA&amp;_nc_ss=7b2a8&amp;oh=00_AQOjodBjmS0_j0jf04e6FFQTcRlWSJdebAz-hS_2oJMDmQ&amp;oe=6ADE43E7</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/239326327_103750072031616_8246519884499016640_n.png?stp=c226.0.1036.1036a_cp0_dst-png&amp;cstp=mx1036x1036&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=VoCMcdQms2kQ7kNvwHGcnao&amp;_nc_oc=Adolgiyk1m5c6zXpxZMofnxHL--Gs1-I-UW6ScqXoisJ0xL8nPGLYLJdAvZFomXgTFM&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=x_eCW6M3_boLIlu9Xz2UVw&amp;_nc_ss=7b2a8&amp;oh=00_AQPnsGKYXLsOnCGlBqyLiHfmVnP-v7OBQ_Wz0737M7M1ug&amp;oe=6ADE538E</t>
         </is>
       </c>
     </row>
@@ -1011,17 +1011,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>61591427093472</t>
+          <t>1930354481705111</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Franklineschipperkes Kennel</t>
+          <t>Prairie Creek Kennel</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=61591427093472</t>
+          <t>https://www.facebook.com/PrairieCreekKennel</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>adult_dog (P=1.00)</t>
+          <t>puppy (P=1.00)</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/818936768_122125355133380903_6137241591030814058_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx845x845&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=hekGuXarAzkQ7kNvwHSLKZB&amp;_nc_oc=AdqK_Pk1Vju7cJ78k38AbjiQxUPrgFfqzKFFtHS2yrhswAlzj4zAGl4mSWwr17GgtnE&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=y4c-DeRUU11dMr2UX5j8JA&amp;_nc_ss=7b2a8&amp;oh=00_AQMzIJk4OUXN4yGcWHszoK85mTqgYKndymGkEqsoTNLJQA&amp;oe=6ADE4719</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/787924714_1930354481705111_8023386184839815697_n.jpg?stp=c0.0.1118.1118a_cp0_dst-jpg_tt6&amp;cstp=mx1118x1118&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=QUF7osBv29sQ7kNvwEs5iLa&amp;_nc_oc=AdqzG72wd25ONZrGn15WhiecIpy6h64OKmGOdQAQGnirgeFQKii7WnI_hZJHUtU9xtU&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=x_eCW6M3_boLIlu9Xz2UVw&amp;_nc_ss=7b2a8&amp;oh=00_AQN0rHZ7YxrseRLDb_rYSmbJf4O0iMqScL10q5MBAWNd0g&amp;oe=6ADE686E</t>
         </is>
       </c>
     </row>
@@ -1054,27 +1054,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>61593315111061</t>
+          <t>434190195177077</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dachshund Puppies For Adoption And Rehoming</t>
+          <t>Creme of the Crop Dachshunds</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=61593315111061</t>
+          <t>https://www.facebook.com/englishcreammniaturedachshunds</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: puppies, dachshund, puppy)</t>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dachshunds, P_dog=1.00)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>puppy (P=1.00)</t>
+          <t>adult_dog (P=1.00)</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>puppies, dachshund, puppy, dog</t>
+          <t>dachshunds</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/766890471_122093395911443837_496170756872224230_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx828x828&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=ihYNssPKU28Q7kNvwEDZvlm&amp;_nc_oc=AdqfWpLpHPGHmq5J1VKT75IRA-swUUjpIjvWsYT90OxxjutYdMMbhfsCNAn4PNy0MWw&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=te8O4haIQ4bk8DSKcpSW7w&amp;_nc_ss=7b2a8&amp;oh=00_AQPNEnh89ueLb2hAllV42UGJvYLcE2NzbTXbGNnpUNbBcg&amp;oe=6ADE644E</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/277559970_434190195177077_5291667728461596283_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1242x1242&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=Af-UHt10BhYQ7kNvwFKMFhu&amp;_nc_oc=Adq4GLGLEcT48PJP2FGuJITIIl12xW0MqVFnpLVN8ykxJJA2HyfIdvsvGCC6h1FU1bc&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=nWISXh2b8NBnOu23IzNfEw&amp;_nc_ss=7b2a8&amp;oh=00_AQM5eU7ropmhOAZJKXeubfTKexBF8l2_bxbDjXlsMd7GCw&amp;oe=6ADE5970</t>
         </is>
       </c>
     </row>
@@ -1097,22 +1097,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>61594494459425</t>
+          <t>122094153387516831</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Autumn's Aussies</t>
+          <t>Salvați cățeii de la Popești-Iași</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=61594494459425</t>
+          <t>https://www.facebook.com/SalvatiCateiiDeLaPopesti</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: aussies, australian shepherd, P_dog=1.00)</t>
+          <t>AI Thị giác nhận diện cún con sắc nét (Puppy=0.93, P_dog=1.00)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1123,14 +1123,10 @@
       <c r="G16" t="n">
         <v>1</v>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>aussies, australian shepherd</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/820934527_2313498826091469_1498160885209143484_n.jpg?stp=c0.0.1536.1536a_cp0_dst-jpg_tt6&amp;cstp=mx1536x1536&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=L03VojkGVZUQ7kNvwEmEWpp&amp;_nc_oc=AdpipHwllV-m4oMIMNa0_C0eG8SYzQy-oJfiT01OuEgrzjRX2jTN7jORBhtWizMu61Y&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=te8O4haIQ4bk8DSKcpSW7w&amp;_nc_ss=7b2a8&amp;oh=00_AQNfQcVVHLnK9yS2OtyTyFQgwP57d7A1ktjz9h38oZnzCQ&amp;oe=6ADE3FE9</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/847550055_122094153387516831_8056891142274074859_n.jpg?stp=c0.70.1500.1500a_cp0_dst-jpg_tt6&amp;cstp=mx1500x1500&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=nmoR64VsmXUQ7kNvwEu-_DI&amp;_nc_oc=AdomVof3gO20cj8WM2qq8xPDzwL6bA_d9roWWyw4iv-1kmsLcGgfYkQpEnN8p3eD9XU&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=nWISXh2b8NBnOu23IzNfEw&amp;_nc_ss=7b2a8&amp;oh=00_AQPm9thyDGnE8BmYq268iL2SrHXYV6zqXBKFWTM_JFnHew&amp;oe=6ADE44D3</t>
         </is>
       </c>
     </row>
@@ -1140,40 +1136,40 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>122193681896610895</t>
+          <t>1138905091673145</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Knock &amp; Bark Miniature Schnauzer.</t>
+          <t>Hyde Park Cavaliers</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/knockandbark</t>
+          <t>https://www.facebook.com/hyde.park.cavaliers.2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: schnauzer, miniature schnauzer, P_dog=0.97)</t>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: cavalier, P_dog=1.00)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>puppy (P=0.97)</t>
+          <t>adult_dog (P=1.00)</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.9741</v>
+        <v>1</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>schnauzer, miniature schnauzer</t>
+          <t>cavalier</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/779082815_122193681896610895_1254854747032187011_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1134x1122&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=N6pIjA1Ts40Q7kNvwGdzE7P&amp;_nc_oc=AdrKeMKHlIsY0Br3XkfOG2hxdtvMcmsaoRr84NZDJtCAPggWhjKVPK2mvbARdKt8b_A&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=te8O4haIQ4bk8DSKcpSW7w&amp;_nc_ss=7b2a8&amp;oh=00_AQOOfR66vg0y_jnCql9iGHPoPUknemKeAXcUGQCJ5PiMOw&amp;oe=6ADE2F3C</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/552894529_1138905091673145_212893724666853543_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=tb5968Uum_8Q7kNvwF09BmR&amp;_nc_oc=AdoFUfd1wwWodC1ZSndp48NB8ar3nHcoCGpKz5UNfbs0gWdyTk1cWhfg9G3Y9Oc3Zfg&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=nWISXh2b8NBnOu23IzNfEw&amp;_nc_ss=7b2a8&amp;oh=00_AQPdYZGVKj-ASBzvtzllRKTEsYbVY2rLz1IXMuYvrfXbEA&amp;oe=6ADE3C32</t>
         </is>
       </c>
     </row>
@@ -1183,22 +1179,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>61593913773814</t>
+          <t>122123912342347266</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Responsible Breeder Mentorship Program</t>
+          <t>MiniDox Pups</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/profile.php?id=61593913773814</t>
+          <t>https://www.facebook.com/minidoxpups</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: breeder)</t>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: pups, puppy, dog)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1211,12 +1207,141 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>breeder</t>
+          <t>pups, puppy, dog, puppies</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/789960755_10215640356039617_8106197547239706512_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1254x1254&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=Ch42QEEATugQ7kNvwFkzIiS&amp;_nc_oc=Adphq4c8PLfRYPgEWIBtAJ-M8vh4V2BGW3LeogcZpQlX8eo9WjUJSbS0GNyPedmjw2I&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=te8O4haIQ4bk8DSKcpSW7w&amp;_nc_ss=7b2a8&amp;oh=00_AQN5vX4_YYWjLBxPJO8dxEdp3cxECEz9Rb-Q5FKwVbRF9w&amp;oe=6ADE3182</t>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/453383289_122123912342347266_388495722924606013_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx641x640&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=7ES5_0tyRfwQ7kNvwE7D1XU&amp;_nc_oc=AdoJKwODYxrlaVzua3BMEIZXWnPoDGVcIzpl-s17BjcF6334NCCXeGLHf_hoeChYpcE&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=nWISXh2b8NBnOu23IzNfEw&amp;_nc_ss=7b2a8&amp;oh=00_AQM0t8pBAyJVLRiu7WdcIl_F9jMEktziUP3kgcN99WY55Q&amp;oe=6ADE3D47</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>855344712613820</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Sausage Dog Central</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SausageDogCentral</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dog, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/360084077_855344712613820_7250726187422931738_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1843x1843&amp;_nc_cat=1&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=EeI4jy4NI6gQ7kNvwHNXgJh&amp;_nc_oc=AdpYXAV-Q_oPfYJlJdBpYbAYLcOjhJypZZdQXPDMKnE3XUqsK8Gr4KuNdMPajEkKrLI&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=ak9sxYgbexO8hxOyCbHoeQ&amp;_nc_ss=7b2a8&amp;oh=00_AQNA75k3wb8Wp2XBtYPTl7XL18k0_dhj93RTFjv5rqZIPg&amp;oe=6ADE416F</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>4486464461616223</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Montpelier Cavaliers</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sarah.vasyukhnevich</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: cavalier, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>cavalier</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/717402555_4486464461616223_2174404301963023400_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1024x1024&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=t_4vuELx2NgQ7kNvwEsfR7S&amp;_nc_oc=AdoJS_nk0XF_8i8yMCxgNnHJFVKgKbHab_dzSD08etDlPt5Okrznfqq9QVaxxpJxNHY&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=ak9sxYgbexO8hxOyCbHoeQ&amp;_nc_ss=7b2a8&amp;oh=00_AQNVLcpIjOWLRxgCTIh3-VO_YwZYmcWZKEwHU5EL5rq7dw&amp;oe=6ADE55CF</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>25642511325416375</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Aurora Lopez Perez</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/aurora.p.lopez</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: shih tzu)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>shih tzu</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/623396454_25642511325416375_1384894326437316373_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=G9Z8RlS_0aUQ7kNvwGXFEQU&amp;_nc_oc=Ado2UrFjqY2E7cXSKqd6cutgVKUlenoSP-wHYT7DZleC0eT_7AfJ83Uu7ai1ku8vrwQ&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=ak9sxYgbexO8hxOyCbHoeQ&amp;_nc_ss=7b2a8&amp;oh=00_AQP8MhvOXcjrxB-f1wAOvmpBnhwk01jQzQQHvj7yeFZQcQ&amp;oe=6ADE54B6</t>
         </is>
       </c>
     </row>

--- a/data/verified_step1/step1_verified_dogs_latest.xlsx
+++ b/data/verified_step1/step1_verified_dogs_latest.xlsx
@@ -428,17 +428,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="41" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -495,40 +495,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1596373112283090</t>
+          <t>100046841782363</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Firestorm Goldens</t>
+          <t>Incognia Kennels</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/Firestormgoldenretrievers</t>
+          <t>https://www.facebook.com/incognia.kennels</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Logo/Biển hiệu trại chó &amp; Từ khóa xác thực: goldens, golden retriever (không có mặt người)</t>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: kennels)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>non_dog (P=0.88)</t>
+          <t>puppy (P=1.00)</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>goldens, golden retriever</t>
+          <t>kennels</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/760620948_1596373112283090_8124428097826053721_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx2048x2048&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=vQnoXfeIIAsQ7kNvwHIoe36&amp;_nc_oc=AdrRtHloFKO14oKmFm4hrxLJpVJ4J7kh_TzW0hNMYCZans0AfawhWRHo7Z3aypBJT94&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=wvBxwXYC6uM7D2fsdOPfcA&amp;_nc_ss=7b2a8&amp;oh=00_AQOkNojq6ZxWDllkdngCdZ4PW99tEfnO33OsWHCSOcAGlQ&amp;oe=6ADE3BAE</t>
+          <t>https://scontent.fsgn2-4.fna.fbcdn.net/v/t39.30808-1/457476800_1114079383496777_4543913186334673000_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1664x1664&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=x8kUliWV5KwQ7kNvwFk_lsj&amp;_nc_oc=AdqLJ773Er4wZDgc3Vn0h3EH2LY9bDLzPbYguYW3T2ACLaoxQl2MES-RfexhGtw2dbc&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-4.fna&amp;_nc_gid=l5l8B0HigM71rwwa5NQEgQ&amp;_nc_ss=7b2a8&amp;oh=00_AQMXkG0su1HP2QhdJFLtjBpsj-CMfwXU_V_XV5zOo5K7lw&amp;oe=6ADECE05</t>
         </is>
       </c>
     </row>
@@ -538,22 +538,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1058086863465242</t>
+          <t>100047929492341</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Smooches for Pooches</t>
+          <t>Cooper T. Golden</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/loveofpups</t>
+          <t>https://www.facebook.com/mishell.krewson</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: puppy, dog, puppies)</t>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: goldens, P_dog=1.00)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -566,12 +566,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>puppy, dog, puppies</t>
+          <t>goldens</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/773486111_1058086863465242_344051957738859922_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1086x1086&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=Q7quceSoaj4Q7kNvwF9pNK7&amp;_nc_oc=Adowdu5feQlQuIM8cMskP7WX5FjSWMgEsv_sozqn4lbdoomeyZZ9i1cgkZALzQ_EcJw&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=wvBxwXYC6uM7D2fsdOPfcA&amp;_nc_ss=7b2a8&amp;oh=00_AQPT5aTSyALYre6DBDFzRfYcLpomB41eaR0Yd_XXP1HpHg&amp;oe=6ADE5BEE</t>
+          <t>https://scontent.fsgn2-10.fna.fbcdn.net/v/t39.30808-1/670296950_1472448341029468_1320452279664119562_n.jpg?stp=c0.152.1745.1745a_cp6_dst-jpg_tt6&amp;cstp=mx1745x1745&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=J4XosXgGeiMQ7kNvwHMXBQv&amp;_nc_oc=AdrKiy1SyoaHvjrc_Fbt7gNMfMVhlTfihnAw11KRzoKNG4feYPVUyMFYp-be_pbdj4M&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-10.fna&amp;_nc_gid=MOAgdzRn0vJfTQZaA3Ox3g&amp;_nc_ss=7b2a8&amp;oh=00_AQPnBObe-GaMdP79D3gXu5mY1TlgSfiazuJiiCqVVv5SBQ&amp;oe=6ADEDB68</t>
         </is>
       </c>
     </row>
@@ -581,40 +581,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>122095855856933094</t>
+          <t>100083348137546</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bailey’s Cajun Canines LLC</t>
+          <t>Knockhill Beagles</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/Baileyscajuncaninesllc</t>
+          <t>https://www.facebook.com/Knockhillbeagles</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: canines, P_dog=0.97)</t>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: beagles, P_dog=1.00)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>puppy (P=0.97)</t>
+          <t>adult_dog (P=1.00)</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.972</v>
+        <v>1</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>canines</t>
+          <t>beagles</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/514361430_122095855856933094_4776262354102086972_n.jpg?stp=c28.0.1160.1160a_cp0_dst-jpg_tt6&amp;cstp=mx1160x1160&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=m0gI9fOCmkoQ7kNvwGO-eGL&amp;_nc_oc=AdqJQi32T0aUKVaL0X8svdciqgtz6-VRtlNQtRrFAGJkrxaU99PDIDKzTD8ht5sJWus&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=pelMvMZbxRbN5uMQAHbS1Q&amp;_nc_ss=7b2a8&amp;oh=00_AQPUrI0rX38UHxgde2mbt26ygN76wHf49g8rVFWk6NIEZw&amp;oe=6ADE463A</t>
+          <t>https://scontent.fsgn2-4.fna.fbcdn.net/v/t39.30808-1/278713108_109844201701543_3317168684718794551_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx959x958&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=pLyguPP1M_QQ7kNvwHLnISo&amp;_nc_oc=Adq7gu6Uu-fhg5Y3f5Uukf39j2pKobHz7VU57gthRck9yJsQfrkIW5mjqCWavba1bKE&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-4.fna&amp;_nc_gid=MOAgdzRn0vJfTQZaA3Ox3g&amp;_nc_ss=7b2a8&amp;oh=00_AQM-aUTE9LW0vFZk1KjhynsTTIrnfNiL_FR0Ep8t2v8Wsw&amp;oe=6ADEE7E3</t>
         </is>
       </c>
     </row>
@@ -624,40 +624,40 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1117686188781662</t>
+          <t>100063452086433</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Doodles of Louisiana</t>
+          <t>UP XL Bullies</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/DoodlesOfLouisiana</t>
+          <t>https://www.facebook.com/UPXLBullies</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: doodles)</t>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: bullies, P_dog=1.00)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>non_dog (P=0.85)</t>
+          <t>puppy (P=1.00)</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>doodles</t>
+          <t>bullies</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/280485787_1117686188781662_1773497406171536734_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx958x958&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=LvizzZ2jb68Q7kNvwG_-9za&amp;_nc_oc=AdrZ-6_n-rmjW0KFAoW248Qa7-Eczl9XNgE3CdB6Cq7AoXc4Fs6vhLSe-W2mKmgREGY&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=pelMvMZbxRbN5uMQAHbS1Q&amp;_nc_ss=7b2a8&amp;oh=00_AQM9fvnyUQYVOsjpJy_ToFyAqhYK3KsK0rzWs8DVS57_BQ&amp;oe=6ADE69C2</t>
+          <t>https://scontent.fsgn2-8.fna.fbcdn.net/v/t39.30808-1/594072587_1400594372065619_1582679061033912634_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx992x1002&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=lkDxZGbzRd8Q7kNvwGAzTpd&amp;_nc_oc=AdoryxlTBA-_28GVIpQcgl4d1FYecNNmuRurxBWbfnOSYNSsSDoTKU-LS4ccw3mBOe0&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-8.fna&amp;_nc_gid=MOAgdzRn0vJfTQZaA3Ox3g&amp;_nc_ss=7b2a8&amp;oh=00_AQPEhuF_jbm0meaXEAfOgPMEmFZzbKUgxSRbaQB5J5J7Xw&amp;oe=6ADEC212</t>
         </is>
       </c>
     </row>
@@ -667,40 +667,40 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>122348323874064888</t>
+          <t>100084581902078</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16 Paws Goldens</t>
+          <t>Kayla Parrish</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/16PawsGoldens</t>
+          <t>https://www.facebook.com/kayla.d.parrish</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: goldens, golden retriever, P_dog=1.00)</t>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: puppies, golden retrievers, retrievers)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>adult_dog (P=1.00)</t>
+          <t>puppy (P=0.95)</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>goldens, golden retriever</t>
+          <t>puppies, golden retrievers, retrievers, puppy, dog, goldens</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/853441685_122348323874064888_3226424898471433872_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx2048x2048&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=12YKDZ0y3MoQ7kNvwE4F8SH&amp;_nc_oc=AdrfUphicb9s0yPRDTKRQnAvg71twQHzKlsle2Vw5awfEH_wJTAAcLXSKsN9Sw-esN0&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=pelMvMZbxRbN5uMQAHbS1Q&amp;_nc_ss=7b2a8&amp;oh=00_AQPwNvT5R7xJXZlNuaZ4yyZlfF4OD0i7s4Y4_3A1PRpPOQ&amp;oe=6ADE3E17</t>
+          <t>https://scontent.fsgn2-10.fna.fbcdn.net/v/t39.30808-1/803102991_10105027621763008_1734711563951480152_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=BF252bHtGZwQ7kNvwGNcaXe&amp;_nc_oc=Adq9QH-4kk-YtFBqbg0xVd5Ia_IzNcCn153pjLol3qlZpuTdqrgPsVdNWMqc4eoM0Q8&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-10.fna&amp;_nc_gid=yU2HfyObD9CQSe5JJy8cQQ&amp;_nc_ss=7b2a8&amp;oh=00_AQMTMOtPEWodhcG31pm12WP_Nayuu2Bb1INlFO98vE7ICg&amp;oe=6ADEBF2B</t>
         </is>
       </c>
     </row>
@@ -710,40 +710,40 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>167575609124204</t>
+          <t>100076486742395</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brandi’s Southern Doodles &amp; Poodles, LLC</t>
+          <t>Golden Locks Of Love</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/BrandisSouthernDoodlesandPoodles</t>
+          <t>https://www.facebook.com/goldenlocksoflove</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: poodles, doodles)</t>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: goldens, P_dog=1.00)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>non_dog (P=0.85)</t>
+          <t>adult_dog (P=1.00)</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>poodles, doodles</t>
+          <t>goldens</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/290874043_167575609124204_8051960330153032304_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=YQZymWJ3-y4Q7kNvwHVe2fB&amp;_nc_oc=Adrqjmp_DmhWnTiBimR93_qm4amEiy2QcxlW4LVFWkB4fnSxouhi4zAZCyA3UsGb2NM&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=pelMvMZbxRbN5uMQAHbS1Q&amp;_nc_ss=7b2a8&amp;oh=00_AQO4M9H1q9mWC48B-W7v-25Td6UV0PlCaHWQh7MMjNl9Lg&amp;oe=6ADE4DE9</t>
+          <t>https://scontent.fsgn2-6.fna.fbcdn.net/v/t39.30808-1/773614800_1066329142593301_5805448399331982091_n.jpg?stp=c0.0.720.720a_cp6_dst-jpg_tt6&amp;cstp=mx720x720&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=Kbw3kR3bm9AQ7kNvwFfZq61&amp;_nc_oc=Ado8DtTEddEjAfwA3nUF2imeI0ONyGMnMKyKmGPE8GMR7848OYfMsxDztfMAqa4y8Z0&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-6.fna&amp;_nc_gid=yU2HfyObD9CQSe5JJy8cQQ&amp;_nc_ss=7b2a8&amp;oh=00_AQOg-H_4KrKuo64O30L8WX-zo16KEIEzuZnbO67CavFv3Q&amp;oe=6ADECB7E</t>
         </is>
       </c>
     </row>
@@ -753,40 +753,40 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>224535483884124</t>
+          <t>100057267985772</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Galaxy Golden Retrievers</t>
+          <t>Five Star Puppies</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/galaxygoldenretrievers</t>
+          <t>https://www.facebook.com/fivestarfarms55</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: golden retrievers, retrievers)</t>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: puppies, puppy, dog)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>non_dog (P=0.85)</t>
+          <t>adult_dog (P=1.00)</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>golden retrievers, retrievers, goldens</t>
+          <t>puppies, puppy, dog</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/368381343_224535483884124_7262168979554044494_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx956x960&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=Fozk3m8ofZUQ7kNvwHk3Dev&amp;_nc_oc=AdoY_TUW80Ixf2IsE5KV1w5oPOPzi_ptw2OQjkTde9VcAhkPP-WYZF--YAjl8MBH2kY&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=W3-63CRhSeTi0X6tRyjinQ&amp;_nc_ss=7b2a8&amp;oh=00_AQMz1t90gf2bxZRAOPmzS40sKuqK23udRILxoIZ99ekuEA&amp;oe=6ADE565A</t>
+          <t>https://scontent.fsgn2-8.fna.fbcdn.net/v/t39.30808-1/601870246_1396074742311445_420822899921986769_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=O5qcrUHOfZMQ7kNvwEq1ozJ&amp;_nc_oc=AdofrN1Z9-iYOlEPD6rPbWqSsEUkGT7PQnRQrBYBcPBq8a1FRzAFGNFqSnRHdmOcqWw&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-8.fna&amp;_nc_gid=yU2HfyObD9CQSe5JJy8cQQ&amp;_nc_ss=7b2a8&amp;oh=00_AQNafh5n6ZTDzFVeb9H8JrnFlp8xnk6BT7gCQKX4Jw54KQ&amp;oe=6ADEE15F</t>
         </is>
       </c>
     </row>
@@ -796,40 +796,40 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>727311656940554</t>
+          <t>1647967647</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Golden Puppies</t>
+          <t>Racquel Perry</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/goldenpuppies2004</t>
+          <t>https://www.facebook.com/racquel.perry.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: puppies, puppy, dog)</t>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: kennel, kennels, rottweiler)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>adult_dog (P=1.00)</t>
+          <t>non_dog (P=0.95)</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>puppies, puppy, dog, goldens</t>
+          <t>kennel, kennels, rottweiler</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/530235894_727311656940554_8801302940165924973_n.jpg?stp=c507.540.1422.1423a_cp0_dst-jpg_tt6&amp;cstp=mx1422x1423&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=Hoq6NuCogV8Q7kNvwEB7GfP&amp;_nc_oc=AdpXKgkhgvSL0qJc_-82d8oRZNf-J9oCE9OiklOMFQxEb4pDVAiVaMHpK6DlJcTS0zU&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=W3-63CRhSeTi0X6tRyjinQ&amp;_nc_ss=7b2a8&amp;oh=00_AQMVJL9PwWeX-QIYDMIBsq4DIFAw8HukSKTfDaAwYbrD_A&amp;oe=6ADE3D7D</t>
+          <t>https://scontent.fsgn2-8.fna.fbcdn.net/v/t39.30808-1/461577689_10229307949757085_5298380598645898547_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx956x960&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=2s3cv7np3roQ7kNvwG1Js9S&amp;_nc_oc=AdqvZkCNfzucgUI3IXOabxthUD0WLusDuMbFVqDiwLhX3xRC8SkgJe05Kzccpu7km94&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-8.fna&amp;_nc_gid=o2oDYmzF6KubLNa1zYKTJA&amp;_nc_ss=7b2a8&amp;oh=00_AQMb1OH0-PKCnp-i3HZXkrLtkSIJ4bsIzOW--x1x_GEf_g&amp;oe=6ADEBC6B</t>
         </is>
       </c>
     </row>
@@ -839,40 +839,40 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1713907270555802</t>
+          <t>100088986828560</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Beauty and the Beast Shih Tzu</t>
+          <t>Christeena Strunk</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/BeautysShihTzu</t>
+          <t>https://www.facebook.com/christeena.strunk</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: shih tzu, P_dog=1.00)</t>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: breeder, dachshund, miniature dachshund)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>adult_dog (P=1.00)</t>
+          <t>adult_dog (P=0.98)</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0.9828</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>shih tzu</t>
+          <t>breeder, dachshund, miniature dachshund</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/854337368_1713907270555802_3166642091340115423_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=WCfvxI38zx8Q7kNvwEjrNu9&amp;_nc_oc=Adob3XQ7o0vsKe8Rgt9BxFxPabxD6XcuUfYHgIvADOzYI7RB2-3hq8lgzeK92i34aLk&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=W3-63CRhSeTi0X6tRyjinQ&amp;_nc_ss=7b2a8&amp;oh=00_AQPuUc2qyLkwN3kVJj2jjdzhdI_z8WbladuDG1hEbwWhcQ&amp;oe=6ADE3F59</t>
+          <t>https://scontent.fsgn2-11.fna.fbcdn.net/v/t39.30808-1/583879940_848902158086004_5859238268894171475_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx2048x2048&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=RUX1HljSnGoQ7kNvwEyNVlw&amp;_nc_oc=AdpbODVYQv3A-Dj5LIuTajmbYYeY6SFHdmJPApAe2ESpuHUAbg0L2h22sVo8QJpad8g&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-11.fna&amp;_nc_gid=bKQGE8v0IHTMPF8yPxKlCg&amp;_nc_ss=7b2a8&amp;oh=00_AQM9XZw7tHJ9l38CcL-UpfByLmuZizWEGI05CUlUzRcpIg&amp;oe=6ADEDB17</t>
         </is>
       </c>
     </row>
@@ -882,22 +882,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>122193969698840038</t>
+          <t>100054535087351</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Shih Tzu Love'r</t>
+          <t>Kennel Visendum</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/shihtzulovers02</t>
+          <t>https://www.facebook.com/kennelvisendum</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: shih tzu, P_dog=1.00)</t>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: kennel)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -910,12 +910,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>shih tzu</t>
+          <t>kennel</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/751883689_122193969698840038_5392462303461976167_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1254x1254&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=6neccbWYohAQ7kNvwE-4Qlt&amp;_nc_oc=AdpFYRDPh9z0v8qmF9i8I8G5BGFYcr52nPHR8mg1--IoueFm2rurFK3muXwEoS5i8Ng&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=W3-63CRhSeTi0X6tRyjinQ&amp;_nc_ss=7b2a8&amp;oh=00_AQMjw30eryhv4uI7o57_txEXm663N77XwQ5uan6uE4rzdw&amp;oe=6ADE3DD7</t>
+          <t>https://scontent.fsgn2-8.fna.fbcdn.net/v/t39.30808-1/305021341_602616581566173_4136007037063285625_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx2048x2048&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=Tlswujp_qJYQ7kNvwFncd20&amp;_nc_oc=Adp91Ixbsm8L1t1KPlPEb0bHNdq1nEBtXk-4JevtLvMMPwN8ByCZa3VydM6HxOaO8hA&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-8.fna&amp;_nc_gid=Dai7BmdD22586KlfinusUA&amp;_nc_ss=7b2a8&amp;oh=00_AQO7Fx_hbMNbFq-mG8x2xRnHBaXAt__2alX6AiZCwfJ9Hg&amp;oe=6ADEDF05</t>
         </is>
       </c>
     </row>
@@ -925,40 +925,40 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>134105013011006</t>
+          <t>100064529596837</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lil’ Bit’s Shih Tzu PUPS of NC</t>
+          <t>Camp Cocker Rescue</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/lilbitspups</t>
+          <t>https://www.facebook.com/CampCockerRescue</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: pups, shih tzu, puppy)</t>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: cocker)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>adult_dog (P=1.00)</t>
+          <t>non_dog (P=0.85)</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>pups, shih tzu, puppy, dog, puppies</t>
+          <t>cocker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/349320352_134105013011006_4377198773058659903_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1170x1170&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=dWgF00YllvgQ7kNvwFoblVY&amp;_nc_oc=AdpcjWk8V-ykX3wgyPm0TKbA-DOC6ueNtT7fBoymBY0v1cD56Oc5vKGCFhYxxsgQkeo&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=W3-63CRhSeTi0X6tRyjinQ&amp;_nc_ss=7b2a8&amp;oh=00_AQNoIW2nGko2V6-xIK8cQ1KYCC5mlJGs3kvJHcor3w8_KQ&amp;oe=6ADE4B68</t>
+          <t>https://scontent.fsgn2-6.fna.fbcdn.net/v/t39.30808-1/504276047_1130611149099861_4708652550929422967_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1080x1080&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=qg7NC_qEfgkQ7kNvwEhdYiY&amp;_nc_oc=AdoghjfJ1gef6r8yh5kN0Zmd5G6C73F5cWyAdRO_2XOiIdbpq7mYzzGyB496IJK1YIY&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-6.fna&amp;_nc_gid=kIqgoVAT4YBIloexM36DxA&amp;_nc_ss=7b2a8&amp;oh=00_AQOFwTuyrcIs0iQPgfXyM3KfEXLajJpSqImcw9a2tGrkYA&amp;oe=6ADEC01F</t>
         </is>
       </c>
     </row>
@@ -968,40 +968,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>103750072031616</t>
+          <t>100083535090833</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Willow Oak Farm White Labs</t>
+          <t>Glasses the Bully</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/willowoakfarmwhitelabs</t>
+          <t>https://www.facebook.com/GlassestheBully</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: labs)</t>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: bully, P_dog=1.00)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>non_dog (P=0.85)</t>
+          <t>adult_dog (P=1.00)</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>labs</t>
+          <t>bully</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/239326327_103750072031616_8246519884499016640_n.png?stp=c226.0.1036.1036a_cp0_dst-png&amp;cstp=mx1036x1036&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=VoCMcdQms2kQ7kNvwHGcnao&amp;_nc_oc=Adolgiyk1m5c6zXpxZMofnxHL--Gs1-I-UW6ScqXoisJ0xL8nPGLYLJdAvZFomXgTFM&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=x_eCW6M3_boLIlu9Xz2UVw&amp;_nc_ss=7b2a8&amp;oh=00_AQPnsGKYXLsOnCGlBqyLiHfmVnP-v7OBQ_Wz0737M7M1ug&amp;oe=6ADE538E</t>
+          <t>https://scontent.fsgn2-3.fna.fbcdn.net/v/t39.30808-1/470242308_562092886585210_1599376514916313682_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1179x1179&amp;_nc_cat=1&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=zXAT8xSe8PAQ7kNvwHlm31m&amp;_nc_oc=AdpjJHfj9hSdiJTq3xrK3QQY1uwOe3nYCwx_Y0pqzE5M3rThSuCKN5ybfTaOpP9R6Y0&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-3.fna&amp;_nc_gid=3MVk_eUCz6l8Fj8pkI4GxA&amp;_nc_ss=7b2a8&amp;oh=00_AQMcrmfLVwcoOr5qMhEAUEps9HEmfjpBhHwMDC4tEBtO-w&amp;oe=6ADEE372</t>
         </is>
       </c>
     </row>
@@ -1011,40 +1011,40 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1930354481705111</t>
+          <t>61583670986481</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Prairie Creek Kennel</t>
+          <t>English Cocker Spaniel Parents</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/PrairieCreekKennel</t>
+          <t>https://www.facebook.com/englishcockerspanielparents</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: kennel)</t>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: cocker spaniel, cocker, P_dog=0.98)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>puppy (P=1.00)</t>
+          <t>puppy (P=0.98)</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0.9809</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>kennel</t>
+          <t>cocker spaniel, cocker, english cocker, spaniel</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/787924714_1930354481705111_8023386184839815697_n.jpg?stp=c0.0.1118.1118a_cp0_dst-jpg_tt6&amp;cstp=mx1118x1118&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=QUF7osBv29sQ7kNvwEs5iLa&amp;_nc_oc=AdqzG72wd25ONZrGn15WhiecIpy6h64OKmGOdQAQGnirgeFQKii7WnI_hZJHUtU9xtU&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=x_eCW6M3_boLIlu9Xz2UVw&amp;_nc_ss=7b2a8&amp;oh=00_AQN0rHZ7YxrseRLDb_rYSmbJf4O0iMqScL10q5MBAWNd0g&amp;oe=6ADE686E</t>
+          <t>https://scontent.fsgn2-8.fna.fbcdn.net/v/t39.30808-1/647300412_122094929217122366_7223711425630644973_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1024x1024&amp;_nc_cat=102&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=SYarsOZDm34Q7kNvwFp8Oed&amp;_nc_oc=AdoSX1LwzAUl_5KfMb14wB3SCgF0S9xt1XPjJBt7PeJGpaI_37_GYV_I8b3FQllY990&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-8.fna&amp;_nc_gid=fbZvpjrFlH0I5LU12I6_Iw&amp;_nc_ss=7b2a8&amp;oh=00_AQO9sZwNXD1f5llLHP5-gyWWTd3xK8DDTbKjtZH1MA7KyQ&amp;oe=6ADECD49</t>
         </is>
       </c>
     </row>
@@ -1054,40 +1054,40 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>434190195177077</t>
+          <t>100075988733897</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Creme of the Crop Dachshunds</t>
+          <t>Puppies Kingdom Team</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/englishcreammniaturedachshunds</t>
+          <t>https://www.facebook.com/mase7y.crushes</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dachshunds, P_dog=1.00)</t>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: puppies, puppy, dog)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>adult_dog (P=1.00)</t>
+          <t>non_dog (P=0.95)</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>dachshunds</t>
+          <t>puppies, puppy, dog</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/277559970_434190195177077_5291667728461596283_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1242x1242&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=Af-UHt10BhYQ7kNvwFKMFhu&amp;_nc_oc=Adq4GLGLEcT48PJP2FGuJITIIl12xW0MqVFnpLVN8ykxJJA2HyfIdvsvGCC6h1FU1bc&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=nWISXh2b8NBnOu23IzNfEw&amp;_nc_ss=7b2a8&amp;oh=00_AQM5eU7ropmhOAZJKXeubfTKexBF8l2_bxbDjXlsMd7GCw&amp;oe=6ADE5970</t>
+          <t>https://scontent.fsgn2-4.fna.fbcdn.net/v/t39.30808-1/677891571_980168644526084_4671543112762367641_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1024x1024&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=gsa-ejJPjJEQ7kNvwFHCOtP&amp;_nc_oc=AdqaENlyLd14PltuVScUwbdcbO-FNCoKrUAnvsDixqe-Wn-ciOxssi6och7ebT6wzFc&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-4.fna&amp;_nc_gid=aHr1UtJkMp08GoMbOytDEQ&amp;_nc_ss=7b2a8&amp;oh=00_AQMyP5J82UleZZ7vNWzGl7zLI07EdkRHpSCJP1hxPDysdg&amp;oe=6ADEE3A1</t>
         </is>
       </c>
     </row>
@@ -1097,27 +1097,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>122094153387516831</t>
+          <t>61592793269294</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Salvați cățeii de la Popești-Iași</t>
+          <t>Misadventures with Meeko</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/SalvatiCateiiDeLaPopesti</t>
+          <t>https://www.facebook.com/MeekoGriffyn</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Thị giác nhận diện cún con sắc nét (Puppy=0.93, P_dog=1.00)</t>
+          <t>AI Thị giác nhận diện chó trưởng thành (Adult=0.98, P_dog=1.00)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>puppy (P=1.00)</t>
+          <t>adult_dog (P=1.00)</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1126,7 +1126,7 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/847550055_122094153387516831_8056891142274074859_n.jpg?stp=c0.70.1500.1500a_cp0_dst-jpg_tt6&amp;cstp=mx1500x1500&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=nmoR64VsmXUQ7kNvwEu-_DI&amp;_nc_oc=AdomVof3gO20cj8WM2qq8xPDzwL6bA_d9roWWyw4iv-1kmsLcGgfYkQpEnN8p3eD9XU&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=nWISXh2b8NBnOu23IzNfEw&amp;_nc_ss=7b2a8&amp;oh=00_AQPm9thyDGnE8BmYq268iL2SrHXYV6zqXBKFWTM_JFnHew&amp;oe=6ADE44D3</t>
+          <t>https://scontent.fsgn2-9.fna.fbcdn.net/v/t39.30808-1/763098261_10116103334655285_2150546350087965337_n.jpg?stp=c0.0.1299.1299a_cp0_dst-jpg_tt6&amp;cstp=mx1299x1299&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=hGaLDCcy8oEQ7kNvwFraclE&amp;_nc_oc=Adri4aw02Z1or38AnH-9Y8Z_ZawO2xJmhxx9U62xktonQ7h07orfIhVTzUUkmgAZFXo&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-9.fna&amp;_nc_gid=aHr1UtJkMp08GoMbOytDEQ&amp;_nc_ss=7b2a8&amp;oh=00_AQMvIg4t3BPZWASBlYnQwPb6Hcjql1H3-IVJka7WVHRDGg&amp;oe=6ADED0DA</t>
         </is>
       </c>
     </row>
@@ -1136,22 +1136,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1138905091673145</t>
+          <t>100063540822399</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hyde Park Cavaliers</t>
+          <t>Dai Rona sa America</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hyde.park.cavaliers.2025</t>
+          <t>https://www.facebook.com/randompicturesandvideosofmydailylife</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: cavalier, P_dog=1.00)</t>
+          <t>AI Thị giác nhận diện chó trưởng thành (Adult=0.86, P_dog=1.00)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1162,14 +1162,10 @@
       <c r="G17" t="n">
         <v>1</v>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>cavalier</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/552894529_1138905091673145_212893724666853543_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=tb5968Uum_8Q7kNvwF09BmR&amp;_nc_oc=AdoFUfd1wwWodC1ZSndp48NB8ar3nHcoCGpKz5UNfbs0gWdyTk1cWhfg9G3Y9Oc3Zfg&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=nWISXh2b8NBnOu23IzNfEw&amp;_nc_ss=7b2a8&amp;oh=00_AQPdYZGVKj-ASBzvtzllRKTEsYbVY2rLz1IXMuYvrfXbEA&amp;oe=6ADE3C32</t>
+          <t>https://scontent.fsgn2-5.fna.fbcdn.net/v/t39.30808-1/656130031_1621209680007044_6361367028614392644_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx2048x2048&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=qFlC0BJJgBUQ7kNvwHGwMj7&amp;_nc_oc=AdqYdtJYihq1bZxV2GA55F1_S7EpjG5cS62Y_mMCanvNQeABKnq2pzi7xXTmRwuTeGM&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-5.fna&amp;_nc_gid=RJy0_6kbDY_Tfn5uj0C8TA&amp;_nc_ss=7b2a8&amp;oh=00_AQNcoBh4jcgljctoUsX47f6pnn0ccWk7iDqnEM_Rfy9dzg&amp;oe=6ADEB677</t>
         </is>
       </c>
     </row>
@@ -1179,40 +1175,40 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>122123912342347266</t>
+          <t>100057522816300</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MiniDox Pups</t>
+          <t>Jamboree Labradors</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/minidoxpups</t>
+          <t>https://www.facebook.com/jamboreelabradors</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: pups, puppy, dog)</t>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: labradors, P_dog=1.00)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>non_dog (P=0.95)</t>
+          <t>puppy (P=1.00)</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>pups, puppy, dog, puppies</t>
+          <t>labradors</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/453383289_122123912342347266_388495722924606013_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx641x640&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=7ES5_0tyRfwQ7kNvwE7D1XU&amp;_nc_oc=AdoJKwODYxrlaVzua3BMEIZXWnPoDGVcIzpl-s17BjcF6334NCCXeGLHf_hoeChYpcE&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=nWISXh2b8NBnOu23IzNfEw&amp;_nc_ss=7b2a8&amp;oh=00_AQM0t8pBAyJVLRiu7WdcIl_F9jMEktziUP3kgcN99WY55Q&amp;oe=6ADE3D47</t>
+          <t>https://scontent.fsgn2-5.fna.fbcdn.net/v/t39.30808-1/293243897_504779544782802_1233221803183950699_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx959x959&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=VhergRIZ6p8Q7kNvwG6ORAC&amp;_nc_oc=AdqdWrAooLJW_vL9r8I1Bi8XtTABTvujg4zo_yj0ueC_uU4mwaKEmzcVd_XSGA18MXA&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-5.fna&amp;_nc_gid=RJy0_6kbDY_Tfn5uj0C8TA&amp;_nc_ss=7b2a8&amp;oh=00_AQP1KdyBQQdgH_cYisiIlWnCv040VV0RM9MZue4Nvpjjhw&amp;oe=6ADECE8E</t>
         </is>
       </c>
     </row>
@@ -1222,40 +1218,40 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>855344712613820</t>
+          <t>100063523452059</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sausage Dog Central</t>
+          <t>Rippee Creek Beagles</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/SausageDogCentral</t>
+          <t>https://www.facebook.com/rippeecreekkennel</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dog, P_dog=1.00)</t>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: beagles)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>adult_dog (P=1.00)</t>
+          <t>non_dog (P=0.85)</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>beagles</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/360084077_855344712613820_7250726187422931738_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1843x1843&amp;_nc_cat=1&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=EeI4jy4NI6gQ7kNvwHNXgJh&amp;_nc_oc=AdpYXAV-Q_oPfYJlJdBpYbAYLcOjhJypZZdQXPDMKnE3XUqsK8Gr4KuNdMPajEkKrLI&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=ak9sxYgbexO8hxOyCbHoeQ&amp;_nc_ss=7b2a8&amp;oh=00_AQNA75k3wb8Wp2XBtYPTl7XL18k0_dhj93RTFjv5rqZIPg&amp;oe=6ADE416F</t>
+          <t>https://scontent.fsgn2-10.fna.fbcdn.net/v/t39.30808-1/300369278_2395184557301495_6789356413619473410_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx959x959&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=mwTC_uAaSxcQ7kNvwG7dZco&amp;_nc_oc=AdqNMdP0tQb2Hga-WJ6uS9awqt1Njt91w-8MW4b95O91fn56F5BjMzsf8P-6B5qUoFg&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-10.fna&amp;_nc_gid=RUynU32ECmHzwFr80fmp7A&amp;_nc_ss=7b2a8&amp;oh=00_AQPPsDJHVoWIFu0RaOo2SYUWiebB7jQvgK52yOR97A771A&amp;oe=6ADEBB72</t>
         </is>
       </c>
     </row>
@@ -1265,40 +1261,40 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4486464461616223</t>
+          <t>61572450787096</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Montpelier Cavaliers</t>
+          <t>Golden Paws Diary</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/sarah.vasyukhnevich</t>
+          <t>https://www.facebook.com/goldenpawsdiary</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: cavalier, P_dog=1.00)</t>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: goldens)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>adult_dog (P=1.00)</t>
+          <t>non_dog (P=0.85)</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>cavalier</t>
+          <t>goldens</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/717402555_4486464461616223_2174404301963023400_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1024x1024&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=t_4vuELx2NgQ7kNvwEsfR7S&amp;_nc_oc=AdoJS_nk0XF_8i8yMCxgNnHJFVKgKbHab_dzSD08etDlPt5Okrznfqq9QVaxxpJxNHY&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=ak9sxYgbexO8hxOyCbHoeQ&amp;_nc_ss=7b2a8&amp;oh=00_AQNVLcpIjOWLRxgCTIh3-VO_YwZYmcWZKEwHU5EL5rq7dw&amp;oe=6ADE55CF</t>
+          <t>https://scontent.fsgn2-4.fna.fbcdn.net/v/t39.30808-1/750565607_122187448034748359_5232057570316147654_n.png?stp=c496.2.617.617a_cp0_dst-png&amp;cstp=mx617x617&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=M43lQHdb0-YQ7kNvwEqPwQm&amp;_nc_oc=AdqitkzVWz3GpyVk-1I1jazALLcR_8i5eETx7OFePIT6tAHUD5g3lVNvcIi2PVqDxx0&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-4.fna&amp;_nc_gid=xLtHPTHpB9XdJQMcHKPUtA&amp;_nc_ss=7b2a8&amp;oh=00_AQPrYa2xN9dfUAv2y77arE8fVpWmcDfd-_uBw0X7sWAgjA&amp;oe=6ADEC840</t>
         </is>
       </c>
     </row>
@@ -1308,40 +1304,6606 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>25642511325416375</t>
+          <t>100083302182985</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>Balakajan’s world</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Balakajansworld</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AI Thị giác nhận diện chó trưởng thành (Adult=0.99, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-7.fna.fbcdn.net/v/t39.30808-1/631160401_902187269234671_742125712373324129_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1290x1290&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=VSGDGjsMNRcQ7kNvwEv3Ljt&amp;_nc_oc=Adq4Q7fP4TywZqpMYcFAQwztdOIha3gF3FgRpc3D66WdbldeSz1lfGxml-USsEgpBDM&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-7.fna&amp;_nc_gid=AHDmN2RkTXAlLe7_7DJ4pA&amp;_nc_ss=7b2a8&amp;oh=00_AQMKIEKTPqk65tkDpQgJmhPDTF4-LbMtsDHTe4iY3A0VAw&amp;oe=6ADEE009</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>61592240453345</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Hot dog with love</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Hotdogwithlove</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dog, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-9.fna.fbcdn.net/v/t39.30808-1/750055127_2006901540019351_6354855122166517476_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1206x1206&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=dqf516NGtt4Q7kNvwFpGCnH&amp;_nc_oc=Adrq93Ua_rtqtWTpyIf7GExbEA6KzxAxPTxpAf41rANvd4gnaDtr48luhVLjS8USZfs&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-9.fna&amp;_nc_gid=ZH_9XXSt8kIb3cWz0DG16A&amp;_nc_ss=7b2a8&amp;oh=00_AQNQs748UHAekA_7Km4WltLI4ANUYKkQ__dXQ7vvnqpgUA&amp;oe=6ADEC559</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>61575822129538</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Remi The Dane Dog</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/remithedanedog</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dog, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-6.fna.fbcdn.net/v/t39.30808-1/740276614_122183737010860737_7196120938254272341_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1254x1254&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=YT5W-EkDN1gQ7kNvwG-YIV2&amp;_nc_oc=AdoUhwqeXIWxuxLqVf6Aa8CDDtOBcDIUwpISp9P_o6qgl5GAxEBmkvWbm07y-jdSEVA&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-6.fna&amp;_nc_gid=ZH_9XXSt8kIb3cWz0DG16A&amp;_nc_ss=7b2a8&amp;oh=00_AQN9X7zdidwHLKepn5dYdNKd4DTyv8fHiNy8vB_uZQir1Q&amp;oe=6ADECA70</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>100084933936077</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Linda Auten</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/linda.auten.827653</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AI Thị giác nhận diện chó trưởng thành (Adult=0.96, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-3.fna.fbcdn.net/v/t39.30808-1/853291913_2982266705459223_4501883956885146006_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx2042x2048&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=BUomUt72-MAQ7kNvwG3v7LA&amp;_nc_oc=AdoJazMYdk19DuMDakyg6w_4w8GLTAlsIPQB5opom9LnLfQKdGHEEXXk1Zxz8vdJwg8&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-3.fna&amp;_nc_gid=xUg_Osbl0V18acGUBEfsBg&amp;_nc_ss=7b2a8&amp;oh=00_AQPx0uQPkJcwq4hgEsSo9Qq88g9xr8l-zAd1mNzHVNC1Rg&amp;oe=6ADECE68</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>100083097738239</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Doxie Life</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/doxie.life.love</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: doxie, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>doxie</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-4.fna.fbcdn.net/v/t39.30808-1/843434392_1110261578015700_696012121046723_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1600x1600&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=9lEI6CK4Ts0Q7kNvwEnIu0v&amp;_nc_oc=AdptoM0Jm-3Gr9jgswH275JR-UICRJOdhL8sNGW77FfHtrLTlqJR7BpJrdK06X5Wgn0&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-4.fna&amp;_nc_gid=xUg_Osbl0V18acGUBEfsBg&amp;_nc_ss=7b2a8&amp;oh=00_AQMeI0NaYjIBjWCaVQlVanGVHOcLLnVZzufC550hicB_0w&amp;oe=6ADEEC8F</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>61587164283010</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Adventures with Faith the Dog</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/FaithTheDogOfficial</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dog, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-7.fna.fbcdn.net/v/t39.30808-1/761149225_122131667829238809_5419710374288643460_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1151x1155&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=Wn7qSP-0ZSQQ7kNvwFJ6x7K&amp;_nc_oc=AdorMLiAnOUDM_XocQzf2fMeiM6949Sldu9OOzHPy2JVM4WT-cRiMGkd3GYvQgDYkqA&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-7.fna&amp;_nc_gid=AcdaWE62x7h5dt5oJoling&amp;_nc_ss=7b2a8&amp;oh=00_AQOps9BC75ovv_3-32WienvKAEhtER7FM06iJiHmyyRMYQ&amp;oe=6ADED43B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>100066643843502</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Greyson The Great Dane</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/greysonthegreatdane</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: great dane, P_dog=0.95)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>puppy (P=0.95)</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0.9478</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>great dane</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-3.fna.fbcdn.net/v/t39.30808-1/614140046_1209614754603308_3423178222890965609_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx564x564&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=ZkIyVWTLUZUQ7kNvwFz5yzB&amp;_nc_oc=AdqkIiCU_n92gH-JIpi6Xep_Dh0d_oNVFS0GdsDmlPLKlb_RaoCDOwAGyyCgThC6r9o&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-3.fna&amp;_nc_gid=AcdaWE62x7h5dt5oJoling&amp;_nc_ss=7b2a8&amp;oh=00_AQNGL2oFU-ZbiXkB6S-uKaeWm6w6xulN2DAOI68LXb787g&amp;oe=6ADEDA55</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>100057021297321</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Wildcat Hollow Retrievers</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/wildcathollowretrievers</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: retrievers)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>retrievers</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-10.fna.fbcdn.net/v/t39.30808-1/310271064_593765562534148_5316021582114503496_n.png?stp=cp0_dst-png&amp;cstp=mx2048x2048&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=UPk_MnpEX4cQ7kNvwHi99I9&amp;_nc_oc=AdpTCn4lcScE9q4cM0ucVROYIN_kQ8FONPnLtpLcRkZeFGfwGaZokYH2xQ_M34aZxHQ&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-10.fna&amp;_nc_gid=6fYtdR7IrngXBtowY_FmyA&amp;_nc_ss=7b2a8&amp;oh=00_AQOyRJEQRdQPdCsikwXN33nSlhGG535yYDXK3G5a2sVKlQ&amp;oe=6ADEBBB9</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>100027125872519</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Fargher Lake Labradors</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/FargherLakeLabrador</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: labradors, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>labradors</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-11.fna.fbcdn.net/v/t39.30808-1/443845422_1318648299049353_2181122309320309926_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=102&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=fLDrnVBkeZEQ7kNvwG4kzpS&amp;_nc_oc=Adocqk6UpH9NRCIFR95Gv1ESqTjmEby9E_al6PU1UdAnE6WEpzAsVQL_H18SOHcnZGk&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-11.fna&amp;_nc_gid=giuE-XiQKjGYVnBHiPWJvQ&amp;_nc_ss=7b2a8&amp;oh=00_AQN2XcCREWRcnJ38U96l3ZQUSD3ECHESTjJkYHaBtWNCbQ&amp;oe=6ADEE21F</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>61592772548651</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>mini vlog for dog's</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Jhonpanon21</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dog, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-9.fna.fbcdn.net/v/t39.30808-1/838579466_122123758335425751_1807630825100443838_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1600x1597&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=MxW63I2YYEkQ7kNvwGh7FhI&amp;_nc_oc=AdpCPc75HKd8n7VsRZ9cCggFjoprRnw8SNJijTPHp5LlcEoUqJFEsz4jsVwZY9qXG9k&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-9.fna&amp;_nc_gid=giuE-XiQKjGYVnBHiPWJvQ&amp;_nc_ss=7b2a8&amp;oh=00_AQMspjiDtFyaC5Rqvwtqvs3G8XwIT7_R5oryiStKQ1a6HA&amp;oe=6ADEC2CF</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>61568918829494</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Beagle Lego</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/beaglelego</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: beagle)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>beagle</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-8.fna.fbcdn.net/v/t39.30808-1/504292937_122134208090630627_809399434218491624_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx2048x2048&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=IBWoZiFdaPEQ7kNvwFVmlcK&amp;_nc_oc=Adp2ADHPJeulUZZB2iea6JRv8XYfJqpl_n6i0sjxFoj-vWtVi70wjB-urBL0DJSH1u8&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-8.fna&amp;_nc_gid=giuE-XiQKjGYVnBHiPWJvQ&amp;_nc_ss=7b2a8&amp;oh=00_AQPcOAcbkpY-lLmiCwqp1crVxJ7hGwbgtbXCsrLQxvlexg&amp;oe=6ADEBA8A</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>100063614227260</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Derdledash Dachshunds</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Derdledash</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dachshunds, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>dachshunds</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-6.fna.fbcdn.net/v/t39.30808-1/462680682_1060540222743109_3375076946566874765_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx953x960&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=JpAQbsyjZCwQ7kNvwEz9_9s&amp;_nc_oc=Adpu3mNfczovdVMbXdipybqHtT6GyadsfmaxkgW6LJLjb42Vlpf6TKH9TeoUFdhRZv4&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-6.fna&amp;_nc_gid=ICzvW__C05wDpxYa1khcVQ&amp;_nc_ss=7b2a8&amp;oh=00_AQOHyah8NGwMrW1Ej63dJm8rdYN_lbNKFwlmcypzvXsQgQ&amp;oe=6ADEE897</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>61573157790857</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Christina Marie Mears</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/stina.marie.546527</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: goldens)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>goldens</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-4.fna.fbcdn.net/v/t39.30808-1/730917689_122193371504771926_9038867539946483850_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x961&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=MOSJYbdEn2sQ7kNvwE748gE&amp;_nc_oc=AdonM8ob9BOv6kGwiziZQXbvXSm_gS9G18gs-jRe3-de3hsrzkMZ5co5i_ANTNMMvWk&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-4.fna&amp;_nc_gid=_SFCkMxmG5sJWOGu8j97Lg&amp;_nc_ss=7b2a8&amp;oh=00_AQOuZKka_TLqlmCoILeUEYL4PMcEt2BaOTV3QJyTlE4w9A&amp;oe=6ADEE069</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>100069131045322</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Hodowla Gangsta</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/HodowcaPsowRasowych2010</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AI Thị giác nhận diện cún con sắc nét (Puppy=0.97, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-5.fna.fbcdn.net/v/t39.30808-1/600511882_1171148851866139_4353957825263347846_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1024x1024&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=vnZFrDg5c3YQ7kNvwFINpq3&amp;_nc_oc=AdqQYFpOlRhAJ4wdRvKA_x-IOEl-Z0-I_ST3gE5s1uvfQC3Un0XlDqK1EiEUtln9EJQ&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-5.fna&amp;_nc_gid=_SFCkMxmG5sJWOGu8j97Lg&amp;_nc_ss=7b2a8&amp;oh=00_AQPZNtLoMpf1iXWYPrwGh0wCeQZk-NLxeQOZstRiacykNw&amp;oe=6ADEE18D</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>61591735042055</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Vivi the Doxie</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vivithedoxie</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: doxie, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>doxie</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-4.fna.fbcdn.net/v/t39.30808-1/736683200_10245494520884442_5992394870288206094_n.jpg?stp=c0.0.1536.1536a_cp6_dst-jpg_tt6&amp;cstp=mx1536x1536&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=P-xZon2qDm8Q7kNvwF6zGin&amp;_nc_oc=Adp93nlJSAUc05G43DUIdSOoaabOhfT5SjWsKxHEhfhV5sO4jmXTbbAUgzKwdoL6xE0&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-4.fna&amp;_nc_gid=bxnKhyU0-zaLEgtw3DZ4TA&amp;_nc_ss=7b2a8&amp;oh=00_AQMlcBUaNzd15E_7At-15evxYprbuEQ7OEroXD2bIOLXXg&amp;oe=6ADECC98</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>100064824393033</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Hodowla z Łowisk Kaszubskich FCI</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/zlowiskkaszubskich</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: fci)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>puppy (P=0.99)</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0.9889</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>fci</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-6.fna.fbcdn.net/v/t39.30808-1/308173501_464333709070772_7771940692265865095_n.jpg?stp=c121.0.477.477a_cp0_dst-jpg_tt6&amp;cstp=mx477x477&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=bMGvanblNwEQ7kNvwF7qL1f&amp;_nc_oc=AdpS_8n062-7qPVZ4_l08CcbufqmXIzEL0NcRKW21DkncOMhL6Y86_vZhXiZBqo2c5E&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-6.fna&amp;_nc_gid=rtmwcGdODEvMUSlUw8JIzw&amp;_nc_ss=7b2a8&amp;oh=00_AQOAuXrq5kI4OXfvHeUjbusSqy9LsITSi5wCDxJNINg6JQ&amp;oe=6ADECACA</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>61575017544582</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CoalRun Retrievers</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CoalRunRetrievers</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: retrievers)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>retrievers</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-5.fna.fbcdn.net/v/t39.30808-1/537202195_122138328026833918_1229799567593563714_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx731x731&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=jtzRUxWW6nsQ7kNvwErl-Ax&amp;_nc_oc=Ado2ZlYfibY-fQ5fonOrBnMPE4RYAbo2Ofh2VcyUVMBuE8zr54yT98zwckWA44bQ75k&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-5.fna&amp;_nc_gid=rtmwcGdODEvMUSlUw8JIzw&amp;_nc_ss=7b2a8&amp;oh=00_AQNEi81KB8gnAp4ykDClraz4xY9DwEn0glO_LSvrNBemyQ&amp;oe=6ADECFF0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>100066548861717</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Doerner’s Star Labs</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/doernersstarlabs</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: labs)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>labs</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-8.fna.fbcdn.net/v/t39.30808-1/719788813_1334352542126362_1284611018648262610_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx2048x2048&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=yFwdBbzqUCcQ7kNvwFI9KQr&amp;_nc_oc=AdoyLwN9T9Z8wAQXBkt4SQzX3SilrYdFKqLMUGz6qkBwnOOedLEwDDigTNfLwZDtrpw&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-8.fna&amp;_nc_gid=jAq-8UGdIBW-RNqxKy6AwQ&amp;_nc_ss=7b2a8&amp;oh=00_AQMfyV_SAKSS8cHZApv5pScvz9taSuLTCOyC_YachYleRg&amp;oe=6ADEDE6E</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>61575343951538</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Dachshund Daily Dose</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/doxiedailys</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dachshund, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>dachshund</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-4.fna.fbcdn.net/v/t39.30808-1/659694259_1610847166634063_6308556825129446535_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx2048x2048&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=yO5oCcskXQcQ7kNvwFkOuPB&amp;_nc_oc=Adr8au2f1bEbA8W65FK_lQWuDnoJW4QyUZle5dQY1k_fFpY1Uq-8Xdjm_vtCgGCjtmk&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-4.fna&amp;_nc_gid=MIIMuvkyxDydMR8zIT9wCA&amp;_nc_ss=7b2a8&amp;oh=00_AQPwc-5GmCEY05QX-F2ovz462X7CO5i-8jMSYFPRsaNTnw&amp;oe=6ADEBF3B</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>61589947891623</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Dog Gone Mobile Dog Walking</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/DogGoneMDW</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: dog)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-9.fna.fbcdn.net/v/t39.30808-1/811589202_122111500425331596_8770801423832591616_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1284x1284&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=3cMbDlzzGwEQ7kNvwEpm8nw&amp;_nc_oc=Adrkw4_gRJQf18Vil50cbCCva4pNG-qJPzGJl7KBMjtKvAtYrSmrl-pKzLOTjpqjZo0&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-9.fna&amp;_nc_gid=wnUJEZi2ZVrRzlJad4w_1A&amp;_nc_ss=7b2a8&amp;oh=00_AQNP783LiKjeS_Eu1AP_vJL4cFMmYZABGcQPFbex3U_D0A&amp;oe=6ADEE48B</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>100070625920033</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Gaige Abney</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/gaige.abney.2025</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: kennels)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>kennels</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-6.fna.fbcdn.net/v/t39.30808-1/363329037_328270642870464_4580842712730076196_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1028x1029&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=67-AILX29t8Q7kNvwH913oq&amp;_nc_oc=Adp9qcWDXKSUDTbrmxqKpNl3si1nRPbyONEC2mhfotNHJNNYNh_zVjGaCbFLkjqraJU&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-6.fna&amp;_nc_gid=6tEFklkHwfrBkD3NPsXhUw&amp;_nc_ss=7b2a8&amp;oh=00_AQN2HYbJ5ptkV5ilLoMlM_Q9cPuhCFNmRy5JrzOC_pYpeQ&amp;oe=6ADEBD2C</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>100064506557557</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Teton Bird Dogs</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/tetonbirddogs</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dogs, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>dogs</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-7.fna.fbcdn.net/v/t39.30808-1/309041798_452316970261851_190881980141657116_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1023x1023&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=q_YXU3jMXTIQ7kNvwEP0PUa&amp;_nc_oc=AdpiaFRTtx5_FY8bT69qytg316skPiHlCiQSKQlUq0j8k4km6q7CAEzCQ7uCcFPr_zY&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-7.fna&amp;_nc_gid=oO3dmZynQ0XKlyfAl-O1yQ&amp;_nc_ss=7b2a8&amp;oh=00_AQN3LaCPV-Cm7zlVCDMQsFnDeoqUkdtF-YL2t42g_tsrww&amp;oe=6ADEDDEB</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>100057143783315</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Meu Fado FCI</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/meufadofci</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: fci)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.95)</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>fci</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-5.fna.fbcdn.net/v/t39.30808-1/294241500_537972111450910_7259806351204223577_n.png?stp=cp0_dst-png&amp;cstp=mx927x920&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=6G1H3SNyEbIQ7kNvwEK6scM&amp;_nc_oc=Ado6E-mUXMWQnq5kOTc528ZcibB5RSDgZBJYG1oyZQx-brNmBJBWd53WJLtxCqoXnAk&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-5.fna&amp;_nc_gid=uq8kDDjQtBBu-wce1xdhwA&amp;_nc_ss=7b2a8&amp;oh=00_AQMUgSLYkrEie_C_2nLFndO-wN6Qjx88lcQAlXlW5VdY7w&amp;oe=6ADED882</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>100071269713597</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Zyra Shepherds</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/zyrashepherds</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: shepherds, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>shepherds</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-9.fna.fbcdn.net/v/t39.30808-1/701004095_988033496915632_6489066231760998358_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1080x1084&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=Wm6VoiXJxgwQ7kNvwEdVx1d&amp;_nc_oc=AdqKC-ame1CB2SoRGd9TJ2Ro5VNZZYcudsm1KJrNNbGjgra1MqNi9DHpRCej1beMYw8&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-9.fna&amp;_nc_gid=uq8kDDjQtBBu-wce1xdhwA&amp;_nc_ss=7b2a8&amp;oh=00_AQMb9ziEQ4pOfTrarFfaZcnHvWwUkxfhRKGrUmuyzXV7fg&amp;oe=6ADECD7A</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>100076802074339</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Noodle The Dachshund</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Noodlelittlelegs</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dachshund, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>dachshund</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-9.fna.fbcdn.net/v/t39.30808-1/846302571_1102301749006551_6233594988145782849_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx566x566&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=SRRrkrrbfYAQ7kNvwE9HR8O&amp;_nc_oc=AdrK3C9TOPGlavC8dn8xkaTbY3S-C6inbXLHw5ccaC0NJBYFKvySdoX91rhZkzdGyMk&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-9.fna&amp;_nc_gid=uq8kDDjQtBBu-wce1xdhwA&amp;_nc_ss=7b2a8&amp;oh=00_AQPadnhDbqKBNF1WH8G9fVO8l-EHuN85OEmcTWzQY3pzAw&amp;oe=6ADEDA33</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>100089833995471</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>MXL Dachshund</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/MxlDachshund</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dachshund, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>dachshund</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-11.fna.fbcdn.net/v/t39.30808-1/473817467_572687019069093_2425743365337881736_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1276x1275&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=hC64MOQJGPgQ7kNvwEmU6Vm&amp;_nc_oc=AdqvQtFAvyZDr1DyqS0dhtNdADmEe80mnH6ZnkVHDNoLJqmSo2Iq_PTN1bwwSOus0ck&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-11.fna&amp;_nc_gid=2zYGj7uhxyp03na_6ZOVeg&amp;_nc_ss=7b2a8&amp;oh=00_AQNvM5fHTvqUyn2ns11a4T5EggScCQnzeKZAapBh6YizeA&amp;oe=6ADED36D</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>534417011</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Emily Scott</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/emily.scott.750546</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dog, k9, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>dog, k9</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-5.fna.fbcdn.net/v/t39.30808-1/691575948_10163588221967012_4470269604939251881_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x958&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=Lmy1IhvC0_cQ7kNvwHT8tMl&amp;_nc_oc=AdqGfE9laiN27hM6ZheTS8B4nLuxJGAUUGDaedctufq3leMVeGOT8roO-yyqxX-p1-Q&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-5.fna&amp;_nc_gid=lkUQf8PbSlcBYGlF3FNkfA&amp;_nc_ss=7b2a8&amp;oh=00_AQNgety06NhjFcmc0w6FA3hp1xBZK6XfQH7gUq3C_qXC4A&amp;oe=6ADEE1A4</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>61555880695539</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Red's Dachshund Ranch</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/RedsDachshundRanch</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dachshund, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>dachshund</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-11.fna.fbcdn.net/v/t39.30808-1/808397631_122319950300196023_9102425185725697782_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1536x1538&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=2wOuk5ouwP8Q7kNvwEke_Kq&amp;_nc_oc=AdriwchX-vTFfmPMsoXpsreIKrvvzLQ_hdmTD8PYE6LxKiOQPiYNWhNoVEUjF80P8R8&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-11.fna&amp;_nc_gid=IpNgj4jDbiR3opr0RWw2-Q&amp;_nc_ss=7b2a8&amp;oh=00_AQNLbLUmc57d_pJ-osKXvUX73g49gdXMRwxG6dMzbdnoVw&amp;oe=6ADED53B</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>100082659958568</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ridley's Red Retrievers LLC</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/RidleysRedRetrievers</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: retrievers, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>retrievers</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-6.fna.fbcdn.net/v/t39.30808-1/293572017_566667084980138_9130840792313773220_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx718x718&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=8QVBOsES0oQQ7kNvwFA3hNQ&amp;_nc_oc=Adq8kPXWZy3Wl2ED4oZd-uG0n8kbxmIcj6eaaEqgQli28gBRyCxphTYImt-kPRwfCQQ&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-6.fna&amp;_nc_gid=IpNgj4jDbiR3opr0RWw2-Q&amp;_nc_ss=7b2a8&amp;oh=00_AQP7Vux2_1j5G7GLXrwBS8DQ2_iDNGDpUG0ghgft0Uu-Gg&amp;oe=6ADED497</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>100063582942947</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Stem-Winder Kennels</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/stemwinderkennels</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Trại chó xác thực qua NLP &amp; Từ khóa (kennels)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>puppy (P=0.95)</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>kennels</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-6.fna.fbcdn.net/v/t39.30808-1/547479688_1418979926898092_7980290441035714576_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=xcYVDpOJ2GAQ7kNvwEQBAjd&amp;_nc_oc=AdoWE3dAMBwNTdvETseeZlipW8VjRAEBjk9-fz-WTVdn3yRxABMNKHVU6I1wYT39TGo&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-6.fna&amp;_nc_gid=yj8saG1BvRxVq6ndY5_dww&amp;_nc_ss=7b2a8&amp;oh=00_AQMqzlghKquQFEOUDp0k0fHnKJMx6dvMPT4j7AyVOvom2A&amp;oe=6ADEE59A</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>61562682404792</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Mini Golden Paws</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/minigoldenspaw</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: golden retriever, goldens, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>golden retriever, goldens</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-5.fna.fbcdn.net/v/t39.30808-1/451959193_122118359198335265_4521382635558848000_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=SIHdRudYjq0Q7kNvwHenNPN&amp;_nc_oc=AdrK190XD3tO1bXBjKYlnjpNsgFMkGUJtWPI856QD2lcarT7_GqHQOmULkultYAvdUU&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-5.fna&amp;_nc_gid=vuX5b_KOaAg3LwZG6xxS_Q&amp;_nc_ss=7b2a8&amp;oh=00_AQOEF5qYInMCsrU1yzSTp6FJYvXALd6D2vrIR0bN79kpRA&amp;oe=6ADEB6FF</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>100063455892186</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ali Howard Boxers</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/alihowardboxers</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: boxers, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>boxers</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-9.fna.fbcdn.net/v/t39.30808-1/816310126_1753755070083006_2737991998280237004_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1836x1836&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=_LHbSg-5IxYQ7kNvwEKRq1K&amp;_nc_oc=Adqkv9AoPqPonEuPM13PP3I3LV4OuHVvruIJfvDWA76DwikHPhd91DDGYXhcMP742KM&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-9.fna&amp;_nc_gid=vuX5b_KOaAg3LwZG6xxS_Q&amp;_nc_ss=7b2a8&amp;oh=00_AQOCH_EVQ8ImZWdftg0DjG9khOIy0rprfmaVv9-afJWfQQ&amp;oe=6ADECFDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>100077969013369</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Marthers Miniature Dachshunds</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/MarthersMiniatureDachshunds</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dachshunds, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>0.9992</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>dachshunds</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-4.fna.fbcdn.net/v/t39.30808-1/460492643_560724956536467_888348308505882879_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx2048x2048&amp;_nc_cat=102&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=G3pTHDGfVnIQ7kNvwEdvTql&amp;_nc_oc=Adpr9LslL5sFg6fBAQgC5T5CvvYNNUOfjjepE4g1H5MsPUDt6SgzsP2mwsGKi2J4j6U&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-4.fna&amp;_nc_gid=xdYGdwHzkdnJboRSsYl7xQ&amp;_nc_ss=7b2a8&amp;oh=00_AQPP9nFX-DG-nNgpzuqvTnLSovpkiw156gYVUtjywz5D5Q&amp;oe=6ADEBAD0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>551642546</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Amond Mathis</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/amond.mathis</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AI Thị giác nhận diện cún con sắc nét (Puppy=0.97, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-8.fna.fbcdn.net/v/t1.6435-1/201247829_10158486259207547_4668857006041483065_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=m9b7IBnhp8IQ7kNvwEwqrFv&amp;_nc_oc=AdomwCCS_Ikxd97rfMZDxjTectufjEklcOkSoEv2zTLfIOnjxPbIZdYLjPg9l_JepIY&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-8.fna&amp;_nc_gid=_P1VAfzSvNxN5XQv0OwLvA&amp;_nc_ss=7b2a8&amp;oh=00_AQPaIW-7uFLX0xeESpMBQZm_leoTx9wlJ8W9B6DZo-HgZg&amp;oe=6B005EBA</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>100063755345551</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>GC Labradors</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/gclabradors</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: labradors)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>labradors</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-9.fna.fbcdn.net/v/t39.30808-1/301958764_476870761114765_6241116631735181893_n.jpg?stp=c100.0.800.800a_cp0_dst-jpg_tt6&amp;cstp=mx800x800&amp;_nc_cat=102&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=-oD7uNqL6VoQ7kNvwEyf0Pj&amp;_nc_oc=AdooUdOe5aUMWpzVWIPRz7PfIOPvKCvLv-ThSDvKd7QVvhlc5dRxBy0ysrRvNZ9Vw8s&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-9.fna&amp;_nc_gid=_P1VAfzSvNxN5XQv0OwLvA&amp;_nc_ss=7b2a8&amp;oh=00_AQPRj-J2v9y_BH55DjW1idam1-batBSNNQBHmCJwv8gvYQ&amp;oe=6ADEC490</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>100063673085325</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ruslana Kennel - Black Russian Terriers</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/BlackRussianTerriers</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: kennel, terriers)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.95)</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>kennel, terriers</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-4.fna.fbcdn.net/v/t39.30808-1/310054116_526122882853477_4586826151300805689_n.jpg?stp=c6.0.224.224a_cp0_dst-jpg_tt6&amp;cstp=mx224x224&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=LXLYnZhdnOAQ7kNvwFZecUQ&amp;_nc_oc=AdqnWlu9cp3rqN-qHNL5y73ZQoXRqiR-GOTocXX6a4coNZhpSU3jn_c5yUAturrdW_Y&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-4.fna&amp;_nc_gid=lxhSSbKmSpyNa47mDfVW0Q&amp;_nc_ss=7b2a8&amp;oh=00_AQPPlT9-_IajM_jBTR0n2eVu__aFdoVAYJ-KweZCDBB7sg&amp;oe=6ADEE4FB</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>100042021046285</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>lunas_golden_life</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LunasGoldenLife</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: goldens, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>goldens</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-3.fna.fbcdn.net/v/t39.30808-1/810149122_1962655408478475_3061494857397150295_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1082x1083&amp;_nc_cat=1&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=elR2iwUSO3IQ7kNvwFeKCTR&amp;_nc_oc=AdoYeFbKTb7WhC_1x_3xaz6lq2oSvNneahgiVUbk2zk8Mm4hU8wcULE6IBpwbIClJGE&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-3.fna&amp;_nc_gid=lxhSSbKmSpyNa47mDfVW0Q&amp;_nc_ss=7b2a8&amp;oh=00_AQN5ZF-tJ7ADW5INTv36YGBSRvBRHN1ujtpHTVgSVVV98g&amp;oe=6ADEDB41</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>100000198559241</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Mihaela Sima</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/mihaela.sima.75</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AI Thị giác nhận diện cún con sắc nét (Puppy=0.73, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-10.fna.fbcdn.net/v/t39.30808-1/546408407_25402970285959574_722020997590043486_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1424x1426&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=ZFnyRruG3OoQ7kNvwHstj1R&amp;_nc_oc=Adrb8Cpxhhd2zwGZfpQP4ss1dyB-K-F0ohfdm3oiPgjSC48vyYAtIg6wTEqSUfd7jrA&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-10.fna&amp;_nc_gid=QlM04b0AIke92W8CHbebRg&amp;_nc_ss=7b2a8&amp;oh=00_AQNSy_dAEYiN_aH9iKysitLTEzDUpbMLvmU_Y4P2hMjO1Q&amp;oe=6ADEBC04</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>100008261735304</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Kỳ Kỳ</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/kykyquyquy</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: breeder)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.95)</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>breeder</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-10.fna.fbcdn.net/v/t39.30808-1/329870351_2369966166537071_7712686341117950536_n.jpg?stp=c0.0.555.555a_cp0_dst-jpg_tt6&amp;cstp=mx555x555&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=ezH9YnblHZoQ7kNvwG-3ljU&amp;_nc_oc=AdokBgN1Hqf5Ke_03SKHnGYXDU2qzJu6enuFlGBLJgGn6wzPqcgGRUtFRSqQ4-zdXL8&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-10.fna&amp;_nc_gid=HIrA_OWScc1LVePUY2jCgg&amp;_nc_ss=7b2a8&amp;oh=00_AQOscyIdNpv_wpBDK8RorNJdaBTEhhRLH8ZxJLFfmiGQCQ&amp;oe=6ADEBD95</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>100037191321615</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>The Berner Bunch</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/thebernerbunch</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AI Thị giác nhận diện cún con sắc nét (Puppy=0.92, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-4.fna.fbcdn.net/v/t39.30808-1/308964793_753694622546908_7008794383212293850_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx958x960&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=awT_8FI6-gMQ7kNvwF4YrY-&amp;_nc_oc=AdqpbVGXowjc7NVf_aSIUZmwATXAB_S30FkTVATTC6xMF_xZbgf-LxBEDFp5LokJnnQ&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-4.fna&amp;_nc_gid=hZagZ8H_wPPAiGHnBHTrZw&amp;_nc_ss=7b2a8&amp;oh=00_AQNvfe_2eEiT11OTlTDFVjEAexyEGdPlP9LWICa2cSSETg&amp;oe=6ADEBDCD</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>100063634177763</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Peer Gynt's Kennel</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/peergyntskennel</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: kennel)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>kennel</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-10.fna.fbcdn.net/v/t39.30808-1/820989103_1638660761598381_7792749562905799324_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx754x754&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=ZzN5EkFKDagQ7kNvwEDkc7Z&amp;_nc_oc=AdqLEJIFqtKRxl4NH3Zw82Dtzmd2RXXHtqAZTGe_SEUbXuq7yM98B73ZP2Q-QHSmgiY&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-10.fna&amp;_nc_gid=hZagZ8H_wPPAiGHnBHTrZw&amp;_nc_ss=7b2a8&amp;oh=00_AQOQ6cHIy1oa7r1WckSuFDVDnCAeiZcW1-aUDHtkzANMHw&amp;oe=6ADEE297</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>61574660902068</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Crystals Miniature Dachshunds</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/crystalsminidachshunds</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dachshunds, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>dachshunds</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-4.fna.fbcdn.net/v/t39.30808-1/825327363_122198684300822030_4028571413894327255_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx2048x2048&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=tGi9KKIiFmIQ7kNvwFeKwps&amp;_nc_oc=AdpiF5OmgZBo80Nm7Qtg0HOoc1NATF-KSMYro0UOAPMsGxqwFKkosTblpnr8zbAipm4&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-4.fna&amp;_nc_gid=hZagZ8H_wPPAiGHnBHTrZw&amp;_nc_ss=7b2a8&amp;oh=00_AQPA6z2j3md9S5EO64EQi1I-QQBCxr_pqIAx1FULDUN0MQ&amp;oe=6ADEE952</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>61591955992742</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Life with Mandy Girl</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lifewithmandygirl</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AI Thị giác nhận diện cún con sắc nét (Puppy=0.97, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-9.fna.fbcdn.net/v/t39.30808-1/741838772_10163800862084081_9072475102064019452_n.jpg?stp=c0.0.737.737a_cp0_dst-jpg_tt6&amp;cstp=mx737x737&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=JRaGuD6nVHYQ7kNvwHSeFmI&amp;_nc_oc=Adqa-FdFm3hSAGOsXFmS-s5SFEP51FYw5qkwTaZVzo0_wiX35hP9InVDA8LW7kppyVk&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-9.fna&amp;_nc_gid=r5Dk5zAC1PkcVacBEvZi0Q&amp;_nc_ss=7b2a8&amp;oh=00_AQOzCTRXS7fGgLvP85tntiLsHuxNY31azy1_B8W82s3sTQ&amp;oe=6ADEC44C</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>100083343218068</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ekaterina Antonova</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antonova.katerinka</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: lab)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>lab</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-6.fna.fbcdn.net/v/t39.30808-1/748763441_4390324447876447_3292436297324436914_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=1d5sc6m0i1oQ7kNvwGMVFfk&amp;_nc_oc=Adqhc286mxNMFYGf3SS2b1AXER1n2tsN36gJ-5Ei-bJ-7q1sSs2tRvtHQ2mg3vptkII&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-6.fna&amp;_nc_gid=O1MipKKzCxL6JDsBNWbufw&amp;_nc_ss=7b2a8&amp;oh=00_AQNzq06GBfBtM4gz99xOXN9nsMBsJ0KFSeObljBWQ7327g&amp;oe=6ADEE376</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>100064536676709</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Z the Dog</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/zthedog916</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dog, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-3.fna.fbcdn.net/v/t39.30808-1/292391456_408308117997074_7331715000336946326_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx761x761&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=65JNsIo2et8Q7kNvwFs0aX0&amp;_nc_oc=AdofkEyW09SCWm0VYzHKlnx-WQhFSnoexRb--wN-2-Oc3I6SCx6P0NaRkBQs-I8B9CI&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-3.fna&amp;_nc_gid=O1MipKKzCxL6JDsBNWbufw&amp;_nc_ss=7b2a8&amp;oh=00_AQNM5gUbB1fjEOf3-5TdJS7qARQTTc5JkTZFLFxJo_09hg&amp;oe=6ADECBD2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>100063537650998</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Akj's Dachshunds</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/akjs.dachshunds</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dachshunds, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>dachshunds</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-7.fna.fbcdn.net/v/t39.30808-1/506319285_1264252099036033_6034303410853765907_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1525x1524&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=4OgreY9vmrAQ7kNvwEgCcmS&amp;_nc_oc=AdqyB7nx1VlC2ntKH6XPGAnVvpFxKZ-Pgsv3eSpe3DItrRyqFnAlzuW7wmi6R57K5Nw&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-7.fna&amp;_nc_gid=x6HHTIf78ITK5NNQnuqB-Q&amp;_nc_ss=7b2a8&amp;oh=00_AQPMkx8CzGkYlL4q197SiCqUbgPBydL6NS0Sn2JFfOn3jw&amp;oe=6ADEBE02</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>61551418342467</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Grateful Dachshunds</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/gratefuldachshunds</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dachshunds, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>dachshunds</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-3.fna.fbcdn.net/v/t39.30808-1/514423996_122206574894047278_5174457543745340809_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1536x1536&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=y4R9QE2_uqoQ7kNvwGDjf45&amp;_nc_oc=AdrGp-Sd-ovAAx7Qg5FWoUqS_OTo8L7mWzSaxVIF7n9iJ62K4J9QhLfE_ZpIjN15Fh8&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-3.fna&amp;_nc_gid=x6HHTIf78ITK5NNQnuqB-Q&amp;_nc_ss=7b2a8&amp;oh=00_AQPsDTzo3GJeF7NsEtSlf9w9_sc35AvVheiQpPUMmnRfVw&amp;oe=6ADEC68E</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>100085409596825</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>River Ridge GSP</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/RiverridgeGSP</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: gsp)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>gsp</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-10.fna.fbcdn.net/v/t39.30808-1/722287238_982988721224772_1733466871049670508_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=ajnF1IdNeQMQ7kNvwF72vsq&amp;_nc_oc=AdoGp2YWTzKfsvW9ncpFZLVvcdLFnNaSYhGlfgxdWQ86k-rZ3EJrfS1hAOU8Eo5-Vrk&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-10.fna&amp;_nc_gid=B_8JSOjIPE_6SrJbxra_Pw&amp;_nc_ss=7b2a8&amp;oh=00_AQNFvSk0Yo-bgJkrXEFugNWwPEYlI3kk6_ak6XqlETmKoA&amp;oe=6ADEEDD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>100069857619930</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Bassbanda Kennel</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/BassbandaKennel</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: kennel)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>kennel</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-11.fna.fbcdn.net/v/t39.30808-1/302144993_378228784515706_7782716192791248684_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx497x498&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=TwVKyU7cM4UQ7kNvwHU1SxB&amp;_nc_oc=AdpXW5Kvvm9CltWwTOu1tl9-s9TDZHogRdXCD8EwNEoTHnWdoQsBOzgBTp6Lpw0HJPY&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-11.fna&amp;_nc_gid=B_8JSOjIPE_6SrJbxra_Pw&amp;_nc_ss=7b2a8&amp;oh=00_AQPtdaMXx6WvrnzDDBc9RdCqPP8R2GjRHewq1v9GsWZIyA&amp;oe=6ADED093</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>100034804999643</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Carter Labradors</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/carter.labradors</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: labradors, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>labradors</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-6.fna.fbcdn.net/v/t1.6435-1/54278887_110650173438482_6008147566175191040_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx750x750&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=wtbm_h9qKDIQ7kNvwFOtFg9&amp;_nc_oc=AdoKLxsl3qBuTS9_o43_BfJ9Yqcl0sd936Olz2M_hldkjHkcaD6kWR_vK_2Gkr71Kfw&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-6.fna&amp;_nc_gid=SkH_iMO6uBRT7rWPlCJi2Q&amp;_nc_ss=7b2a8&amp;oh=00_AQOtYKPt6f_IRhmAG3o6jiikjLBleMwXtcIyte6yKd0aZQ&amp;oe=6B008A15</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>100067583220189</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Kamiah Kennels</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/kamiahkennels</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Trại chó xác thực qua NLP &amp; Từ khóa (kennels)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>adult_dog (P=0.99)</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>kennels</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-5.fna.fbcdn.net/v/t39.30808-1/306493975_417348100527961_3719208576067603080_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx922x922&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=X7L_QFueHukQ7kNvwHUEENh&amp;_nc_oc=AdpmNydj3BlQs2FfBuZEQSBMXPsNZTC-JQqtyzkgOinvgarZgJTvmic13kG8v-IpMGM&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-5.fna&amp;_nc_gid=SkH_iMO6uBRT7rWPlCJi2Q&amp;_nc_ss=7b2a8&amp;oh=00_AQMXk9qRyh9AyKMWRyll_Hvxlhbn02I-V5UeYZV6D6vkQA&amp;oe=6ADEDE82</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>100063642247242</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ciao Bella Retrievers</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ciaobellaretrievers</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: retrievers, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>retrievers</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-5.fna.fbcdn.net/v/t39.30808-1/301507313_502381525226585_8830100451591189121_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1536x1536&amp;_nc_cat=102&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=bXZ6R6qXceYQ7kNvwFkhoWz&amp;_nc_oc=AdpjT1CJIz3C_7knsu_sPm4J-xYJoeg14GL2v3-hrZg1H8UDHaHKQ_A3gMPAQxKfxng&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-5.fna&amp;_nc_gid=SkH_iMO6uBRT7rWPlCJi2Q&amp;_nc_ss=7b2a8&amp;oh=00_AQP165bCQzlNmb5GOvBJicBWH1VR5reQx84RC7SY1FzjVg&amp;oe=6ADEBB0D</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>100080903007016</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Teatro Beagles - Philippines</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/teatrobeagles</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: beagles)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>beagles</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-9.fna.fbcdn.net/v/t39.30808-1/435688202_442630488443714_3639845615656862718_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx480x484&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=b0xS3NaFzGUQ7kNvwFEXOaR&amp;_nc_oc=Adoy9MNDbCpchLoeb97huVJlygbqKAGarLUjHqxQ8WVSAHgb7YSsV4AWFgKIOIss5RM&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-9.fna&amp;_nc_gid=BBCJ_8CCJ4_xrGxrhMPybA&amp;_nc_ss=7b2a8&amp;oh=00_AQNJwMrtdqtDcbfZZqyy-WvJE7G3tf4xRUaQTL6d1hAnwg&amp;oe=6ADEE92D</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>100064554444655</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Hounds Hollow Farms and Bassets</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/houndshollowfarms</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: bassets)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>bassets</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-3.fna.fbcdn.net/v/t39.30808-1/506349438_1112232714271866_2620181235567613675_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1024x1028&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=vF0hXcJXYG4Q7kNvwFiu39S&amp;_nc_oc=AdouK5kIGEvxzHWPRh0Zmlv2J3pjjmMGXzQ9a34mDJMMAvleeZWKjmikogskL4BSrPM&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-3.fna&amp;_nc_gid=vEuhP_YVH2KoC-z-UPwunA&amp;_nc_ss=7b2a8&amp;oh=00_AQMFRMQgKnFm5FJFzVO_AYjjS2DvdiTIWwI-fzfsuE2Wgg&amp;oe=6ADEE05A</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>100090261195847</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Corgi Ú Nần</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/corgiunanvanhungnguoiban</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: corgi, P_dog=0.81)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>puppy (P=0.81)</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>0.8131</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>corgi</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-3.fna.fbcdn.net/v/t39.30808-1/680345634_907194532299245_8050442921733413682_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx2048x2048&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=30XWV6iDxfgQ7kNvwFd1zWi&amp;_nc_oc=AdqwkXxcVvA8nRp6D-ND4ChAFUm8ntWLHxxDha817Gh1OfLhjQCg_gjjRecYTBCoHa0&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-3.fna&amp;_nc_gid=SJp1jGetVPO3ERoEHI3wLA&amp;_nc_ss=7b2a8&amp;oh=00_AQMQ902ICz5emcwOc_QwPv_GcEsAjXYGj9G8Krm4uQakGw&amp;oe=6ADEC8D7</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>100063594955168</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Dachshund Maddie</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Lhizadventure</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dachshund, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>dachshund</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-10.fna.fbcdn.net/v/t39.30808-1/679434636_1564699005659916_8965088491556189323_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx2048x2048&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=LHT8HTDTA1AQ7kNvwHTaRBX&amp;_nc_oc=Adq57XEzbDI3RIvUSikbibLnD4tBwWjB7UCFfEK3Tnr25mq4UZVkWMY2K1iLpfcinxQ&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-10.fna&amp;_nc_gid=dibZpsV78J4Fh9xLinB5fA&amp;_nc_ss=7b2a8&amp;oh=00_AQPKGaKtIcUjPnmuQ__5Tjko1yNZ2dsD5QDarPwLODsbqA&amp;oe=6ADED33A</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>100058870425587</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Gunderson Dog Training and Boarding</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Gundersondogtrainingandboarding</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: dog, dog training)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>dog, dog training</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-6.fna.fbcdn.net/v/t39.30808-1/290207996_499182558720754_7704497780115556736_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1465x1465&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=w2V0iD1ECZoQ7kNvwHKBwN_&amp;_nc_oc=AdqFbtJ-wwQKs6JLu2VyfO8CSoQlHyq9HfDX-tuPDLMs6zMPLjJnlQ1Ie3lXZAGKpbo&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-6.fna&amp;_nc_gid=dibZpsV78J4Fh9xLinB5fA&amp;_nc_ss=7b2a8&amp;oh=00_AQMwyNvXWRN63AgUzPK80j-CseQMDMgPgtpyANMLuC6-5A&amp;oe=6ADEE22D</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>100089378418224</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Faith's Bernese</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/faith.s.bernese</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: bernese, bernese mountain dog, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>bernese, bernese mountain dog</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-11.fna.fbcdn.net/v/t39.30808-1/560636045_817524957903444_3992353453240733862_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=eQ_JIOZbMUwQ7kNvwEWBNgM&amp;_nc_oc=AdqkyutKI7lKXQ415g8ryHzrduUak58uGxEXmjhQBiQpj6Dkw7iEzOicF4-LrpGNQp4&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-11.fna&amp;_nc_gid=d9qn_2bjiSbcSIL-VceNPQ&amp;_nc_ss=7b2a8&amp;oh=00_AQOHpghXhCrf-N6zpFln03hzRgiocDY4EdaebyXLBq_NzQ&amp;oe=6ADEEDEA</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>100063931754012</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Bond Mountain Kennels</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bondmountainkennels</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: kennels)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>kennels</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-7.fna.fbcdn.net/v/t39.30808-1/468297332_1015427913931591_445771739120971526_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1080x1089&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=y2L5h3V85kIQ7kNvwHreEDn&amp;_nc_oc=Adopf13ux7xjQy8OcJp9xJtGGeya9zL49W9WSAxArkoCremt1pBJK0FvQOSOTKWIsrQ&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-7.fna&amp;_nc_gid=FicMpt5bfDX5dX0OCJyoqA&amp;_nc_ss=7b2a8&amp;oh=00_AQMAcA4I9FQvSgdLERT7rG6MzUbGagmco8cy63UAUBHaiQ&amp;oe=6ADEE518</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>100063588491495</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Bayla Belle the Boxer</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/BaylaBelleTheBoxer</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: boxer, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>boxer</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-3.fna.fbcdn.net/v/t39.30808-1/310432828_553826026747009_5002588463408852096_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx2007x2015&amp;_nc_cat=102&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=2XbZTVJxn2sQ7kNvwFPu2an&amp;_nc_oc=Adr8E88G5xlQVnF3IB6Da1ZZXReFwmQuPku6PupnB5-0nQnJzva6HfHJTJMAsJOWD08&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-3.fna&amp;_nc_gid=M-jWSlzD6_KUbnLelwtmOQ&amp;_nc_ss=7b2a8&amp;oh=00_AQMg3c_DaNpAhYmWfOBi0J3jlo3UC4o6fqAFWBO-oTbOHA&amp;oe=6ADEDD7B</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>100063542262170</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>3 Color Kennels</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/3ColorKennel</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: kennels)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>kennels</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-3.fna.fbcdn.net/v/t39.30808-1/742317203_1610833574378036_6321014815444810406_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=102&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=7gK2flm-fEgQ7kNvwE2RSMm&amp;_nc_oc=Adr3FEiYlCBpSUB5jAvvwwrtT-o3iSYLVZ3T7j_1mTkXIuXwibO2io4nELfXxGmMjsM&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-3.fna&amp;_nc_gid=Jo388aEb-yYfX_g-DakEvw&amp;_nc_ss=7b2a8&amp;oh=00_AQN0bZz-jr3oL22Q0hInizQssQfSaXyEs1hYRQv-K0fgqw&amp;oe=6ADEC3E9</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>100092709731153</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Campbell's Family Dobermans</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/campbellsdobermans</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: doberman)</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>doberman</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-6.fna.fbcdn.net/v/t39.30808-1/434057462_311109635322692_6588181080330491679_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x958&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=eZcNXPw0vuoQ7kNvwGDLMTf&amp;_nc_oc=AdonSuwolnWOc76RGwW4WgkAgSz1vQryXIqppaRLYAr7DQMEdliZ87R1PAmvReFxJIE&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-6.fna&amp;_nc_gid=a4WTiINT1Qo5z_JR_KKX3A&amp;_nc_ss=7b2a8&amp;oh=00_AQN_a9NuvjR9S3BVtRn5ZqxUAusBSKnq1nWIK6yuIi-m3g&amp;oe=6ADED609</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>100001119918590</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Nutra Gold</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/juancarlos.espin.77</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AI Thị giác nhận diện cún con sắc nét (Puppy=0.89, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-4.fna.fbcdn.net/v/t39.30808-1/839884717_28579594968327786_1761950544024189800_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx916x915&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=iGJe5-vwMx0Q7kNvwEFeu7-&amp;_nc_oc=AdpJrIsaBaObTb-1XwtEVau82vifYTS_IFqWD-U5mkf-kr_ulRXyV2ZwxOzDW_6meF4&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-4.fna&amp;_nc_gid=a4WTiINT1Qo5z_JR_KKX3A&amp;_nc_ss=7b2a8&amp;oh=00_AQOH5cb-QEolPWg_j_wdVBtP1GRtWKmkJyG1ybMOS5gQ8g&amp;oe=6ADEEC8A</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>100031018432731</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Bellbidgee Labrador Retrievers</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bellbidgeelabradors</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: retrievers, labrador, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>retrievers, labrador</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-10.fna.fbcdn.net/v/t39.30808-1/214885325_4525671050828700_1717656194059483742_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x959&amp;_nc_cat=102&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=pU1TFgfnyz4Q7kNvwFn4G6Z&amp;_nc_oc=AdpEEinKguUawSwBjKF45CpthKWjrVFHGZQnWRMIw8YhIVrTLe6TrPCzev7FyHrfkvo&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-10.fna&amp;_nc_gid=tj_o8yig_5t6oUmhGw2mmg&amp;_nc_ss=7b2a8&amp;oh=00_AQMW2ReVBMYqPaZy-JGbpuWnmQsi-vdsyy6PGYft-HfWZw&amp;oe=6ADEE8A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>100083250373087</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Tiny Doodle Paws</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/TinyDoodlePaws</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: doodle, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>doodle</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-3.fna.fbcdn.net/v/t39.30808-1/289433961_111983374886220_8602933645312508401_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx868x868&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=mqTzCUhnfcwQ7kNvwHgECQq&amp;_nc_oc=AdqqjD_Xb_mMDcWYaVGoTKsdQA0XwwIeUGTbCJKcRKDH8pXwbILaaMh00uK1lGCVYJY&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-3.fna&amp;_nc_gid=tj_o8yig_5t6oUmhGw2mmg&amp;_nc_ss=7b2a8&amp;oh=00_AQPODWYuzmlh7dTgcBLIRRV1zCTBWNSTuU0LTRtfoXh5tw&amp;oe=6ADEC007</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>100063686825046</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Mitchell's Bulldogs</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/MitchellsBulldogs</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: bulldogs, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>bulldogs</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-10.fna.fbcdn.net/v/t39.30808-1/279022249_5208584735870014_4316431710155677890_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx959x959&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=MgrBcJBjtbsQ7kNvwFI8Ar5&amp;_nc_oc=AdqVZxK6MYKrKxQMRHQXKn24wNc1STyRqKtB8Asb5wT0kEcjcbm0gybOGujrYZHE25I&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-10.fna&amp;_nc_gid=_yetsS5s8CGcOd0yReUl2A&amp;_nc_ss=7b2a8&amp;oh=00_AQPtt8toHYoxiVXk7XGWSC_rj5IMwD-hftIWOJ2PICmbxg&amp;oe=6ADECBE6</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>100062232236519</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>RedDoor English Springer Spaniels</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/reddooress</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Logo/Biển hiệu trại chó &amp; Từ khóa xác thực: spaniels (không có mặt người)</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.88)</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>spaniels</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-7.fna.fbcdn.net/v/t39.30808-1/305988707_501015138649556_6265477696001944159_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx94x94&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=9SidU36RouMQ7kNvwECvQ0X&amp;_nc_oc=AdoULjrMEDd9dk4qJFIq1kp9aJjEcMsSRYn0jZhPNFmTOWWt14diPgqpoaqTQHzZmGI&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-7.fna&amp;_nc_gid=_yetsS5s8CGcOd0yReUl2A&amp;_nc_ss=7b2a8&amp;oh=00_AQN4LL0wm9HhBND7Lt8JBPsUqb2zfoGP3_iw37PjLYYOrQ&amp;oe=6ADEDC09</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>100002525775156</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
           <t>Aurora Lopez Perez</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>https://www.facebook.com/aurora.p.lopez</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: shih tzu)</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>non_dog (P=0.85)</t>
         </is>
       </c>
-      <c r="G21" t="n">
+      <c r="G88" t="n">
         <v>0.85</v>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>shih tzu</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>https://scontent.fsgn8-4.fna.fbcdn.net/v/t39.30808-1/623396454_25642511325416375_1384894326437316373_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=G9Z8RlS_0aUQ7kNvwGXFEQU&amp;_nc_oc=Ado2UrFjqY2E7cXSKqd6cutgVKUlenoSP-wHYT7DZleC0eT_7AfJ83Uu7ai1ku8vrwQ&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn8-4.fna&amp;_nc_gid=ak9sxYgbexO8hxOyCbHoeQ&amp;_nc_ss=7b2a8&amp;oh=00_AQP8MhvOXcjrxB-f1wAOvmpBnhwk01jQzQQHvj7yeFZQcQ&amp;oe=6ADE54B6</t>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-8.fna.fbcdn.net/v/t39.30808-1/623396454_25642511325416375_1384894326437316373_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=G9Z8RlS_0aUQ7kNvwG_oeWM&amp;_nc_oc=AdpaOTtE8GvysgCEtWGaMscXHcE5oQYIBOdDE1opKN6o2t8GxYmZcPR29h9vw01xHvw&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-8.fna&amp;_nc_gid=mUgTey2-g7zWjLTftn443A&amp;_nc_ss=7b2a8&amp;oh=00_AQPbgaNRfnucQ46Vl7Qp1JdYRFAXWHWqZTONf6f3q_89hQ&amp;oe=6ADEC536</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>61551553590786</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Infinity Labradors</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/infinitylabradors</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: labradors, P_dog=0.98)</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>adult_dog (P=0.98)</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>labradors</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-6.fna.fbcdn.net/v/t39.30808-1/471550061_122167368176051786_4228868388669043714_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx2048x2048&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=MGHDgEceqNUQ7kNvwEwqbaM&amp;_nc_oc=Adq0Vep3_35QbFh6pqb-m0va14ca8Xu4WPMJvj5zh5IbHVfSZRXIHYGVAji__bjN5D4&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-6.fna&amp;_nc_gid=mUgTey2-g7zWjLTftn443A&amp;_nc_ss=7b2a8&amp;oh=00_AQNj4ZmathKkmFBEUqi2Ad0AQ2G5oIl688x6TFS5HxHaqw&amp;oe=6ADEC2A0</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>100005180677307</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Renata Garbiec-Grabarczuk</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/renata.garbiecgrabarczuk</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dog, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>0.9993</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-10.fna.fbcdn.net/v/t39.30808-1/421270792_2463445120504820_8678303496292284906_n.jpg?stp=c298.0.1523.1523a_cp0_dst-jpg_tt6&amp;cstp=mx1523x1523&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=npMxMi0XlSMQ7kNvwHJOA-m&amp;_nc_oc=Adr7FPRthN2QRlnxWVl2tdYWqQL11EyjayPfIkGI5xo_gYgD7tbk89Oza_5Czu7zv3U&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-10.fna&amp;_nc_gid=mUgTey2-g7zWjLTftn443A&amp;_nc_ss=7b2a8&amp;oh=00_AQPIcm0B3xOmIE7zO1srinfC6Y0_rEfg7C11ROnOVC900w&amp;oe=6ADECF1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>100082739012812</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Friendly Goldens &amp; GSPs</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/golden.wells.96</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: goldens, golden retriever)</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>goldens, golden retriever</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-9.fna.fbcdn.net/v/t39.30808-1/449971727_457129867054977_5116582570273371989_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx500x500&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=NsKOzGB39BAQ7kNvwG7FXZw&amp;_nc_oc=AdqbDae1Vpa4XTcQ7ok58bMWvXNBtENcQFUSiF4cJ9u26eUmDM6cydsyvmM3rA4h978&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-9.fna&amp;_nc_gid=mUgTey2-g7zWjLTftn443A&amp;_nc_ss=7b2a8&amp;oh=00_AQNyLxAke6460Q_KTSNeRqgeG6ik7p-uE4x7r_kQKyU5VA&amp;oe=6ADED1D8</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>100042892844118</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Madi Hewitt Madanwitt Cocker's</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/madi.hewitt.5</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: cocker, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>0.9956</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>cocker</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-3.fna.fbcdn.net/v/t39.30808-1/286991137_759314845508270_8271362334676756874_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx828x828&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=x0V8zLkAeUIQ7kNvwHdjVXZ&amp;_nc_oc=AdqwXRQVvlaRGiYxk7GOY1Rzfc4yHnzOp4xDDt0wtP6qSTskX5M7NrsbsbS83ma1Erg&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-3.fna&amp;_nc_gid=2DzOGn0D_ti_vgHmgCh5aw&amp;_nc_ss=7b2a8&amp;oh=00_AQM-gq-ni5citD_BL9vgvztE3fJkIue1n-0DYcwZ1_pk8Q&amp;oe=6ADEECEB</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>100051070886140</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Houston bull terriers</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/officialhoustonbullterriers</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: terriers)</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>terriers</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-4.fna.fbcdn.net/v/t39.30808-1/638213482_1491553099223705_7519236817093027216_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x958&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=D4aAcYrS9pMQ7kNvwGSITwV&amp;_nc_oc=AdoplIRLpmKPcjfvkZ_bxjk9mQC6i0CA25qkVM2UyamKigCbIXA66vjdjRq68LmJEeM&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-4.fna&amp;_nc_gid=2DzOGn0D_ti_vgHmgCh5aw&amp;_nc_ss=7b2a8&amp;oh=00_AQOnZJGbyfIf-BsAbxzbVZzj5BoPYrqpsoSjUxd4GV26GQ&amp;oe=6ADEB6B5</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>100064769614476</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Varkata Labradors and Leonbergers</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/VarkataLabsnLeos</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: labradors, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>labradors</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-7.fna.fbcdn.net/v/t39.30808-1/275570477_2464872986980560_4938544357444121951_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx958x959&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=nnng0_-DaBUQ7kNvwGN6yCl&amp;_nc_oc=AdpBUFDjCVo1yGLXvLTQZzD2ZASC5T5nK899baz7xHkJwz3IXNQlys5N0vLRVNMq_IY&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-7.fna&amp;_nc_gid=hoUZ4ooshuAQ1g9K1oUDNA&amp;_nc_ss=7b2a8&amp;oh=00_AQMhWUkIxPh7ME5GIco4FALKR10eL8W3ny3y5NBIlyNxWA&amp;oe=6ADEDB04</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>61592880550563</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Golden Retriever Joy</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/goldenretrieverjoy</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: golden retriever, retriever)</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>golden retriever, retriever, goldens</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-8.fna.fbcdn.net/v/t39.30808-1/772376171_122100681831433154_4450795957241860146_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1254x1254&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=BqnW1NcgkG4Q7kNvwH1On5g&amp;_nc_oc=AdoxgQ6uz_j-CBDIkDHedxTzFPRTkSID9sRjNmTLuySu04YEcGKXbLL04Ier9nygVWI&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-8.fna&amp;_nc_gid=3yzvbAxXiCVHiI0GxRcFRQ&amp;_nc_ss=7b2a8&amp;oh=00_AQMCnCde0A-v9C4X7VpTfTfag5nm8-VFZJdPf0-HWFhmsQ&amp;oe=6ADECE91</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>61591727084764</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>TuffyBruno</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/tuffybrunopup</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: puppy, dog)</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>puppy, dog</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-9.fna.fbcdn.net/v/t39.30808-1/746565201_122106949149390902_7753833943234317682_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx2048x2048&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=PJallGj1-A8Q7kNvwGTA1u2&amp;_nc_oc=AdqFyoRodg9VWF8rhgwXoFBJ8Ymyh2MWX5tAFqAcCqQqxHx0cBQGJ45vOiFi0cK_fes&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-9.fna&amp;_nc_gid=3yzvbAxXiCVHiI0GxRcFRQ&amp;_nc_ss=7b2a8&amp;oh=00_AQMJd_TDgdEs1TzAd8-AYO23mNfzhixLCKk54pRUAn9eeg&amp;oe=6ADEE846</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>100067467135488</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Crooks Mastinos Neapolitan Mastiffs</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/crooksmastinos</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: mastiffs)</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>mastiffs</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-9.fna.fbcdn.net/v/t39.30808-1/292549537_372268345032067_1411509536215338141_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx605x613&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=Elc5YWxBH_UQ7kNvwFBq7A3&amp;_nc_oc=AdoeZulbVyuT3AiNAtvDjRtssgbX7r8mcu89b85J1J9x1OQGr2ZnsOYcfhfVoBuigK0&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-9.fna&amp;_nc_gid=Kii7-Gb3KafE8SFh_EJm6A&amp;_nc_ss=7b2a8&amp;oh=00_AQPQi8-lOUJLh-xN_PFRmSMz799dlBiQtxrWg7kCat022A&amp;oe=6ADED5A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>100057565813576</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Sandy Hill Basset Hounds</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SandyHillBassetHounds</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: basset, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>basset</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-10.fna.fbcdn.net/v/t39.30808-1/297230730_512171227378400_7632117691078612958_n.jpg?stp=c78.0.480.480a_cp0_dst-jpg_tt6&amp;cstp=mx480x480&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=D7SXNu839QwQ7kNvwGV1dGc&amp;_nc_oc=AdqBjSD-2MJnxWHt6NsByRNpBBt8SULOtKx9UL6Z4e7oOngJ65Z2oHbotIMYldqZbhw&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-10.fna&amp;_nc_gid=Kii7-Gb3KafE8SFh_EJm6A&amp;_nc_ss=7b2a8&amp;oh=00_AQM2prruxXe6ILoIVRaP0LWVAnTnQYk5M-f6rmMCwt8Wow&amp;oe=6ADED6AC</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>61588564431986</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Bloodhound Nation</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/BloodhoundNation</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: bloodhound)</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>bloodhound</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-10.fna.fbcdn.net/v/t39.30808-1/747839852_122118403827285481_7827330566004084443_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1254x1254&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=lqi38oFd4r4Q7kNvwGpsdvY&amp;_nc_oc=AdrDLW55uldxIJ2v9g1m5ZvM8L3KFpDJ0FQPIhsnBjfVHiWCKjGCFxIDlAsJ_S0g13g&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-10.fna&amp;_nc_gid=JRg8ri3HmCFt3O1UX3flfg&amp;_nc_ss=7b2a8&amp;oh=00_AQN4p4YMu467jlB1v885VhPi735bFwW-QbbP1jgNKp1hJQ&amp;oe=6ADED46A</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>61593441883043</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Lady the Dot Dog</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ladythedotdog</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dog, P_dog=0.87)</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>puppy (P=0.87)</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>0.8651</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-3.fna.fbcdn.net/v/t39.30808-1/784252620_27599526439743908_3099950496219197605_n.jpg?stp=c0.0.1071.1071a_cp0_dst-jpg_tt6&amp;cstp=mx1071x1071&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=bxXcYKeQVSMQ7kNvwHqCwZw&amp;_nc_oc=Adrmr1LKvlqPvi41Obe_s5Zn1rHQi1_yNQi8xTiXrDmsPpTW3Pc5lSCAC3eP-WGkvYY&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-3.fna&amp;_nc_gid=o_wszqXVgflS35kyfRRv3A&amp;_nc_ss=7b2a8&amp;oh=00_AQMLwkWIT37XjKWu8Zezh5wM7wQDhlj8VWXSpOtIM9BEPQ&amp;oe=6ADEEA4D</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>61589562862025</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Phoebe girl the Lab</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/PhoebeGirlTheLab1</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: lab, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>lab</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-6.fna.fbcdn.net/v/t39.30808-1/793378166_122116965369318762_4035498590816003615_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx2048x2048&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=PqFkIj-I0WEQ7kNvwG_2x-C&amp;_nc_oc=Adoz-Fkorlu-7Tr2at1MmDByPWyIO4aFnX7_yml2TSiSc_3BI1Wk1Ja3bQYieHbCAO0&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-6.fna&amp;_nc_gid=o_wszqXVgflS35kyfRRv3A&amp;_nc_ss=7b2a8&amp;oh=00_AQOVQlXMI5di93A87Ej5LCZeHilzsX5YoOCUTonN07ZEDQ&amp;oe=6ADEB5DF</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>100083207986779</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Von Haus Moon Rottweiler Kennel</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/von.haus.moon</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: kennel, rottweiler)</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.95)</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>kennel, rottweiler</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-6.fna.fbcdn.net/v/t39.30808-1/766890168_1038950428888547_5417004000130221779_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1141x1141&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=Oss85vTuDQMQ7kNvwG5HMlt&amp;_nc_oc=AdrnJFmHFF7eexsD_IcOFn-w2iWnwACGIXQgl3jtpTnwkBYfUrwV07a5NNG2kW4SitY&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-6.fna&amp;_nc_gid=09seLmbMHQQWryTKPFoE-Q&amp;_nc_ss=7b2a8&amp;oh=00_AQN1ObrdYunE_HxHOVdIwbu2YYDqBzGInmQcn-OKjpyufQ&amp;oe=6ADECFBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>61593270983943</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>B-Hive Bulldogs</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bhivebulldogs</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: bulldogs)</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>bulldogs</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-5.fna.fbcdn.net/v/t39.30808-1/769317989_1702047594419579_3850571583909919585_n.jpg?stp=c67.0.1407.1407a_cp0_dst-jpg_tt6&amp;cstp=mx1407x1407&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=7DbQO95__c0Q7kNvwEmd7YI&amp;_nc_oc=Adp1LYGzU0PvxkiSfarJNCXBBnuEVfNLRt8Yy67JReszl8PsuGLtq7zLXDSodeBKEgc&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-5.fna&amp;_nc_gid=09seLmbMHQQWryTKPFoE-Q&amp;_nc_ss=7b2a8&amp;oh=00_AQMiNlWWqHJ0Y_910gBPkMJ-w3bLW3a7Ziug6YjjnaTBOw&amp;oe=6ADEDB26</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>100064037679529</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Heyd's Mini Dachshunds</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/heydsminidachshunds</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dachshunds, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>dachshunds</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-8.fna.fbcdn.net/v/t39.30808-1/426454175_796535009157748_2961623968999047031_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=NVm_C36kAHoQ7kNvwE7MPLz&amp;_nc_oc=AdqMHHVZk7ZAj8RWnTsgY8zkRsYLtSJtQ-iHyk5MulqrHYjDHzkTY2b4Z0pZCEDvKag&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-8.fna&amp;_nc_gid=_OPKQEa2wDgAZ0Cc5hY6-g&amp;_nc_ss=7b2a8&amp;oh=00_AQNnMsp7ht5N-TWC-cX7PI5yB5ocK2_LFkN9CTz2B53C6w&amp;oe=6ADED461</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>100076157324386</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Beagle lovers &amp; Owners</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/usabeaglelover</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: beagle)</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>beagle</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-5.fna.fbcdn.net/v/t39.30808-1/311572740_181240931091150_5343857396870952561_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx2048x2048&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=VqC6qXp7cTMQ7kNvwHWqHJk&amp;_nc_oc=Adr5oJwOC_VELERUqeF5jMmXjqDyg2Neyq9cwqPTfWPq85D5RBriAASE6_9qmfv5T7Q&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-5.fna&amp;_nc_gid=GwwaZWAvsRE88Vn4QHc3Nw&amp;_nc_ss=7b2a8&amp;oh=00_AQO_LFooBqa07qqH6O2w2v82jklkUTixNatseXdV-9tz7g&amp;oe=6ADEEB92</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>61570211577054</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Mark Taylor</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/mark.taylor.548492</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: bulldogs, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>bulldogs</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-9.fna.fbcdn.net/v/t39.30808-1/821223486_122196142340673719_2640066306750276577_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx752x752&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=qQUw6YRYmFgQ7kNvwGMODTt&amp;_nc_oc=Adq5vj-ThhU-bVPMJ00iyEgGyPk9VEzd3BwrHTITCnmLTaMezehp_ACpi-Q4fWRl7Kk&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-9.fna&amp;_nc_gid=K_ogHgbXVUhTaAmbewPtkw&amp;_nc_ss=7b2a8&amp;oh=00_AQMVAkR8eyC_sNV-zTUcWvRSS3OTQD3oknFPr7JDYBMoTg&amp;oe=6ADEDEF6</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>100070760426814</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Gambel's Goldens</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/gambelsgoldens</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: goldens, golden retriever, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>goldens, golden retriever</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-8.fna.fbcdn.net/v/t39.30808-1/420044496_405780098457334_5364298849667547704_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx954x954&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=otUWdcb_6vUQ7kNvwFxKI6b&amp;_nc_oc=AdrrLR-bBkvO1Gb5qovAizpzyggg81wuS2wVl_dmzoH2jWMJGHiz9PepL6iT6PcoHd4&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-8.fna&amp;_nc_gid=0YROSQhQGJmx5P2ha4JVPQ&amp;_nc_ss=7b2a8&amp;oh=00_AQNfzIs82P2EnUT59XZYqemOvyqeTGlhUK0jNcYLNuJo8w&amp;oe=6ADED235</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>61567528932117</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>River &amp; Banks • Golden Retrievers</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/riverandbanks</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: golden retrievers, retrievers, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>1</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>golden retrievers, retrievers, goldens</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-7.fna.fbcdn.net/v/t39.30808-1/643872992_122185900580584297_7708745231991445351_n.jpg?stp=c0.0.720.720a_cp0_dst-jpg_tt6&amp;cstp=mx720x720&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=fT3E5NfIShYQ7kNvwEtr35s&amp;_nc_oc=AdrJJTXmL2dRuHstLI_pIZnesw4HAjsNs-hScVubiYevWpyU3rqhc5r70Tc01d1p5s8&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-7.fna&amp;_nc_gid=0YROSQhQGJmx5P2ha4JVPQ&amp;_nc_ss=7b2a8&amp;oh=00_AQO_x2u9UGdfHb0vuvxMSfuI67Q9oEJoDbRlG6VEOZ_voQ&amp;oe=6ADEEBC5</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>61557194374998</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Rottweiler Love'r</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/rottweilerlovers2.0</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: rottweiler, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>0.9993</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>rottweiler</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-4.fna.fbcdn.net/v/t39.30808-1/434086425_122112045590239812_2421138693220769099_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx512x512&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=WrIPnjRx36QQ7kNvwFQLsY1&amp;_nc_oc=AdqJhY8T-jHcOH5tRk5E5uvs0weRapZMu89Jubq4qvrdzoZseGB2EKDIDxsZFnnwJBg&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-4.fna&amp;_nc_gid=0YROSQhQGJmx5P2ha4JVPQ&amp;_nc_ss=7b2a8&amp;oh=00_AQM5EF2fOq0alIwzihQChi_vNAlsQWBkIiMikcgEwTp5UQ&amp;oe=6ADEE8CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>100057660429188</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Vizslas Devon</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/VizslasDevon</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: vizsla, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>vizsla</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-6.fna.fbcdn.net/v/t39.30808-1/292548844_483168133615197_4458197433449984666_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx650x650&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=4Hz1PmzBmNEQ7kNvwHx5CWw&amp;_nc_oc=AdpU9CZiBD7dW4ZoJHMHWxFErURvvxnmoH4ftfQ21zf5daoNoviH7FOBUzX6lgUa33E&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-6.fna&amp;_nc_gid=K_ogHgbXVUhTaAmbewPtkw&amp;_nc_ss=7b2a8&amp;oh=00_AQMrbaKYywd6ePvsL8ZA1qMbjLZvGrbRywGYn3vTCoXcpA&amp;oe=6ADEE0F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>61584930023400</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Bowie The Great Dane</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/BowieTheGreatDane</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: great dane, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>great dane</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-8.fna.fbcdn.net/v/t39.30808-1/597428340_122093899563164334_9167502203056476107_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=E_7Cm7ja4TcQ7kNvwEKEOnn&amp;_nc_oc=AdoFL9d8ajy5JFUWR_p0EtYf2JUBsNVRS2tfknFDzPum8P7omTyKb8aaDDN0KUWjzjw&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-8.fna&amp;_nc_gid=dzu9xJ8T9eRRwDX0mL6E0A&amp;_nc_ss=7b2a8&amp;oh=00_AQNrqGDruJJt5f0-aHJVnHA2Z1f1We_nOI4tI7dqOSo9Cg&amp;oe=6ADED768</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>100067895330899</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>A &amp; M's Boxer In Southeast Texas</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/AandMboxerInSouthEastTexas</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: boxer)</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>boxer</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-6.fna.fbcdn.net/v/t39.30808-1/435702508_756781846594986_7558030160658695620_n.jpg?stp=c120.0.720.720a_cp6_dst-jpg_tt6&amp;cstp=mx720x720&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=4H3235eV8wUQ7kNvwFR6ey6&amp;_nc_oc=Adq7Ta01Bt7AmI94B0Lq0xNlLZHisoLYHWWZtWjWiXJuU9NTh-1MxrScWygcowRtcRY&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-6.fna&amp;_nc_gid=dzu9xJ8T9eRRwDX0mL6E0A&amp;_nc_ss=7b2a8&amp;oh=00_AQMNY5vsbSEnoG7bp41ajX5FS06ongo_PeI36nJcgPybQg&amp;oe=6ADEBF24</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>61569213089881</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>DoggoDaily</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/OfficialDoggoDaily</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dog, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-10.fna.fbcdn.net/v/t39.30808-1/853716744_122117780270640436_5690628097570458668_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx525x516&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=-L713tEhVAEQ7kNvwEWq7p2&amp;_nc_oc=AdoHVvVSwz2JlUVSJpzdM4DUnusMKCd24-Fi8lr3uYFGItdHYYXZo-w-Vi9jp8McDIY&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-10.fna&amp;_nc_gid=Pr-wK7aW5lkvrlzBMP9QKg&amp;_nc_ss=7b2a8&amp;oh=00_AQNdSVBVAzlqgAQmtjBF6gAJi8F_AVU0FNxLkIR2XezS-w&amp;oe=6ADEBA25</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>61593193674451</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Count Grof The Vizsla</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CountGrofTheVizsla</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: vizsla, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>1</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>vizsla</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-7.fna.fbcdn.net/v/t39.30808-1/768414017_122096558667439789_8787858061448834881_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=Q7GwPB1zoWAQ7kNvwE4S2IU&amp;_nc_oc=AdrJWa-HJdf4OudRxCmux71edOZRRK1QVxeaiUPRXQTH_XVGV10Kyc3WpL61YCTd23g&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-7.fna&amp;_nc_gid=g-FobwExjWrxaAfUZ3CzLg&amp;_nc_ss=7b2a8&amp;oh=00_AQNZOxdqUhsFYwioopO4XWovWQtJlcbcXQIILgaCpk2oZg&amp;oe=6ADEE664</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>61591834145189</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Great Dane Love</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GreatDaneLovee</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: great dane, P_dog=0.81)</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>adult_dog (P=0.81)</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>0.8103</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>great dane</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-4.fna.fbcdn.net/v/t39.30808-1/746842823_2832899100397008_4161057587275812338_n.jpg?stp=c320.0.1280.1280a_cp0_dst-jpg_tt6&amp;cstp=mx1280x1280&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=D-50LfbKEikQ7kNvwFyRvp7&amp;_nc_oc=AdrR32eESOy_2gZx5ZhweTbY-eQz1mQ-goX6p7Ype0KNpno-F9w_DC8t__NAfqsBrBc&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-4.fna&amp;_nc_gid=g-FobwExjWrxaAfUZ3CzLg&amp;_nc_ss=7b2a8&amp;oh=00_AQOz4VSk0RjIVhHuBMFATs8tVp8Xayg_UolcOE41vxw84g&amp;oe=6ADEE88D</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>61577796267591</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Élevage du Tonnerre d’Argent</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ElevageDuTonnerredArgent</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: canine, P_dog=0.72)</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>puppy (P=0.72)</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>0.7231</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>canine</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-8.fna.fbcdn.net/v/t39.30808-1/760984342_122212435868926542_8341279238099236164_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1254x1254&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=P9S3MET9VhQQ7kNvwHlOooS&amp;_nc_oc=AdqwKnAY58nCrLMvNOU8mgHpHPKLWdezy2Z4x9aYJ14iDLW8WX_mxG_A1kMUHXSYKUI&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-8.fna&amp;_nc_gid=ALBFQ_vA1Q6WGWb8Hr1SnA&amp;_nc_ss=7b2a8&amp;oh=00_AQMkdcnqI0SZFEgKBBVEEblmV_UOUip0bLW1qTRLlOh7yg&amp;oe=6ADEC2B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>100063490870885</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Jack russell de Capsil</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/jackrusselldecapsil</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: jack russell, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>jack russell</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-4.fna.fbcdn.net/v/t1.6435-1/162384489_130465989079763_909318710300129859_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1474x1475&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=QY6aFgeky-gQ7kNvwHy0bwK&amp;_nc_oc=AdrGuyMuUYjzSWQfSaujTsgMT3GYI6lx8QhPrzw6JwHnC8yTbJzSFcJ8jLD9D5s9B0g&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-4.fna&amp;_nc_gid=pWGTNWutzSM9DQXeV3n25w&amp;_nc_ss=7b2a8&amp;oh=00_AQO4Ig1mDOvyBO3U8NaVGsE_0gas8-jWEKXwlQ3WRfEGuw&amp;oe=6B0087D6</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>100064742856562</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Tuhannenjayhden terrierit</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lolajackrussellinterrieri</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: terrier, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>terrier</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-11.fna.fbcdn.net/v/t39.30808-1/788171641_1502149658619782_505961264761570581_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1086x1086&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=zfvnn9d3ykIQ7kNvwFGLyF8&amp;_nc_oc=AdoA_AFwaZNRN83ugx2NoxnY5NGQF5wyhyxsS5OG5TmxL-o_qzejetWoy4LqIELsByc&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-11.fna&amp;_nc_gid=pWGTNWutzSM9DQXeV3n25w&amp;_nc_ss=7b2a8&amp;oh=00_AQMxO_a6Twh6TGCZLyoNwCWNDdpB3jgVU6_bI7bmXKgwPw&amp;oe=6ADEDE28</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>61592766563310</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>CupidPup</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CupidPup</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: puppy, dog)</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>puppy, dog</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-3.fna.fbcdn.net/v/t39.30808-1/779017746_122109198381425552_3903327327137967765_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx536x536&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=q9-wDmbv9m8Q7kNvwGUz8Hg&amp;_nc_oc=AdrKQFZts07Rw2GgoYKV2ukT8tldhp20IStolMiMcj10CCOTj0sn2Pt4HGMcBOi_cRU&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-3.fna&amp;_nc_gid=l2JchbDwM67IjYOAd9YZ_w&amp;_nc_ss=7b2a8&amp;oh=00_AQOgfghJooQ8Io1cPbY8ynkLkNEyY_b_uHBcS9A9l4Z5gw&amp;oe=6ADEE05D</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>61591116954347</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Benta-Valley Kennel</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bentakennel</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: kennel)</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>kennel</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-11.fna.fbcdn.net/v/t39.30808-1/799316923_122115602541370565_4081854376755700726_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1254x1254&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=28Ej3wYPGXoQ7kNvwEKh96w&amp;_nc_oc=AdqBSm7xvjR4qluKeJUpQbaE2CX83q8ACs5h_7fFBu4dKF35vMDAk170NGj2wWRsRZo&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-11.fna&amp;_nc_gid=a144GRXcntJnMOrrBsvvPg&amp;_nc_ss=7b2a8&amp;oh=00_AQNXjzyv15dK0lNg6W9mipTMoFL-Zwv8-t8rkWp35MxFxg&amp;oe=6ADEBFC6</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>61590200701593</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Doggo Diaries</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Doggodiaries11</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: dog)</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-11.fna.fbcdn.net/v/t39.30808-1/702660234_122095476489340023_5772803633032787602_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=hGmp2o4p7OgQ7kNvwEnkl8c&amp;_nc_oc=Adpr5xUgIPypqGYaJzlVKAFnuTs0Z50ZUlFJjlL3bYEaQUVcjL1iLpdglIlD3uLOpok&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-11.fna&amp;_nc_gid=ex1sshGbjRJB6vstgwuYjw&amp;_nc_ss=7b2a8&amp;oh=00_AQMvlZPvHLHc76VqagvGQNf_E4nD3vKwomnNP49nG4-4ow&amp;oe=6ADEC12C</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>100050565657234</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Melissa Julie</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Tareq8652</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AI Thị giác nhận diện chó trưởng thành (Adult=0.87, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>1</v>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-7.fna.fbcdn.net/v/t39.30808-1/458774640_1134904921538352_1084980262848951044_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx526x526&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=LjAAKDSGV_8Q7kNvwGuJkh-&amp;_nc_oc=Adql0MBt3s845wjtQdQd02lceEFl_Exz6d97BCs4xkgh-U_R-tDVtDe3m41TnkDfFqg&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-7.fna&amp;_nc_gid=t0R9CPECWuAlwCSbvWf4IQ&amp;_nc_ss=7b2a8&amp;oh=00_AQNtl2q2AbYG2Qq_me8V0oyaCivdG3Fxc2ih7xqsiVxV3w&amp;oe=6ADEBC2E</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>100082898406313</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Joalbe Labradors &amp; Golden Retrievers</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/JoalbeLabs</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: golden retrievers, retrievers, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>1</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>golden retrievers, retrievers, labradors, goldens</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-11.fna.fbcdn.net/v/t39.30808-1/275724953_108238128489326_7066313032836647715_n.jpg?stp=c0.0.1484.1484a_cp0_dst-jpg_tt6&amp;cstp=mx1484x1484&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=qB9k4Xb8XD8Q7kNvwGK_-kb&amp;_nc_oc=AdonwPti8Ie4PQfJ-02qsrM7HQUswZMCV2dM0mE_HsjQuhQD_RVX6seOGOCZ9D3RmaI&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-11.fna&amp;_nc_gid=PDKx4fCNLMWCVUAZxGgktw&amp;_nc_ss=7b2a8&amp;oh=00_AQPRUnnz1FTanQcUmL1fW-FWzCB5_LLJFcz6xtOSCi_dng&amp;oe=6ADECBCB</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>100063484961246</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Windy Knoll Goldens</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/windyknollgoldens</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: goldens, golden retriever, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>goldens, golden retriever</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-6.fna.fbcdn.net/v/t39.30808-1/731808501_1655457386580411_7546275350165960697_n.jpg?stp=c0.294.1460.1460a_cp0_dst-jpg_tt6&amp;cstp=mx1460x1460&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=EJ6QpoaMsckQ7kNvwHkaIkP&amp;_nc_oc=Adrc76ISIg-A0XtaLxEZlctgPizB2ywPD_fioU8bkV91DkR5x6ZOxDrPTNZnXOc31eU&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-6.fna&amp;_nc_gid=PDKx4fCNLMWCVUAZxGgktw&amp;_nc_ss=7b2a8&amp;oh=00_AQPGppg83XnNmXN5P1g2sI5S0y8acxr6jZy6Xr5Xo7wThA&amp;oe=6ADEBFFD</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>61590797755179</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Beagles Lover</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/beaglelovershn</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: beagles, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>1</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>beagles</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-11.fna.fbcdn.net/v/t39.30808-1/719223452_122096483265359925_3535393914211963049_n.jpg?stp=c8.0.559.559a_cp0_dst-jpg_tt6&amp;cstp=mx559x559&amp;_nc_cat=102&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=K-sgpx_dYSYQ7kNvwGMHKql&amp;_nc_oc=Adq8soJEfV-ZpPJ-k05oWuu3t9csXa2ntmd6JquA-JH6DhBUY25GCxWcJXnwLWgHHyA&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-11.fna&amp;_nc_gid=U7N6TOfWN2XFC2nnYsz9WA&amp;_nc_ss=7b2a8&amp;oh=00_AQOToPJCyUolL_c0bRaPXZz0gm4C6njo_1dqQF8wRND9Wg&amp;oe=6ADEB970</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>61552444205399</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Golden Retriever Central</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GoldenRetrieverCentral</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: golden retriever, retriever, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>golden retriever, retriever, goldens</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-7.fna.fbcdn.net/v/t39.30808-1/633736330_122264231642081473_5524987927071470986_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1024x1024&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=aO-1BtyMKdIQ7kNvwHXQDlq&amp;_nc_oc=AdpaVVuZmFHjyArDoqfNG4eWFPcNreRicEgMlTD0Q1FnC_pREt309H1fcnPHg89AxuA&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-7.fna&amp;_nc_gid=U7N6TOfWN2XFC2nnYsz9WA&amp;_nc_ss=7b2a8&amp;oh=00_AQOZVmLgcBc0rq1_PbOHcC8qkjZpz5OT9kmcCPK34vuqpg&amp;oe=6ADECAA6</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>100057874636157</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Royal Vizslas</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/RoyalVizslas</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: vizsla, P_dog=0.57)</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>puppy (P=0.57)</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>0.5704</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>vizsla</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-3.fna.fbcdn.net/v/t39.30808-1/731038513_1581229137149559_7876230745013025798_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1254x1254&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=tpcakbdpU04Q7kNvwFBd1vC&amp;_nc_oc=Adr29PBLJ1K3yOszAGTe2wmD2ogFqGG3BZW4G0vfWbvz3hdmfV-3Dml4iWMVHZUr4RI&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-3.fna&amp;_nc_gid=IjqAcFEEVHv_1HD1xTh74A&amp;_nc_ss=7b2a8&amp;oh=00_AQM-ULhCSspaJZWLwOknovcPG3BGgew346EilVxV6S3Lww&amp;oe=6ADED693</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>100057875790774</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Eromit Labrador Retrievers</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/eromitlabs</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: retrievers, labrador)</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>retrievers, labrador</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-3.fna.fbcdn.net/v/t39.30808-1/302538708_504683728137483_3945852592640168843_n.png?stp=c128.0.552.552a_cp0_dst-png&amp;cstp=mx552x552&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=JtWquD3PE5wQ7kNvwGFiXJg&amp;_nc_oc=AdpqO4xbZVLP7L4DNKm_i56G6KVqIMXr3GXOb_1dySFg317o6myuNfO7PrO6jteERK0&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-3.fna&amp;_nc_gid=58aBJLJMdpcbJo5Wmvbsfg&amp;_nc_ss=7b2a8&amp;oh=00_AQPx3RNEWVoLzuXYxCOpsPWaphwzHrqUWs_Fr0cFra3Jpg&amp;oe=6ADEE790</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>100063752955883</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Bailiwick Kennel Page</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/BailiwickRetrievers</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: kennel)</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>1</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>kennel</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-10.fna.fbcdn.net/v/t39.30808-1/480434432_1159649292836825_4124578515465561687_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx612x612&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=xyO6npN34JMQ7kNvwHxG_gl&amp;_nc_oc=AdoN07nfxeWieAPi1-mDm6YbWVuG6JkhcS5ubV_6CQY-oDqrrINtM1EtIFrS9MEoF1M&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-10.fna&amp;_nc_gid=QeE199_4xp8tfcWL9gsgUw&amp;_nc_ss=7b2a8&amp;oh=00_AQO8uwy8DTOdxy_pXwvzlnT7xpXIFeg0jZf0-sq4IahsSA&amp;oe=6ADEE8C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>100064925761123</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Of The Saints Rottweilers</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/OfTheSaintsRottweilers</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: rottweilers, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>1</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>rottweilers</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-6.fna.fbcdn.net/v/t39.30808-1/367754729_685689826938537_7180713289749781704_n.jpg?stp=c0.0.720.720a_cp6_dst-jpg_tt6&amp;cstp=mx720x720&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=PS3Q0VHA9xcQ7kNvwGtdDQ7&amp;_nc_oc=Adqe4zcdQI7GpfTzotXKBrVjRXuy9v3wOMObHP-xhu-ogSaDvz1BLgu7HWtF6b4zDnA&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-6.fna&amp;_nc_gid=QeE199_4xp8tfcWL9gsgUw&amp;_nc_ss=7b2a8&amp;oh=00_AQMV6cXzc9Qkb9XQEhPZubZkE8Vnyqnwy8lWB28iTb8q5Q&amp;oe=6ADEE133</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>100076634641803</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>High Desert Labradors</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/HighDesertLabradors</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: labradors, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>1</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>labradors</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-4.fna.fbcdn.net/v/t39.30808-1/309443552_183876164176871_4978428568921530792_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx853x853&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=fY9uqlf787gQ7kNvwHUMsh9&amp;_nc_oc=AdqY9Kha0UGgfyEdq8dlUk0MpAlhqMNErLS7DEHXGhilsfmTabI8UdKlNTyplv3ExBs&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-4.fna&amp;_nc_gid=QeE199_4xp8tfcWL9gsgUw&amp;_nc_ss=7b2a8&amp;oh=00_AQNts3h45phv8T6A8wGvD2eRCpjFQE9cKaLLQovZQ2O1eQ&amp;oe=6ADEBBFB</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>100083008230958</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>B3 Labradors</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/B3Labradors</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: labradors, P_dog=0.95)</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>puppy (P=0.95)</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>0.9456</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>labradors</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-3.fna.fbcdn.net/v/t39.30808-1/760160833_1043948175048781_3428325921078086460_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1536x1537&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=jQNmO16fHB4Q7kNvwFET5n-&amp;_nc_oc=AdpHyuGLt5oQ9DruyWNgz9U40dwidcIuEJP0DtbxJAdFmvxNDnhvwmQamCFyZQSbpK4&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-3.fna&amp;_nc_gid=xIdNETCtyKuAJHbgZrr_Lg&amp;_nc_ss=7b2a8&amp;oh=00_AQPxsjhbqkG-TtMLvvvUYpNzbFE6bWlanlaRhszAlIUthQ&amp;oe=6ADEE8BE</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>100057576396012</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Travis’ Chocolate Labradors</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Travischocolatelabradors</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: labradors)</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>labradors</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-5.fna.fbcdn.net/v/t39.30808-1/306096077_531192185476657_3291338591321900134_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=AbKz9JgxPjYQ7kNvwGoHQe3&amp;_nc_oc=AdqD9gWGSHceHyz0CjQ6MmnYngsocYMkrIkbi6uV6VbnCmnqno-79r1niuXn75i_iKg&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-5.fna&amp;_nc_gid=EI1pIpQWqvcBeRw12t7CqA&amp;_nc_ss=7b2a8&amp;oh=00_AQMmuYvJjDCMObljBzXZ8EVTyjACda2CI5ZflxxBZv1JeA&amp;oe=6ADECB92</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>61587861193734</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Shepherd Team</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/shepherdteam.main</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: shepherd, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>1</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>shepherd</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-11.fna.fbcdn.net/v/t39.30808-1/788840025_122123158617262039_4138130132946908301_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1024x1024&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=ewHd_jAdxIYQ7kNvwG7CFtP&amp;_nc_oc=AdpKiLu2UiwRaYXwY_Qe6TQRNPZzeC0WzoYtGRcWJtTzpC4eujUetcq7MMmAM10i_q0&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-11.fna&amp;_nc_gid=EI1pIpQWqvcBeRw12t7CqA&amp;_nc_ss=7b2a8&amp;oh=00_AQN-Seh63jiE5TlB1-kC4Za9rFNYuKhlxw75i3yJa1kUEg&amp;oe=6ADEBE0C</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>100000150423660</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Liliy Zierova</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/liliy.zierova</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: kennel, breeder)</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>1</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>kennel, breeder</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-8.fna.fbcdn.net/v/t39.30808-1/727243678_28202474649340839_1820696212814651877_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx2048x2048&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=bQ0IReEHQfMQ7kNvwEkHcln&amp;_nc_oc=Adp0FOoPLXuyS1wUo87eYoFOK-zHbL9y9i68WnE6Cag034kscKlzyS5qK3j7lxGV0lo&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-8.fna&amp;_nc_gid=L9UgM_7E37MCP_tHB1AzrA&amp;_nc_ss=7b2a8&amp;oh=00_AQOGy2uhU4daM1h5jEfeBuKSuRDvEOnUj8ep8_3wchWhWg&amp;oe=6ADEBD11</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>100094072895433</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Westgate Goldens</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WestgateGoldens</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: goldens, golden retriever, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>1</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>goldens, golden retriever</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-8.fna.fbcdn.net/v/t39.30808-1/758193134_943150775497344_3604073036194876414_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=D-Cvw4AIdVMQ7kNvwFK9Ohq&amp;_nc_oc=AdrGWpCV4aOFgm70-mtlrXlCDPkJ4HMbDf0xlPaOBLjz6oa4rhk__tZHh8i1QiiLxGE&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-8.fna&amp;_nc_gid=Wxf27v4juzwm_d7019zGyg&amp;_nc_ss=7b2a8&amp;oh=00_AQOpyUBnvIG1JZ-RlL01_kRQEhf9fB7cjVYNdZOxeWlimA&amp;oe=6ADEC53B</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>100062598430160</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Enchanted Retrievers</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Enchantedretrievers</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: retrievers)</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>retrievers</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-6.fna.fbcdn.net/v/t39.30808-1/327003700_868179674288429_7318008481298332750_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx720x726&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=660mRRJKaC8Q7kNvwGrlPMq&amp;_nc_oc=AdorLAhndZvq49fZUDqtm8OoxMXl_eSyE8GPYZUVwt95kou5dILYZ5jYFkU2TZ_NLew&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-6.fna&amp;_nc_gid=Wxf27v4juzwm_d7019zGyg&amp;_nc_ss=7b2a8&amp;oh=00_AQNKgBYN6OaeJZi8l-DR_NS3E36by54x929CgBaPexVLuA&amp;oe=6ADEDB25</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>61557795360541</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Cute Dog Simba</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CuteDogSimba</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dog, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>1</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-4.fna.fbcdn.net/v/t39.30808-1/654308219_122231127392259845_1121846747960313492_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx486x491&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=adEuhPqBBZcQ7kNvwHj4qCs&amp;_nc_oc=Adp8Q1NfEhfYMgbGA58ieCGkm9CKSkwQgeGU4ajlRnGfYPSkTG3LmJtjA5MvNyCf3Hc&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-4.fna&amp;_nc_gid=Wxf27v4juzwm_d7019zGyg&amp;_nc_ss=7b2a8&amp;oh=00_AQMxTQ2EXX0_sSueR_0BEfYxYe8G9RLYIg-_0lbzF7VLQQ&amp;oe=6ADED30C</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>100044506773309</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Endless Mt. Labradors</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/emlabradors</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: labradors)</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>labradors</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-3.fna.fbcdn.net/v/t39.30808-1/763701025_1622308132596064_7964782675470577463_n.jpg?stp=c28.0.580.580a_cp6_dst-jpg_tt6&amp;cstp=mx580x580&amp;_nc_cat=102&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=bE9s3_E--7UQ7kNvwGFDQ3I&amp;_nc_oc=AdqgryalLDWXeCb9jUgHnstZYTbnfCRAYip8l0qF1d4aTZZJnKj32e0XFlwrfMPCWP4&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-3.fna&amp;_nc_gid=Wxf27v4juzwm_d7019zGyg&amp;_nc_ss=7b2a8&amp;oh=00_AQOf8CzLH7xw7IvBURQuAUJ1yOVRw2ibfHTQTguWrkDWjQ&amp;oe=6ADED3EB</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>100069521066191</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Shepherd's Way English Shepherds</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ShepherdsWay.EnglishShepherds</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: shepherd, shepherds, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>1</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>shepherd, shepherds</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-11.fna.fbcdn.net/v/t39.30808-1/459556431_835298262130868_7431452521616242736_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx2047x2048&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=X_S7d2v11DsQ7kNvwG9AH-T&amp;_nc_oc=AdrmtAM8w9K4PGetx-zgUol47bSh09s8JZ5uGOY2NSmQ47e0z-K8vAADhy4lUvPyYpo&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-11.fna&amp;_nc_gid=eFjKz0mNc3Kw8-KeKqb7sQ&amp;_nc_ss=7b2a8&amp;oh=00_AQOhAwEpIKdN0MrHzTH7EqnVumAKZA_YXvj4atXbrkh1mw&amp;oe=6ADEE0DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>61585601724093</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Rottweiler Legends</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/RottweilerLegends</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: rottweiler)</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>rottweiler</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-8.fna.fbcdn.net/v/t39.30808-1/602398062_2021566008688281_8056565105102010473_n.jpg?stp=c465.0.1117.1117a_cp0_dst-jpg_tt6&amp;cstp=mx1117x1117&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=y9xza2oozdcQ7kNvwGDVbi_&amp;_nc_oc=AdpmZHe3eeM4pEPsciGGp5Xl4BXtNcMqNt2J28uCrNMSe2-k24vhah4zN4SdhsOGE_c&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-8.fna&amp;_nc_gid=eFjKz0mNc3Kw8-KeKqb7sQ&amp;_nc_ss=7b2a8&amp;oh=00_AQPhM6ar6PTV5ddSfnORWlkD3D4QYOpK2RD6jxr66HMDcg&amp;oe=6ADEE3A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>100001688766508</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>София Милева</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sofia.mileva.2025</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: kennel, fci)</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>1</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>kennel, fci</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-6.fna.fbcdn.net/v/t39.30808-1/409916444_7027441537322069_5485516251846600476_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx2047x2048&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=_dKyeR2dK08Q7kNvwGSKGgI&amp;_nc_oc=Adqf1fo2fRHLnwz-t5-cLiTZXnsncY7wEzNSTkJdUoKzBTyfTCct8ehOPCrZEtYP-t8&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-6.fna&amp;_nc_gid=q2mnMUZUI1ZNyuXeWosblw&amp;_nc_ss=7b2a8&amp;oh=00_AQPZ251smzxxVI9aB2ACRe1E_FjgRPcIOWAKAAjJgdxE1A&amp;oe=6ADEDE28</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>100063557829931</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Curly Oak Kennels</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CurlyOakKennels</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: kennels)</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.95)</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>kennels</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-10.fna.fbcdn.net/v/t39.30808-1/644494279_1550881267040453_6610626484995088292_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=bDGebBH99XsQ7kNvwGyVFFc&amp;_nc_oc=AdqzbZr3qNEAYfufrJIW_Te2ZgANQMgmxXodFAQ9n9OHM77gwDZeiYysTmVPPcfAdyg&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-10.fna&amp;_nc_gid=jga4X5nHjfw-OQr_rKEY1w&amp;_nc_ss=7b2a8&amp;oh=00_AQM4KG9_dPNpUyyJDICvDeq4Z6xTEXuyUSbAzoYky4AAjQ&amp;oe=6ADEC911</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>100067126625595</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Cajun Water Retrievers</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CajunWaterRetrievers</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: retrievers, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>1</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>retrievers</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-5.fna.fbcdn.net/v/t39.30808-1/305271304_414023160845235_5046809754017833108_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x958&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=L1d959ft_PUQ7kNvwFV1swt&amp;_nc_oc=AdrlSKhiG3di9zhnojBa3JAR1BsqFomriE4ELJQEV_9mNkQFam4QuiSgYqB_3ryJoaU&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-5.fna&amp;_nc_gid=jga4X5nHjfw-OQr_rKEY1w&amp;_nc_ss=7b2a8&amp;oh=00_AQOZlm_tt-K97O32MdJ5JcKP1MgaXMqPRraPXLHAnLKz5g&amp;oe=6ADEE212</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>61592907083422</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Dog Paradise</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/dogparadisefb</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dog, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>1</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-6.fna.fbcdn.net/v/t39.30808-1/760472265_122094488577430236_7756804057685000845_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx360x365&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=Z_WzZPwDuEEQ7kNvwGIVAKh&amp;_nc_oc=AdpENI-TcCrqZtxomBSMIBW_7oexxSbxfAIb8V_5kD0hCZGzKVKMy0nUPmBjPonnV0s&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-6.fna&amp;_nc_gid=VI6dM6ibLogWdtK8X0CBQg&amp;_nc_ss=7b2a8&amp;oh=00_AQOzdw5NGf4iRv3vYzfFNQs-QcgylGUmysMU5kwdnoH7SA&amp;oe=6ADEDEE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>100067195304231</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Elvisbatzthelab</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/elvisbatzthelab</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AI Thị giác nhận diện chó trưởng thành (Adult=0.71, P_dog=0.98)</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>adult_dog (P=0.98)</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>0.9782999999999999</v>
+      </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-3.fna.fbcdn.net/v/t39.30808-1/416949533_694313346151836_7730579964566429374_n.jpg?stp=c517.0.1152.1152a_cp0_dst-jpg_tt6&amp;cstp=mx1152x1152&amp;_nc_cat=1&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=BToSisCmsoIQ7kNvwGHlbLH&amp;_nc_oc=Adr7x8y1GOUK42I9DAAFk0GtyfG9mKKrbGIezFwH-1bXD3fxEGEHjBvltZz4zzuUT5c&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-3.fna&amp;_nc_gid=VI6dM6ibLogWdtK8X0CBQg&amp;_nc_ss=7b2a8&amp;oh=00_AQPHlweGKNiPM0iBgpyXzlfwy519KcFusqVKXACsc_ExRw&amp;oe=6ADEBA9D</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>100092642324017</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Tussock Jack Russell Terriers</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/haidee.burrows</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: jack russell, terriers, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>1</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>jack russell, terriers</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-11.fna.fbcdn.net/v/t39.30808-1/480442425_558860470545359_1742690516810960007_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1536x1536&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=EbTN_Wx-OygQ7kNvwEAYMQx&amp;_nc_oc=Adrg2IK7ApZQRqvAVf9TMyy4ggHSFsmdDnQ2HRx1lRBoekUByHNzKajq3Dye42xQvzA&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-11.fna&amp;_nc_gid=VI6dM6ibLogWdtK8X0CBQg&amp;_nc_ss=7b2a8&amp;oh=00_AQPIUOrKUnyqcBq7r6HFEu3URviPymQZgKkUxEWUmxkX2w&amp;oe=6ADEC17A</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>61574234521502</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Teddy Bad Boy</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Teddybadboy1</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AI Thị giác nhận diện chó trưởng thành (Adult=0.93, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-9.fna.fbcdn.net/v/t39.30808-1/786268051_122190688124807817_5176560422516035687_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1166x1166&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=ofEq_G3LZOIQ7kNvwHZT4JQ&amp;_nc_oc=Adqj6PVHya5pIbYkJ85miIBBz49pKAS9yDYK4JY545W-qNPIQ58uynCDDRrXhX3EnJg&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-9.fna&amp;_nc_gid=sAFHUnkHFNeh1hcRNqjWDg&amp;_nc_ss=7b2a8&amp;oh=00_AQP9D5AfbU0WhupfAJAsCLEWp7q9rCd7u8d3-XbjnFN54g&amp;oe=6ADECF9B</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>100080095584422</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Akat Labrador</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/akat.labrador</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: kennel, labrador)</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>1</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>kennel, labrador</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-8.fna.fbcdn.net/v/t39.30808-1/474503963_610755344937646_1745461094526601207_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1040x1035&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=CRKtGyhHkxUQ7kNvwFvSrTy&amp;_nc_oc=AdoqJexr7yCtwjclMqeqEuvAZMwPT8J7k8o41vYPZIVWw_CP2mdXRu29m0SGW2nGgRk&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-8.fna&amp;_nc_gid=HUSD2epdJIoGJxjYQTXosg&amp;_nc_ss=7b2a8&amp;oh=00_AQNx6F4RxPy6-07eEzy00ZNPtxcSsdf9sWAhJSWcYAj2_g&amp;oe=6ADEDE5D</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>61565259196121</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Benny and Jett</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/BennyandJett</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AI Thị giác nhận diện chó trưởng thành (Adult=0.95, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>1</v>
+      </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-10.fna.fbcdn.net/v/t39.30808-1/702837545_122099842856508639_89586723838619756_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=myG9KnGnXaIQ7kNvwG4u3Yr&amp;_nc_oc=Adq5u8G5AeRtrzLMppBtwTizwnjUgr998lGzBQc-BxVLFjcQw48Qt2B_lupQRBFMSa8&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-10.fna&amp;_nc_gid=HUSD2epdJIoGJxjYQTXosg&amp;_nc_ss=7b2a8&amp;oh=00_AQPvX52Y7gQQhheqmWGBhIkigbFgfGMh0n10qfAkNlhArg&amp;oe=6ADECFBA</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1424606573</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Melissa Mershon</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/berriomelissa</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: k9, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>k9</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-4.fna.fbcdn.net/v/t39.30808-1/520074087_10240235337807511_8522772657524527713_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x960&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=BxJ5-WaQp50Q7kNvwGkVWYr&amp;_nc_oc=Adq8MyOp4SZTSpizKnYHrZ76riiWaou7oR_3q6gokIaCQPfroWDR1tfxZh2gMSlfsUw&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-4.fna&amp;_nc_gid=92f836k_oJ69WUwifeit2w&amp;_nc_ss=7b2a8&amp;oh=00_AQPxBiO1T5WKGnyAs7V09r8uYPuMgXeAUjLDDce04ew1Bw&amp;oe=6ADEC433</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>61590687576698</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Living on Labrador Time</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/livingonlabradortime</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: labrador, P_dog=0.99)</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>puppy (P=0.99)</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>0.9909</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>labrador</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-11.fna.fbcdn.net/v/t39.30808-1/720634497_122106304143356252_3230861867731265384_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1254x1254&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=2FiUQwhEse0Q7kNvwGNFDUT&amp;_nc_oc=AdqpNHzRcHuxj4W_xx7aSNbn8MJkB9a1xyM-A4pHJU3IpxpU6afxiRAzsqMmhV5_IT8&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-11.fna&amp;_nc_gid=92f836k_oJ69WUwifeit2w&amp;_nc_ss=7b2a8&amp;oh=00_AQPbF_28Jyx0qsfuhoF7Q0VPi56uIQDzpWsNKkgk3wYaAg&amp;oe=6ADEC4FF</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>100083733460399</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Birchwood Tennessee Silver Labs</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Birchwoodsilverlabs</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: labs, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>1</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>labs</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-7.fna.fbcdn.net/v/t39.30808-1/356831702_236925135775267_8082229228302631384_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1754x1754&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=ZSUhMo0TfCgQ7kNvwEZkv_c&amp;_nc_oc=AdpDVTduYqbw5OXlmiGu0fRC43Qh4M515kcYkXedv0ti2zXRiX_QcTNcvAAL9TO_mzc&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-7.fna&amp;_nc_gid=92f836k_oJ69WUwifeit2w&amp;_nc_ss=7b2a8&amp;oh=00_AQNfxcPwmn0tvOfyyz-Lzr8pH_xaH7phuSriXKf0niPn1w&amp;oe=6ADEBC04</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>61587590061189</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Hey Tomy Doggo</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/HeyTomyDoggo</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dog, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-8.fna.fbcdn.net/v/t39.30808-1/640679194_122105308935253002_529724390351121614_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx696x697&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=sImmLUYLaPkQ7kNvwFxXC2R&amp;_nc_oc=Adq2YDZ4XkHVfpwv4CavVHJY82pn54VVfKHI1sRJJ3sHqUSM_xiTfys1g_17PzPiHMs&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-8.fna&amp;_nc_gid=3_5yMv6PmDq2DzCkZ6CezQ&amp;_nc_ss=7b2a8&amp;oh=00_AQOxoCKTO-z7C8TMXSGgymTU0wq2ErW1KaMYbFCzeKPmPw&amp;oe=6ADEEC21</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>61593937491163</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Balck Labrador</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/blacklabrador24</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: labrador, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>1</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>labrador</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-7.fna.fbcdn.net/v/t39.30808-1/777298017_122093701329464583_3586754973459932425_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx736x746&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=iorGBBqG3QoQ7kNvwEzO4st&amp;_nc_oc=Adozovzi2hn_iiEAUCxDYhBS0c-mkewyuIU1RiMwOy4B7DNKj-vehqGWoArc6Nkt2RA&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-7.fna&amp;_nc_gid=Y7l8XW3XfRb5QWjqCK6tkg&amp;_nc_ss=7b2a8&amp;oh=00_AQPC5xxLdMh5FwX2F4BxYCCMkEyrpjb9Z1iyu-URcU-Lmg&amp;oe=6ADEC689</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>100084325923647</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Holley&amp;Tuner the Rotties</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/HolleyTunerEfi</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: rottie, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>1</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>rottie</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-5.fna.fbcdn.net/v/t39.30808-1/378274669_279724151515114_1601422720004676205_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1284x1284&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=z4Xf2vRwvigQ7kNvwFjzmSL&amp;_nc_oc=AdqCc8Jvq-chgH_t_B-zaI4qZvXrOAJrE7pJIKnKVJHYS9dJXoXEf2-0bbWMfPuULDo&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-5.fna&amp;_nc_gid=Y7l8XW3XfRb5QWjqCK6tkg&amp;_nc_ss=7b2a8&amp;oh=00_AQNtN9_6BFICR4DsT3RY-OcxCVLQoLgRDMr20NDbOLwoQw&amp;oe=6ADED0F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>61585980297712</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Just Puppies</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/justpuppieshq</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: puppies, puppy, dog)</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>puppy (P=0.99)</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>0.9903999999999999</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>puppies, puppy, dog</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-10.fna.fbcdn.net/v/t39.30808-1/817268969_122139407931199343_1258210750557734744_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1024x1024&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=6Nl_FJQCqJQQ7kNvwG-wFnN&amp;_nc_oc=AdqXOPaQk-pwxIigJiWWdeA8wKEzKebhcMB25FI-89cnYkPX-aH6ZgqplcSBoPK3ai8&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-10.fna&amp;_nc_gid=113CV-94GhBMVYYURyZ9WA&amp;_nc_ss=7b2a8&amp;oh=00_AQPkSCEasvyFnhFP3kUJhvWnBElBsTmpISnZ_SWGsCIbiQ&amp;oe=6ADECD36</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>677427313</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Kay Cook Exelby Labradors</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/kay.cook.5209</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: labradors, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>labradors</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-7.fna.fbcdn.net/v/t39.30808-1/666418495_10162554488987314_4974116361569081185_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1362x1362&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=rlZTwSO0pLYQ7kNvwEafTB-&amp;_nc_oc=Adpww88UQhbQk5c7Oy8VJrGpCLQeBlxJd7Yiw8FzYz69nlc1-OoSM3VrqU0Yknp6Wzk&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-7.fna&amp;_nc_gid=Hz4O75y4IKQem0j_OctRzg&amp;_nc_ss=7b2a8&amp;oh=00_AQNwgsVWa61jmxdZu3nNViaoYyIj0CctZwszUgMPgukCxw&amp;oe=6ADEBE95</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>61584921141507</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Apollo</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/apollogolden0</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Cún cưng đạt chuẩn AI Thị Giác (P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>1</v>
+      </c>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-7.fna.fbcdn.net/v/t39.30808-1/597471503_122093819247164038_2529134409623300229_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1280x1290&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=4yy4nI-UIagQ7kNvwFb0z02&amp;_nc_oc=AdrnV5I5740U1w_jBYSpOL_fibXYGGHhKri241tt5mvzylqWtOtwf7F6k7v54Kl_QO8&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-7.fna&amp;_nc_gid=Hz4O75y4IKQem0j_OctRzg&amp;_nc_ss=7b2a8&amp;oh=00_AQOENg84Ya1rxxpj3Mf4MZYHg5wHvUn9anzl3aBBivSUUg&amp;oe=6ADEEC5F</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>61575165165359</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>BAR L Labradors</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/barllabradors</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: labradors)</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>labradors</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-7.fna.fbcdn.net/v/t39.30808-1/775229241_122185772336838838_8151463793330168202_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1024x1024&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=_E2YpuiEVPkQ7kNvwEAavr0&amp;_nc_oc=Adr3r5z0tQWeapfOF1Y3tU71YzxXw9PE_xUrC5pfkKf3-91G75sSB1tiHfoXdwo66KE&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-7.fna&amp;_nc_gid=Hz4O75y4IKQem0j_OctRzg&amp;_nc_ss=7b2a8&amp;oh=00_AQOCfFPRqxjqqu-T-gztQSGxWKnLQgs1Wr4__jrxrcib9w&amp;oe=6ADEB6CD</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>100057302806604</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Rebel's Ridge AKC English Labs</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/rebelsridgeenglishlabs</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Trại chó xác thực qua NLP &amp; Từ khóa (akc, labs)</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>1</v>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>akc, labs</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-4.fna.fbcdn.net/v/t39.30808-1/574482615_1373157231271024_4658569782028203130_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx2048x2048&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=NQekvfIfGIcQ7kNvwFqzO6r&amp;_nc_oc=AdrOG4h4bQspegJbCbasYEALoT0xyGVvO5gMJd7h8vd_doi35Q8fv7tGwCCER-16rLo&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-4.fna&amp;_nc_gid=e0l2MBvbCSB31sDYG40JuQ&amp;_nc_ss=7b2a8&amp;oh=00_AQOPNb4bN3d5nLOffHxAUC9s2YwmNjI4Q2RrfmQSvv65xQ&amp;oe=6ADEC48F</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>100068487573004</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Elk Creek Gun Dogs</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ronelkcreekgundogs</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dogs, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>1</v>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>dogs</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-8.fna.fbcdn.net/v/t39.30808-1/650697837_1224303019862606_3686527487095261674_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1008x1008&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=JRRYyPh125gQ7kNvwEfZDcW&amp;_nc_oc=AdoYMnbCK6_2QHYHisoJxWyOQVJpZKBbuGt_pOTw7jxGfRIlKAn3dd3mX3N5F_oQsCI&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-8.fna&amp;_nc_gid=dIe1nZWae49vXPyc--fAAg&amp;_nc_ss=7b2a8&amp;oh=00_AQOSOUEsESNlYfUH3vi7z0yvvNrxdFKsO27Gjg-w6reqFg&amp;oe=6ADEC33A</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>100057095815124</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Bear Creek Dachshunds Backup Page</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bearcreekyorkies</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: dachshunds)</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>dachshunds</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-11.fna.fbcdn.net/v/t39.30808-1/756434785_1598360695410442_3565608818965275860_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1294x1293&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=be-7C7kRp18Q7kNvwHCmo8_&amp;_nc_oc=Adq_FvSHJpq0wpDYEBcTwPki5NRXJKexAP2N7FcPtEBaETnuYzS468m_isrxivMJUS0&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-11.fna&amp;_nc_gid=dIe1nZWae49vXPyc--fAAg&amp;_nc_ss=7b2a8&amp;oh=00_AQNu_0ptOMx7gQa1Q2roOTIsqMM-Pks5kEphazhB5uNH3w&amp;oe=6ADEC0A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>100058199374166</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Magnus The Therapy Dog</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/magnusthetherapydog</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: dog, P_dog=0.94)</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>puppy (P=0.94)</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>0.9429999999999999</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-9.fna.fbcdn.net/v/t39.30808-1/470865242_996292378987399_549693047878856482_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx2048x2048&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=jUJoEVhBLocQ7kNvwFoRsqm&amp;_nc_oc=AdpvpbFObicmDq7ZnucWT1xWxdDap5xgG97mExlQTf1E57_cdvnT64B2ZLbZEWXDhwI&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-9.fna&amp;_nc_gid=dIe1nZWae49vXPyc--fAAg&amp;_nc_ss=7b2a8&amp;oh=00_AQN40BGe9iNimjI1RKqcj6fk20Ofy6ikpPRmtR8-nix8Yg&amp;oe=6ADECDC8</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>61593725080944</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Lucy the Chocolate Lab</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lucy.the.chocolate.lab</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: lab, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>1</v>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>lab</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-10.fna.fbcdn.net/v/t39.30808-1/799172770_122106761007457502_3664214129017661907_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1024x1024&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=ugYNwkik4BQQ7kNvwFsu9Aj&amp;_nc_oc=AdocAoRbqqOJExLM53QUzp2i0SiyRrZIJEtbXhrpukehlRkuewEDwfx7xzSoxb1LTp8&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-10.fna&amp;_nc_gid=NPFc8eaFcKnCSJsaflzjow&amp;_nc_ss=7b2a8&amp;oh=00_AQO7pURs4lVyW5GdNjq7Uc_xqwkMuJmRQdpcExoKrqO7Xw&amp;oe=6ADED61B</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>100070107828453</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Killhamforge</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/killhamforge</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>AI Thị giác nhận diện cún con sắc nét (Puppy=0.98, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>1</v>
+      </c>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-3.fna.fbcdn.net/v/t39.30808-1/756042868_1345307854482796_5933321660750054745_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1080x1082&amp;_nc_cat=102&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=5hN-dPFEVxcQ7kNvwE_usEY&amp;_nc_oc=AdqsKunNFcSgBeDw4mHxdO6PJ19GdmAZTEDq0CNJMIxetnStEEOmIUPkCz1JlvaSMkE&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-3.fna&amp;_nc_gid=NPFc8eaFcKnCSJsaflzjow&amp;_nc_ss=7b2a8&amp;oh=00_AQOe3aH9tcG7bpfko1Si35_49Ti-QxEKvh70a-XUEpCJxw&amp;oe=6ADEC5DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>100081229211689</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Gavins Point Labs</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/gavinspointlabs</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: labs, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>0.9978</v>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>labs</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-10.fna.fbcdn.net/v/t39.30808-1/290357637_128703146513992_5832229842805142942_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1594x1594&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=d68E1XIsSzoQ7kNvwGFRZpb&amp;_nc_oc=AdrXmUcAuKnM0npjEBwWjB7UDjjmPwun3TOqhAMUOq8BrzXZwpbF5UjkuRHXaVjOB5U&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-10.fna&amp;_nc_gid=D20sM1mTm-_Laxf0oxxC2w&amp;_nc_ss=7b2a8&amp;oh=00_AQNWcIXG0N0XMVgtnxmKW2Hzucb5wZMLL8z-f1-yLBHpzw&amp;oe=6ADEEC56</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>1278979465</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Patt Pattisia Labrador</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/patt.panyawong</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: kennel, labrador, goldens)</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>1</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>kennel, labrador, goldens</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-11.fna.fbcdn.net/v/t39.30808-1/612456419_10243836148220667_6312644508797315004_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1559x1559&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=bWM35Edi24UQ7kNvwGVrGqS&amp;_nc_oc=AdotdOycwv-u9na-RA2xOOi0lyryReRBq3Jq2q2xXkqqB5SLrfbraq0xgqt5avMiyJw&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-11.fna&amp;_nc_gid=D20sM1mTm-_Laxf0oxxC2w&amp;_nc_ss=7b2a8&amp;oh=00_AQMb2zJESOwa15TzoJcOoaxhftXRWWpTQPVdOsgJWiab5w&amp;oe=6ADEBCB7</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>100077530491621</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Country Heart Labrador Retrievers</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CountryHeartLabradors</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: retrievers, labrador, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>1</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>retrievers, labrador</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-9.fna.fbcdn.net/v/t39.30808-1/467489698_593893683204976_8029473080393987530_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1536x1536&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=wHodH_M9SxgQ7kNvwG2jV-4&amp;_nc_oc=Adpha_gVD9Acn66lz4sl3Al0OtW29hj5D8FlGSxJJ006QvJ-npVU9i919yqu4ryVzBQ&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-9.fna&amp;_nc_gid=D20sM1mTm-_Laxf0oxxC2w&amp;_nc_ss=7b2a8&amp;oh=00_AQPcIYOTejgWxvXqwwCtS9IPzLXb7iRHwzEIFjYK1fzoXA&amp;oe=6ADEEA25</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>100092381136712</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Cutepuppy316</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Cutepuppy316</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>B2B Breeder / Chủ trại cún xác thực qua NLP &amp; Chân dung Chủ trại (Breeder: puppy, dog)</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>1</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>puppy, dog</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-3.fna.fbcdn.net/v/t39.30808-1/463020197_464902413265793_7509421627453956872_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx2048x2048&amp;_nc_cat=1&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=jTcvEiUZs9EQ7kNvwFJ11nv&amp;_nc_oc=AdpURLVZozfeWDPSke5IAugi9a4Ok-gEssIEoAfInwNwRZOn6tcKnixArGL1yBvTWoo&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-3.fna&amp;_nc_gid=D20sM1mTm-_Laxf0oxxC2w&amp;_nc_ss=7b2a8&amp;oh=00_AQMSg1LnaWqM6JD-GUedpYlKmHDO7ywVPILDE9T2ulkq9Q&amp;oe=6ADEBB4D</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>100064493719981</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Last Frontier Labradors</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LastFrontierLabs</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: labradors, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>puppy (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
+        <v>1</v>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>labradors</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-9.fna.fbcdn.net/v/t39.30808-1/327282530_600626841901155_1545445276623897061_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1440x1440&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=HAfuKjLmJfYQ7kNvwERId2E&amp;_nc_oc=AdpWEewMJS30CRHUSmS6aC-EZplv4k3c6mnn-3hDhrampWALCy3W65bpb0KeZjcba54&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-9.fna&amp;_nc_gid=Me26xbjSnSXqnuFN5tQbSQ&amp;_nc_ss=7b2a8&amp;oh=00_AQMRWAW7zrd85aV3o5D5CYjP8Cc7gl0n48wR-9uO2thjOA&amp;oe=6ADED0E8</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>61590486935768</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>The Trifecta Labradors</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Trifectalabradors</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: labradors, P_dog=1.00)</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>adult_dog (P=1.00)</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
+        <v>1</v>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>labradors</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-4.fna.fbcdn.net/v/t39.30808-1/741906810_122119189161349564_6735390622894065509_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx1082x1082&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=kM2GMIGDg70Q7kNvwEHyfSF&amp;_nc_oc=Ado8AXyTpMRRMjcUi5iMajM9IiAh_jtZrbrrrM0qGrpCBPo2wau00umNvVhKSyvl6Mo&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-4.fna&amp;_nc_gid=Me26xbjSnSXqnuFN5tQbSQ&amp;_nc_ss=7b2a8&amp;oh=00_AQMSiMM6fo2I7eJ8fxvmwrZWVZWKzyVhrxjRNFQMHv05FA&amp;oe=6ADEC81C</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>61575129002106</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Lord Jack The Yellow Lab</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lordjacktheyellowlab</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Chó xác thực qua Từ khóa &amp; AI (Từ khóa: lab, P_dog=0.98)</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>puppy (P=0.98)</t>
+        </is>
+      </c>
+      <c r="G173" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>lab</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-3.fna.fbcdn.net/v/t39.30808-1/641380115_122165487830837633_997392880214523819_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1198x1198&amp;_nc_cat=1&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=1_s5SeQRq1wQ7kNvwEJDLZv&amp;_nc_oc=Adqp1Gw8jgiVvkX6lH9ICyP3NlOYjPCH3G_vQdBuOCivrIBHue-LkopJ090QwbxaACs&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-3.fna&amp;_nc_gid=0byCmmhNXkR8bDVTRU7oNw&amp;_nc_ss=7b2a8&amp;oh=00_AQOjQTwuN3r687hJh0XIfBjTirIrWvqUVlbJNxAguwf7lw&amp;oe=6ADECA24</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>100063500594808</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Fairfax Pines Labrador Retrievers</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/fairfaxpinesenglishlabradorretrievers</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: retrievers, labrador)</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G174" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>retrievers, labrador</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-5.fna.fbcdn.net/v/t39.30808-1/449121936_985341813592496_9076357750249204002_n.jpg?stp=c111.111.1153.1153a_cp0_dst-jpg_tt6&amp;cstp=mx1153x1153&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=1N5VjHradYcQ7kNvwEiZ8Zd&amp;_nc_oc=Adqj0BmKtkkYbfyMtRlRgbfO_Da3u-QSbGFsd0joIc5h06FFwjQsmmLH_XDG0eaRB6w&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-5.fna&amp;_nc_gid=j8cNnzbk2aLFGEUNzBqFGA&amp;_nc_ss=7b2a8&amp;oh=00_AQPizBf--VOFF0gjTtCzqlf1lLMAyRd_WWIMcpraKTPecg&amp;oe=6ADEBF21</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>100092595634947</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Carolina Labradors</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/carolina.labs1</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Khách hàng nuôi cún xác thực qua NLP &amp; Tên (Từ khóa: labradors)</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>non_dog (P=0.85)</t>
+        </is>
+      </c>
+      <c r="G175" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>labradors</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>https://scontent.fsgn2-7.fna.fbcdn.net/v/t39.30808-1/628214735_839242312505616_8142150978904169452_n.jpg?stp=cp0_dst-jpg_tt6&amp;cstp=mx960x958&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=edd80f&amp;_nc_ohc=E1Diy3CwzXAQ7kNvwGLI8Op&amp;_nc_oc=Adqjvk5oyWaqBFvot8uPWnIr2yfWrzc_WvPQFEpWTy4tBSVmeSuUurfH_2cA--mecO4&amp;_nc_zt=24&amp;_nc_ht=scontent.fsgn2-7.fna&amp;_nc_gid=j8cNnzbk2aLFGEUNzBqFGA&amp;_nc_ss=7b2a8&amp;oh=00_AQMIuNrQ26MxKBftpLdbdC2pUEIO7bmZwxN0ESHNk3wGMw&amp;oe=6ADEBAFD</t>
         </is>
       </c>
     </row>
